--- a/naver-place-crawler/results_nail/강남_네일샵.xlsx
+++ b/naver-place-crawler/results_nail/강남_네일샵.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V438"/>
+  <dimension ref="A1:V445"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -41141,34 +41141,26 @@
     <row r="437">
       <c r="A437" t="inlineStr">
         <is>
-          <t>세무사</t>
+          <t>네일아트,네일샵</t>
         </is>
       </c>
       <c r="B437" t="inlineStr">
         <is>
-          <t>세성세무법인 삼성지점</t>
-        </is>
-      </c>
-      <c r="C437" t="inlineStr">
-        <is>
-          <t>sesung1216@naver.com</t>
-        </is>
-      </c>
+          <t>소금네일</t>
+        </is>
+      </c>
+      <c r="C437" t="inlineStr"/>
       <c r="D437" t="inlineStr"/>
-      <c r="E437" t="inlineStr">
-        <is>
-          <t>02-515-4642</t>
-        </is>
-      </c>
+      <c r="E437" t="inlineStr"/>
       <c r="F437" t="inlineStr"/>
       <c r="G437" t="inlineStr">
         <is>
-          <t>서울특별시 강남구 봉은사로 454 금탁타워 5층</t>
+          <t>서울특별시 강남구 개포로21길 10 1층</t>
         </is>
       </c>
       <c r="H437" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/sesung1216</t>
+          <t>https://www.instagram.com/sogeum_nail</t>
         </is>
       </c>
       <c r="I437" t="inlineStr">
@@ -41183,7 +41175,7 @@
       </c>
       <c r="K437" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L437" t="inlineStr">
@@ -41199,17 +41191,17 @@
       </c>
       <c r="O437" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P437" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="Q437" t="n">
-        <v>41</v>
+        <v>5</v>
       </c>
       <c r="R437" t="n">
-        <v>41</v>
+        <v>19</v>
       </c>
       <c r="S437" t="inlineStr">
         <is>
@@ -41218,12 +41210,12 @@
       </c>
       <c r="T437" t="inlineStr">
         <is>
-          <t>1397509005</t>
+          <t>1003640740</t>
         </is>
       </c>
       <c r="U437" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1397509005</t>
+          <t>https://m.place.naver.com/place/1003640740</t>
         </is>
       </c>
       <c r="V437" t="inlineStr">
@@ -41235,39 +41227,35 @@
     <row r="438">
       <c r="A438" t="inlineStr">
         <is>
-          <t>속눈썹증모,연장</t>
+          <t>네일아트,네일샵</t>
         </is>
       </c>
       <c r="B438" t="inlineStr">
         <is>
-          <t>워너비뷰티</t>
+          <t>나다움네일</t>
         </is>
       </c>
       <c r="C438" t="inlineStr">
         <is>
-          <t>doyi2@naver.com</t>
+          <t>onsoo1214@naver.com</t>
         </is>
       </c>
       <c r="D438" t="inlineStr"/>
-      <c r="E438" t="inlineStr">
-        <is>
-          <t>02-552-4043</t>
-        </is>
-      </c>
+      <c r="E438" t="inlineStr"/>
       <c r="F438" t="inlineStr"/>
       <c r="G438" t="inlineStr">
         <is>
-          <t>서울특별시 강남구 삼성로100길 25 2층</t>
+          <t>서울특별시 강남구 도산대로12길 9 3층</t>
         </is>
       </c>
       <c r="H438" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_xaxfwTC</t>
+          <t>https://instagram.com/nail_nadaum</t>
         </is>
       </c>
       <c r="I438" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J438" t="inlineStr">
@@ -41288,39 +41276,689 @@
       <c r="M438" t="inlineStr"/>
       <c r="N438" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O438" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P438" t="n">
+        <v>298</v>
+      </c>
+      <c r="Q438" t="n">
+        <v>49</v>
+      </c>
+      <c r="R438" t="n">
+        <v>347</v>
+      </c>
+      <c r="S438" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T438" t="inlineStr">
+        <is>
+          <t>1587252605</t>
+        </is>
+      </c>
+      <c r="U438" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1587252605</t>
+        </is>
+      </c>
+      <c r="V438" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="439">
+      <c r="A439" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B439" t="inlineStr">
+        <is>
+          <t>뷰티인비</t>
+        </is>
+      </c>
+      <c r="C439" t="inlineStr">
+        <is>
+          <t>beauty_inb@naver.com</t>
+        </is>
+      </c>
+      <c r="D439" t="inlineStr"/>
+      <c r="E439" t="inlineStr"/>
+      <c r="F439" t="inlineStr"/>
+      <c r="G439" t="inlineStr">
+        <is>
+          <t>서울특별시 강남구 선릉로120길 14 2층</t>
+        </is>
+      </c>
+      <c r="H439" t="inlineStr">
+        <is>
+          <t>http://www.instagram.com/beauty_inb</t>
+        </is>
+      </c>
+      <c r="I439" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J439" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K439" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L439" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M439" t="inlineStr"/>
+      <c r="N439" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O439" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P439" t="n">
+        <v>412</v>
+      </c>
+      <c r="Q439" t="n">
+        <v>103</v>
+      </c>
+      <c r="R439" t="n">
+        <v>515</v>
+      </c>
+      <c r="S439" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T439" t="inlineStr">
+        <is>
+          <t>1028984231</t>
+        </is>
+      </c>
+      <c r="U439" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1028984231</t>
+        </is>
+      </c>
+      <c r="V439" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="440">
+      <c r="A440" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B440" t="inlineStr">
+        <is>
+          <t>레푸스 강남세곡점</t>
+        </is>
+      </c>
+      <c r="C440" t="inlineStr">
+        <is>
+          <t>segok569@naver.com</t>
+        </is>
+      </c>
+      <c r="D440" t="inlineStr"/>
+      <c r="E440" t="inlineStr">
+        <is>
+          <t>0507-1494-9977</t>
+        </is>
+      </c>
+      <c r="F440" t="inlineStr"/>
+      <c r="G440" t="inlineStr">
+        <is>
+          <t>서울특별시 강남구 헌릉로 569 강남리더스프라자 4층 401-1호</t>
+        </is>
+      </c>
+      <c r="H440" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/segok569</t>
+        </is>
+      </c>
+      <c r="I440" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J440" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K440" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L440" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M440" t="inlineStr"/>
+      <c r="N440" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O440" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P440" t="n">
+        <v>190</v>
+      </c>
+      <c r="Q440" t="n">
+        <v>480</v>
+      </c>
+      <c r="R440" t="n">
+        <v>670</v>
+      </c>
+      <c r="S440" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T440" t="inlineStr">
+        <is>
+          <t>1486263326</t>
+        </is>
+      </c>
+      <c r="U440" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1486263326</t>
+        </is>
+      </c>
+      <c r="V440" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="441">
+      <c r="A441" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B441" t="inlineStr">
+        <is>
+          <t>엠블랑네일</t>
+        </is>
+      </c>
+      <c r="C441" t="inlineStr">
+        <is>
+          <t>jieun4294@naver.com</t>
+        </is>
+      </c>
+      <c r="D441" t="inlineStr"/>
+      <c r="E441" t="inlineStr"/>
+      <c r="F441" t="inlineStr"/>
+      <c r="G441" t="inlineStr">
+        <is>
+          <t>서울특별시 강남구 도산대로85길 30 2층 211호</t>
+        </is>
+      </c>
+      <c r="H441" t="inlineStr">
+        <is>
+          <t>http://pf.kakao.com/_xkRxhxcG</t>
+        </is>
+      </c>
+      <c r="I441" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J441" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K441" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L441" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M441" t="inlineStr"/>
+      <c r="N441" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O441" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P441" t="n">
+        <v>19</v>
+      </c>
+      <c r="Q441" t="n">
+        <v>0</v>
+      </c>
+      <c r="R441" t="n">
+        <v>19</v>
+      </c>
+      <c r="S441" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T441" t="inlineStr">
+        <is>
+          <t>1850537636</t>
+        </is>
+      </c>
+      <c r="U441" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1850537636</t>
+        </is>
+      </c>
+      <c r="V441" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="442">
+      <c r="A442" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B442" t="inlineStr">
+        <is>
+          <t>에스제이네일</t>
+        </is>
+      </c>
+      <c r="C442" t="inlineStr">
+        <is>
+          <t>g4um4j4k@naver.com</t>
+        </is>
+      </c>
+      <c r="D442" t="inlineStr"/>
+      <c r="E442" t="inlineStr">
+        <is>
+          <t>0507-1463-4145</t>
+        </is>
+      </c>
+      <c r="F442" t="inlineStr"/>
+      <c r="G442" t="inlineStr">
+        <is>
+          <t>서울특별시 강남구 논현로102길 8 101호</t>
+        </is>
+      </c>
+      <c r="H442" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I442" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J442" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K442" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L442" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M442" t="inlineStr"/>
+      <c r="N442" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O442" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P442" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q442" t="n">
+        <v>2</v>
+      </c>
+      <c r="R442" t="n">
+        <v>8</v>
+      </c>
+      <c r="S442" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T442" t="inlineStr">
+        <is>
+          <t>37191892</t>
+        </is>
+      </c>
+      <c r="U442" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/37191892</t>
+        </is>
+      </c>
+      <c r="V442" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="443">
+      <c r="A443" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B443" t="inlineStr">
+        <is>
+          <t>네일앙뜨 강남역점</t>
+        </is>
+      </c>
+      <c r="C443" t="inlineStr">
+        <is>
+          <t>mel_holic@naver.com</t>
+        </is>
+      </c>
+      <c r="D443" t="inlineStr"/>
+      <c r="E443" t="inlineStr">
+        <is>
+          <t>0507-1445-2523</t>
+        </is>
+      </c>
+      <c r="F443" t="inlineStr"/>
+      <c r="G443" t="inlineStr">
+        <is>
+          <t>서울특별시 강남구 도곡로3길 19 105호, 106호</t>
+        </is>
+      </c>
+      <c r="H443" t="inlineStr">
+        <is>
+          <t>http://pf.kakao.com/_glsmxj</t>
+        </is>
+      </c>
+      <c r="I443" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J443" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K443" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L443" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M443" t="inlineStr"/>
+      <c r="N443" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O443" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P443" t="n">
+        <v>533</v>
+      </c>
+      <c r="Q443" t="n">
+        <v>58</v>
+      </c>
+      <c r="R443" t="n">
+        <v>591</v>
+      </c>
+      <c r="S443" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T443" t="inlineStr">
+        <is>
+          <t>1957548139</t>
+        </is>
+      </c>
+      <c r="U443" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1957548139</t>
+        </is>
+      </c>
+      <c r="V443" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="444">
+      <c r="A444" t="inlineStr">
+        <is>
+          <t>세무사</t>
+        </is>
+      </c>
+      <c r="B444" t="inlineStr">
+        <is>
+          <t>세성세무법인 삼성지점</t>
+        </is>
+      </c>
+      <c r="C444" t="inlineStr">
+        <is>
+          <t>sesung1216@naver.com</t>
+        </is>
+      </c>
+      <c r="D444" t="inlineStr"/>
+      <c r="E444" t="inlineStr">
+        <is>
+          <t>02-515-4642</t>
+        </is>
+      </c>
+      <c r="F444" t="inlineStr"/>
+      <c r="G444" t="inlineStr">
+        <is>
+          <t>서울특별시 강남구 봉은사로 454 금탁타워 5층</t>
+        </is>
+      </c>
+      <c r="H444" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/sesung1216</t>
+        </is>
+      </c>
+      <c r="I444" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J444" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K444" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L444" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M444" t="inlineStr"/>
+      <c r="N444" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O444" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P444" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q444" t="n">
+        <v>41</v>
+      </c>
+      <c r="R444" t="n">
+        <v>41</v>
+      </c>
+      <c r="S444" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T444" t="inlineStr">
+        <is>
+          <t>1397509005</t>
+        </is>
+      </c>
+      <c r="U444" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1397509005</t>
+        </is>
+      </c>
+      <c r="V444" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="445">
+      <c r="A445" t="inlineStr">
+        <is>
+          <t>속눈썹증모,연장</t>
+        </is>
+      </c>
+      <c r="B445" t="inlineStr">
+        <is>
+          <t>워너비뷰티</t>
+        </is>
+      </c>
+      <c r="C445" t="inlineStr">
+        <is>
+          <t>doyi2@naver.com</t>
+        </is>
+      </c>
+      <c r="D445" t="inlineStr"/>
+      <c r="E445" t="inlineStr">
+        <is>
+          <t>02-552-4043</t>
+        </is>
+      </c>
+      <c r="F445" t="inlineStr"/>
+      <c r="G445" t="inlineStr">
+        <is>
+          <t>서울특별시 강남구 삼성로100길 25 2층</t>
+        </is>
+      </c>
+      <c r="H445" t="inlineStr">
+        <is>
+          <t>http://pf.kakao.com/_xaxfwTC</t>
+        </is>
+      </c>
+      <c r="I445" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J445" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K445" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L445" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M445" t="inlineStr"/>
+      <c r="N445" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O445" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P445" t="n">
         <v>228</v>
       </c>
-      <c r="Q438" t="n">
+      <c r="Q445" t="n">
         <v>65</v>
       </c>
-      <c r="R438" t="n">
+      <c r="R445" t="n">
         <v>293</v>
       </c>
-      <c r="S438" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T438" t="inlineStr">
+      <c r="S445" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T445" t="inlineStr">
         <is>
           <t>1523636698</t>
         </is>
       </c>
-      <c r="U438" t="inlineStr">
+      <c r="U445" t="inlineStr">
         <is>
           <t>https://m.place.naver.com/place/1523636698</t>
         </is>
       </c>
-      <c r="V438" t="inlineStr">
+      <c r="V445" t="inlineStr">
         <is>
           <t>2026-04-14</t>
         </is>

--- a/naver-place-crawler/results_nail/강남_네일샵.xlsx
+++ b/naver-place-crawler/results_nail/강남_네일샵.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V341"/>
+  <dimension ref="A1:V444"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -32035,34 +32035,30 @@
     <row r="340">
       <c r="A340" t="inlineStr">
         <is>
-          <t>세무사</t>
+          <t>네일아트,네일샵</t>
         </is>
       </c>
       <c r="B340" t="inlineStr">
         <is>
-          <t>세성세무법인 삼성지점</t>
+          <t>서정적네일</t>
         </is>
       </c>
       <c r="C340" t="inlineStr">
         <is>
-          <t>sesung1216@naver.com</t>
+          <t>rito_bt@naver.com</t>
         </is>
       </c>
       <c r="D340" t="inlineStr"/>
-      <c r="E340" t="inlineStr">
-        <is>
-          <t>02-515-4642</t>
-        </is>
-      </c>
+      <c r="E340" t="inlineStr"/>
       <c r="F340" t="inlineStr"/>
       <c r="G340" t="inlineStr">
         <is>
-          <t>서울특별시 강남구 봉은사로 454 금탁타워 5층</t>
+          <t>서울특별시 강남구 자곡로 201 라르고 B동 117호 서정적네일</t>
         </is>
       </c>
       <c r="H340" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/sesung1216</t>
+          <t>http://www.instagram.com/nail_seojung</t>
         </is>
       </c>
       <c r="I340" t="inlineStr">
@@ -32077,7 +32073,7 @@
       </c>
       <c r="K340" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L340" t="inlineStr">
@@ -32093,17 +32089,17 @@
       </c>
       <c r="O340" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P340" t="n">
-        <v>0</v>
+        <v>270</v>
       </c>
       <c r="Q340" t="n">
-        <v>44</v>
+        <v>1</v>
       </c>
       <c r="R340" t="n">
-        <v>44</v>
+        <v>271</v>
       </c>
       <c r="S340" t="inlineStr">
         <is>
@@ -32112,12 +32108,12 @@
       </c>
       <c r="T340" t="inlineStr">
         <is>
-          <t>1397509005</t>
+          <t>1087290493</t>
         </is>
       </c>
       <c r="U340" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1397509005</t>
+          <t>https://m.place.naver.com/place/1087290493</t>
         </is>
       </c>
       <c r="V340" t="inlineStr">
@@ -32129,96 +32125,9486 @@
     <row r="341">
       <c r="A341" t="inlineStr">
         <is>
-          <t>속눈썹증모,연장</t>
+          <t>네일아트,네일샵</t>
         </is>
       </c>
       <c r="B341" t="inlineStr">
         <is>
-          <t>워너비뷰티</t>
-        </is>
-      </c>
-      <c r="C341" t="inlineStr">
-        <is>
-          <t>wannabe1105@naver.com</t>
-        </is>
-      </c>
+          <t>언드네일</t>
+        </is>
+      </c>
+      <c r="C341" t="inlineStr"/>
       <c r="D341" t="inlineStr"/>
       <c r="E341" t="inlineStr">
         <is>
-          <t>02-552-4043</t>
+          <t>0507-1349-0237</t>
         </is>
       </c>
       <c r="F341" t="inlineStr"/>
       <c r="G341" t="inlineStr">
         <is>
+          <t>서울특별시 강남구 학동로45길 3-4 4층</t>
+        </is>
+      </c>
+      <c r="H341" t="inlineStr">
+        <is>
+          <t>http://pf.kakao.com/_xoxeKNn</t>
+        </is>
+      </c>
+      <c r="I341" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J341" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K341" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L341" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M341" t="inlineStr"/>
+      <c r="N341" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O341" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P341" t="n">
+        <v>49</v>
+      </c>
+      <c r="Q341" t="n">
+        <v>1</v>
+      </c>
+      <c r="R341" t="n">
+        <v>50</v>
+      </c>
+      <c r="S341" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T341" t="inlineStr">
+        <is>
+          <t>2082058115</t>
+        </is>
+      </c>
+      <c r="U341" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2082058115</t>
+        </is>
+      </c>
+      <c r="V341" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B342" t="inlineStr">
+        <is>
+          <t>인비네일샵 압구정점</t>
+        </is>
+      </c>
+      <c r="C342" t="inlineStr">
+        <is>
+          <t>kingcair@naver.com</t>
+        </is>
+      </c>
+      <c r="D342" t="inlineStr"/>
+      <c r="E342" t="inlineStr">
+        <is>
+          <t>0507-1413-8864</t>
+        </is>
+      </c>
+      <c r="F342" t="inlineStr"/>
+      <c r="G342" t="inlineStr">
+        <is>
+          <t>서울특별시 강남구 압구정로 334 한양상가 207호</t>
+        </is>
+      </c>
+      <c r="H342" t="inlineStr">
+        <is>
+          <t>http://invinail.co.kr/</t>
+        </is>
+      </c>
+      <c r="I342" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J342" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K342" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L342" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M342" t="inlineStr"/>
+      <c r="N342" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O342" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P342" t="n">
+        <v>19</v>
+      </c>
+      <c r="Q342" t="n">
+        <v>0</v>
+      </c>
+      <c r="R342" t="n">
+        <v>19</v>
+      </c>
+      <c r="S342" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T342" t="inlineStr">
+        <is>
+          <t>36960199</t>
+        </is>
+      </c>
+      <c r="U342" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/36960199</t>
+        </is>
+      </c>
+      <c r="V342" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B343" t="inlineStr">
+        <is>
+          <t>네일 앤 젤</t>
+        </is>
+      </c>
+      <c r="C343" t="inlineStr">
+        <is>
+          <t>zzzopq123@naver.com</t>
+        </is>
+      </c>
+      <c r="D343" t="inlineStr"/>
+      <c r="E343" t="inlineStr">
+        <is>
+          <t>02-508-4905</t>
+        </is>
+      </c>
+      <c r="F343" t="inlineStr"/>
+      <c r="G343" t="inlineStr">
+        <is>
+          <t>서울특별시 강남구 삼성로 150 1층 108호</t>
+        </is>
+      </c>
+      <c r="H343" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I343" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J343" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K343" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L343" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M343" t="inlineStr"/>
+      <c r="N343" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O343" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P343" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q343" t="n">
+        <v>1</v>
+      </c>
+      <c r="R343" t="n">
+        <v>8</v>
+      </c>
+      <c r="S343" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T343" t="inlineStr">
+        <is>
+          <t>37427551</t>
+        </is>
+      </c>
+      <c r="U343" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/37427551</t>
+        </is>
+      </c>
+      <c r="V343" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B344" t="inlineStr">
+        <is>
+          <t>살롱드마리 네일</t>
+        </is>
+      </c>
+      <c r="C344" t="inlineStr"/>
+      <c r="D344" t="inlineStr"/>
+      <c r="E344" t="inlineStr">
+        <is>
+          <t>0506-487-1171</t>
+        </is>
+      </c>
+      <c r="F344" t="inlineStr"/>
+      <c r="G344" t="inlineStr">
+        <is>
+          <t>서울특별시 강남구 테헤란로64길 14 1층 107호</t>
+        </is>
+      </c>
+      <c r="H344" t="inlineStr">
+        <is>
+          <t>http://pf.kakao.com/_Tbxlqxb/45328000</t>
+        </is>
+      </c>
+      <c r="I344" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J344" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K344" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L344" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M344" t="inlineStr"/>
+      <c r="N344" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O344" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P344" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q344" t="n">
+        <v>1</v>
+      </c>
+      <c r="R344" t="n">
+        <v>1</v>
+      </c>
+      <c r="S344" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T344" t="inlineStr">
+        <is>
+          <t>2060514833</t>
+        </is>
+      </c>
+      <c r="U344" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2060514833</t>
+        </is>
+      </c>
+      <c r="V344" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B345" t="inlineStr">
+        <is>
+          <t>슈애네일 청담점</t>
+        </is>
+      </c>
+      <c r="C345" t="inlineStr"/>
+      <c r="D345" t="inlineStr"/>
+      <c r="E345" t="inlineStr"/>
+      <c r="F345" t="inlineStr"/>
+      <c r="G345" t="inlineStr">
+        <is>
+          <t>서울특별시 강남구 도산대로81길 31</t>
+        </is>
+      </c>
+      <c r="H345" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I345" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J345" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K345" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L345" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M345" t="inlineStr"/>
+      <c r="N345" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O345" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P345" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q345" t="n">
+        <v>0</v>
+      </c>
+      <c r="R345" t="n">
+        <v>0</v>
+      </c>
+      <c r="S345" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T345" t="inlineStr">
+        <is>
+          <t>38782427</t>
+        </is>
+      </c>
+      <c r="U345" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/38782427</t>
+        </is>
+      </c>
+      <c r="V345" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B346" t="inlineStr">
+        <is>
+          <t>어썸네일</t>
+        </is>
+      </c>
+      <c r="C346" t="inlineStr"/>
+      <c r="D346" t="inlineStr"/>
+      <c r="E346" t="inlineStr"/>
+      <c r="F346" t="inlineStr"/>
+      <c r="G346" t="inlineStr">
+        <is>
+          <t>서울특별시 강남구 남부순환로378길 14 1층</t>
+        </is>
+      </c>
+      <c r="H346" t="inlineStr">
+        <is>
+          <t>https://pf.kakao.com/_xbnCxnb</t>
+        </is>
+      </c>
+      <c r="I346" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J346" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K346" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L346" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M346" t="inlineStr"/>
+      <c r="N346" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O346" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P346" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q346" t="n">
+        <v>8</v>
+      </c>
+      <c r="R346" t="n">
+        <v>11</v>
+      </c>
+      <c r="S346" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T346" t="inlineStr">
+        <is>
+          <t>37917809</t>
+        </is>
+      </c>
+      <c r="U346" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/37917809</t>
+        </is>
+      </c>
+      <c r="V346" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B347" t="inlineStr">
+        <is>
+          <t>다바다네일 논현점</t>
+        </is>
+      </c>
+      <c r="C347" t="inlineStr"/>
+      <c r="D347" t="inlineStr"/>
+      <c r="E347" t="inlineStr">
+        <is>
+          <t>0507-1393-8865</t>
+        </is>
+      </c>
+      <c r="F347" t="inlineStr"/>
+      <c r="G347" t="inlineStr">
+        <is>
+          <t>서울특별시 강남구 강남대로118길 60</t>
+        </is>
+      </c>
+      <c r="H347" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/davada_2021</t>
+        </is>
+      </c>
+      <c r="I347" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J347" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K347" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L347" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M347" t="inlineStr"/>
+      <c r="N347" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O347" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P347" t="n">
+        <v>217</v>
+      </c>
+      <c r="Q347" t="n">
+        <v>63</v>
+      </c>
+      <c r="R347" t="n">
+        <v>280</v>
+      </c>
+      <c r="S347" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T347" t="inlineStr">
+        <is>
+          <t>1871608707</t>
+        </is>
+      </c>
+      <c r="U347" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1871608707</t>
+        </is>
+      </c>
+      <c r="V347" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="348">
+      <c r="A348" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B348" t="inlineStr">
+        <is>
+          <t>티파니네일</t>
+        </is>
+      </c>
+      <c r="C348" t="inlineStr"/>
+      <c r="D348" t="inlineStr"/>
+      <c r="E348" t="inlineStr"/>
+      <c r="F348" t="inlineStr"/>
+      <c r="G348" t="inlineStr">
+        <is>
+          <t>서울특별시 강남구 삼성로 212 은마아파트상가 130호</t>
+        </is>
+      </c>
+      <c r="H348" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I348" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J348" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K348" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L348" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M348" t="inlineStr"/>
+      <c r="N348" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O348" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P348" t="n">
+        <v>9</v>
+      </c>
+      <c r="Q348" t="n">
+        <v>0</v>
+      </c>
+      <c r="R348" t="n">
+        <v>9</v>
+      </c>
+      <c r="S348" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T348" t="inlineStr">
+        <is>
+          <t>35021811</t>
+        </is>
+      </c>
+      <c r="U348" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/35021811</t>
+        </is>
+      </c>
+      <c r="V348" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="349">
+      <c r="A349" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B349" t="inlineStr">
+        <is>
+          <t>엘슈네일</t>
+        </is>
+      </c>
+      <c r="C349" t="inlineStr">
+        <is>
+          <t>leena004@naver.com</t>
+        </is>
+      </c>
+      <c r="D349" t="inlineStr"/>
+      <c r="E349" t="inlineStr">
+        <is>
+          <t>0507-1436-7791</t>
+        </is>
+      </c>
+      <c r="F349" t="inlineStr"/>
+      <c r="G349" t="inlineStr">
+        <is>
+          <t>서울특별시 강남구 강남대로118길 59 2층</t>
+        </is>
+      </c>
+      <c r="H349" t="inlineStr">
+        <is>
+          <t>http://www.instagram.com/elchounail</t>
+        </is>
+      </c>
+      <c r="I349" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J349" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K349" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L349" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M349" t="inlineStr"/>
+      <c r="N349" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O349" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P349" t="n">
+        <v>151</v>
+      </c>
+      <c r="Q349" t="n">
+        <v>20</v>
+      </c>
+      <c r="R349" t="n">
+        <v>171</v>
+      </c>
+      <c r="S349" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T349" t="inlineStr">
+        <is>
+          <t>1246175984</t>
+        </is>
+      </c>
+      <c r="U349" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1246175984</t>
+        </is>
+      </c>
+      <c r="V349" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="350">
+      <c r="A350" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B350" t="inlineStr">
+        <is>
+          <t>네일앙뜨 강남역점</t>
+        </is>
+      </c>
+      <c r="C350" t="inlineStr"/>
+      <c r="D350" t="inlineStr"/>
+      <c r="E350" t="inlineStr">
+        <is>
+          <t>0507-1445-2523</t>
+        </is>
+      </c>
+      <c r="F350" t="inlineStr"/>
+      <c r="G350" t="inlineStr">
+        <is>
+          <t>서울특별시 강남구 도곡로3길 19 105호, 106호</t>
+        </is>
+      </c>
+      <c r="H350" t="inlineStr">
+        <is>
+          <t>http://pf.kakao.com/_glsmxj</t>
+        </is>
+      </c>
+      <c r="I350" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J350" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K350" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L350" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M350" t="inlineStr"/>
+      <c r="N350" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O350" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P350" t="n">
+        <v>539</v>
+      </c>
+      <c r="Q350" t="n">
+        <v>59</v>
+      </c>
+      <c r="R350" t="n">
+        <v>598</v>
+      </c>
+      <c r="S350" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T350" t="inlineStr">
+        <is>
+          <t>1957548139</t>
+        </is>
+      </c>
+      <c r="U350" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1957548139</t>
+        </is>
+      </c>
+      <c r="V350" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="351">
+      <c r="A351" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B351" t="inlineStr">
+        <is>
+          <t>선릉 네일 보에나</t>
+        </is>
+      </c>
+      <c r="C351" t="inlineStr"/>
+      <c r="D351" t="inlineStr"/>
+      <c r="E351" t="inlineStr">
+        <is>
+          <t>0507-1486-0412</t>
+        </is>
+      </c>
+      <c r="F351" t="inlineStr"/>
+      <c r="G351" t="inlineStr">
+        <is>
+          <t>서울특별시 강남구 선릉로 514 성원빌딩b1 119호</t>
+        </is>
+      </c>
+      <c r="H351" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/nail_boena/</t>
+        </is>
+      </c>
+      <c r="I351" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J351" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K351" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L351" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M351" t="inlineStr"/>
+      <c r="N351" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O351" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P351" t="n">
+        <v>147</v>
+      </c>
+      <c r="Q351" t="n">
+        <v>82</v>
+      </c>
+      <c r="R351" t="n">
+        <v>229</v>
+      </c>
+      <c r="S351" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T351" t="inlineStr">
+        <is>
+          <t>35117729</t>
+        </is>
+      </c>
+      <c r="U351" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/35117729</t>
+        </is>
+      </c>
+      <c r="V351" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="352">
+      <c r="A352" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B352" t="inlineStr">
+        <is>
+          <t>더네일스튜디오</t>
+        </is>
+      </c>
+      <c r="C352" t="inlineStr"/>
+      <c r="D352" t="inlineStr"/>
+      <c r="E352" t="inlineStr"/>
+      <c r="F352" t="inlineStr"/>
+      <c r="G352" t="inlineStr">
+        <is>
+          <t>서울특별시 강남구 선릉로157길 13-3 로건빌딩 4층</t>
+        </is>
+      </c>
+      <c r="H352" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/thenailstudio_</t>
+        </is>
+      </c>
+      <c r="I352" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J352" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K352" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L352" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M352" t="inlineStr"/>
+      <c r="N352" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O352" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P352" t="n">
+        <v>9</v>
+      </c>
+      <c r="Q352" t="n">
+        <v>15</v>
+      </c>
+      <c r="R352" t="n">
+        <v>24</v>
+      </c>
+      <c r="S352" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T352" t="inlineStr">
+        <is>
+          <t>21884512</t>
+        </is>
+      </c>
+      <c r="U352" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/21884512</t>
+        </is>
+      </c>
+      <c r="V352" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="353">
+      <c r="A353" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B353" t="inlineStr">
+        <is>
+          <t>제이블리</t>
+        </is>
+      </c>
+      <c r="C353" t="inlineStr"/>
+      <c r="D353" t="inlineStr"/>
+      <c r="E353" t="inlineStr"/>
+      <c r="F353" t="inlineStr"/>
+      <c r="G353" t="inlineStr">
+        <is>
+          <t>서울특별시 강남구 학동로 342 Sk허브블루빌딩 지하1층 106호</t>
+        </is>
+      </c>
+      <c r="H353" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/j.vely.nail</t>
+        </is>
+      </c>
+      <c r="I353" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J353" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K353" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L353" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M353" t="inlineStr"/>
+      <c r="N353" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O353" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P353" t="n">
+        <v>21</v>
+      </c>
+      <c r="Q353" t="n">
+        <v>19</v>
+      </c>
+      <c r="R353" t="n">
+        <v>40</v>
+      </c>
+      <c r="S353" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T353" t="inlineStr">
+        <is>
+          <t>1641958617</t>
+        </is>
+      </c>
+      <c r="U353" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1641958617</t>
+        </is>
+      </c>
+      <c r="V353" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="354">
+      <c r="A354" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B354" t="inlineStr">
+        <is>
+          <t>네일살롱</t>
+        </is>
+      </c>
+      <c r="C354" t="inlineStr"/>
+      <c r="D354" t="inlineStr"/>
+      <c r="E354" t="inlineStr">
+        <is>
+          <t>02-544-4758</t>
+        </is>
+      </c>
+      <c r="F354" t="inlineStr"/>
+      <c r="G354" t="inlineStr">
+        <is>
+          <t>서울특별시 강남구 언주로114길 11</t>
+        </is>
+      </c>
+      <c r="H354" t="inlineStr">
+        <is>
+          <t>http://instagram.com/nail_salon4758</t>
+        </is>
+      </c>
+      <c r="I354" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J354" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K354" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L354" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M354" t="inlineStr"/>
+      <c r="N354" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O354" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P354" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q354" t="n">
+        <v>8</v>
+      </c>
+      <c r="R354" t="n">
+        <v>16</v>
+      </c>
+      <c r="S354" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T354" t="inlineStr">
+        <is>
+          <t>1252146109</t>
+        </is>
+      </c>
+      <c r="U354" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1252146109</t>
+        </is>
+      </c>
+      <c r="V354" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="355">
+      <c r="A355" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B355" t="inlineStr">
+        <is>
+          <t>네일 바이 단</t>
+        </is>
+      </c>
+      <c r="C355" t="inlineStr"/>
+      <c r="D355" t="inlineStr"/>
+      <c r="E355" t="inlineStr">
+        <is>
+          <t>0507-1366-0737</t>
+        </is>
+      </c>
+      <c r="F355" t="inlineStr"/>
+      <c r="G355" t="inlineStr">
+        <is>
+          <t>서울특별시 강남구 테헤란로4길 46 쌍용플래티넘밸류 상가 1층 104호</t>
+        </is>
+      </c>
+      <c r="H355" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/nail_by_dan_</t>
+        </is>
+      </c>
+      <c r="I355" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J355" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K355" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L355" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M355" t="inlineStr"/>
+      <c r="N355" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O355" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P355" t="n">
+        <v>170</v>
+      </c>
+      <c r="Q355" t="n">
+        <v>16</v>
+      </c>
+      <c r="R355" t="n">
+        <v>186</v>
+      </c>
+      <c r="S355" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T355" t="inlineStr">
+        <is>
+          <t>2054628396</t>
+        </is>
+      </c>
+      <c r="U355" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2054628396</t>
+        </is>
+      </c>
+      <c r="V355" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="356">
+      <c r="A356" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B356" t="inlineStr">
+        <is>
+          <t>홍혜선프로네일</t>
+        </is>
+      </c>
+      <c r="C356" t="inlineStr"/>
+      <c r="D356" t="inlineStr"/>
+      <c r="E356" t="inlineStr">
+        <is>
+          <t>0507-1389-2368</t>
+        </is>
+      </c>
+      <c r="F356" t="inlineStr"/>
+      <c r="G356" t="inlineStr">
+        <is>
+          <t>서울특별시 강남구 학동로38길 40 1층 101호</t>
+        </is>
+      </c>
+      <c r="H356" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/honghyesun_pronail/</t>
+        </is>
+      </c>
+      <c r="I356" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J356" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K356" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L356" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M356" t="inlineStr"/>
+      <c r="N356" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O356" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P356" t="n">
+        <v>397</v>
+      </c>
+      <c r="Q356" t="n">
+        <v>133</v>
+      </c>
+      <c r="R356" t="n">
+        <v>530</v>
+      </c>
+      <c r="S356" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T356" t="inlineStr">
+        <is>
+          <t>1488876783</t>
+        </is>
+      </c>
+      <c r="U356" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1488876783</t>
+        </is>
+      </c>
+      <c r="V356" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="357">
+      <c r="A357" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B357" t="inlineStr">
+        <is>
+          <t>네일야르</t>
+        </is>
+      </c>
+      <c r="C357" t="inlineStr"/>
+      <c r="D357" t="inlineStr"/>
+      <c r="E357" t="inlineStr">
+        <is>
+          <t>02-501-7873</t>
+        </is>
+      </c>
+      <c r="F357" t="inlineStr"/>
+      <c r="G357" t="inlineStr">
+        <is>
+          <t>서울특별시 강남구 테헤란로4길 6 센트럴에비뉴 2층207호 네일야르</t>
+        </is>
+      </c>
+      <c r="H357" t="inlineStr">
+        <is>
+          <t>http://www.instagram.com/nail_yarr</t>
+        </is>
+      </c>
+      <c r="I357" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J357" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K357" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L357" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M357" t="inlineStr"/>
+      <c r="N357" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O357" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P357" t="n">
+        <v>78</v>
+      </c>
+      <c r="Q357" t="n">
+        <v>34</v>
+      </c>
+      <c r="R357" t="n">
+        <v>112</v>
+      </c>
+      <c r="S357" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T357" t="inlineStr">
+        <is>
+          <t>1319876790</t>
+        </is>
+      </c>
+      <c r="U357" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1319876790</t>
+        </is>
+      </c>
+      <c r="V357" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="358">
+      <c r="A358" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B358" t="inlineStr">
+        <is>
+          <t>네일킹왁싱</t>
+        </is>
+      </c>
+      <c r="C358" t="inlineStr"/>
+      <c r="D358" t="inlineStr"/>
+      <c r="E358" t="inlineStr">
+        <is>
+          <t>02-557-1003</t>
+        </is>
+      </c>
+      <c r="F358" t="inlineStr"/>
+      <c r="G358" t="inlineStr">
+        <is>
+          <t>서울특별시 강남구 역삼로69길 25</t>
+        </is>
+      </c>
+      <c r="H358" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I358" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J358" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K358" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L358" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M358" t="inlineStr"/>
+      <c r="N358" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O358" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P358" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q358" t="n">
+        <v>23</v>
+      </c>
+      <c r="R358" t="n">
+        <v>33</v>
+      </c>
+      <c r="S358" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T358" t="inlineStr">
+        <is>
+          <t>640677691</t>
+        </is>
+      </c>
+      <c r="U358" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/640677691</t>
+        </is>
+      </c>
+      <c r="V358" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="359">
+      <c r="A359" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B359" t="inlineStr">
+        <is>
+          <t>보벨르네일</t>
+        </is>
+      </c>
+      <c r="C359" t="inlineStr"/>
+      <c r="D359" t="inlineStr"/>
+      <c r="E359" t="inlineStr">
+        <is>
+          <t>0507-1308-4255</t>
+        </is>
+      </c>
+      <c r="F359" t="inlineStr"/>
+      <c r="G359" t="inlineStr">
+        <is>
+          <t>서울특별시 강남구 삼성로71길 25 1층 103호 보벨르네일(Beau Belle Nail)</t>
+        </is>
+      </c>
+      <c r="H359" t="inlineStr">
+        <is>
+          <t>https://keywordco.my.canva.site/beaubelle-nail</t>
+        </is>
+      </c>
+      <c r="I359" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J359" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K359" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L359" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M359" t="inlineStr"/>
+      <c r="N359" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O359" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P359" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q359" t="n">
+        <v>8</v>
+      </c>
+      <c r="R359" t="n">
+        <v>13</v>
+      </c>
+      <c r="S359" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T359" t="inlineStr">
+        <is>
+          <t>2012748069</t>
+        </is>
+      </c>
+      <c r="U359" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2012748069</t>
+        </is>
+      </c>
+      <c r="V359" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="360">
+      <c r="A360" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B360" t="inlineStr">
+        <is>
+          <t>도쿄네일 신사점</t>
+        </is>
+      </c>
+      <c r="C360" t="inlineStr">
+        <is>
+          <t>yurinail0610@naver.com</t>
+        </is>
+      </c>
+      <c r="D360" t="inlineStr"/>
+      <c r="E360" t="inlineStr"/>
+      <c r="F360" t="inlineStr"/>
+      <c r="G360" t="inlineStr">
+        <is>
+          <t>서울특별시 강남구 논현로149길 65 2층 201호</t>
+        </is>
+      </c>
+      <c r="H360" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/yurinail0610</t>
+        </is>
+      </c>
+      <c r="I360" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J360" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K360" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L360" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M360" t="inlineStr"/>
+      <c r="N360" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O360" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P360" t="n">
+        <v>83</v>
+      </c>
+      <c r="Q360" t="n">
+        <v>58</v>
+      </c>
+      <c r="R360" t="n">
+        <v>141</v>
+      </c>
+      <c r="S360" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T360" t="inlineStr">
+        <is>
+          <t>1676138057</t>
+        </is>
+      </c>
+      <c r="U360" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1676138057</t>
+        </is>
+      </c>
+      <c r="V360" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="361">
+      <c r="A361" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B361" t="inlineStr">
+        <is>
+          <t>보니크</t>
+        </is>
+      </c>
+      <c r="C361" t="inlineStr"/>
+      <c r="D361" t="inlineStr"/>
+      <c r="E361" t="inlineStr">
+        <is>
+          <t>0507-1349-8293</t>
+        </is>
+      </c>
+      <c r="F361" t="inlineStr"/>
+      <c r="G361" t="inlineStr">
+        <is>
+          <t>서울특별시 강남구 논현로66길 9 1층 1호</t>
+        </is>
+      </c>
+      <c r="H361" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/bonique_nail</t>
+        </is>
+      </c>
+      <c r="I361" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J361" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K361" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L361" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M361" t="inlineStr"/>
+      <c r="N361" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O361" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P361" t="n">
+        <v>15</v>
+      </c>
+      <c r="Q361" t="n">
+        <v>2</v>
+      </c>
+      <c r="R361" t="n">
+        <v>17</v>
+      </c>
+      <c r="S361" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T361" t="inlineStr">
+        <is>
+          <t>2064544033</t>
+        </is>
+      </c>
+      <c r="U361" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2064544033</t>
+        </is>
+      </c>
+      <c r="V361" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="362">
+      <c r="A362" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B362" t="inlineStr">
+        <is>
+          <t>코코네일</t>
+        </is>
+      </c>
+      <c r="C362" t="inlineStr"/>
+      <c r="D362" t="inlineStr"/>
+      <c r="E362" t="inlineStr">
+        <is>
+          <t>02-545-6278</t>
+        </is>
+      </c>
+      <c r="F362" t="inlineStr"/>
+      <c r="G362" t="inlineStr">
+        <is>
+          <t>서울특별시 강남구 학동로77길 27 대림아파트상가 1층</t>
+        </is>
+      </c>
+      <c r="H362" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I362" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J362" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K362" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L362" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M362" t="inlineStr"/>
+      <c r="N362" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O362" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P362" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q362" t="n">
+        <v>1</v>
+      </c>
+      <c r="R362" t="n">
+        <v>4</v>
+      </c>
+      <c r="S362" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T362" t="inlineStr">
+        <is>
+          <t>31536180</t>
+        </is>
+      </c>
+      <c r="U362" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/31536180</t>
+        </is>
+      </c>
+      <c r="V362" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="363">
+      <c r="A363" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B363" t="inlineStr">
+        <is>
+          <t>도로시</t>
+        </is>
+      </c>
+      <c r="C363" t="inlineStr">
+        <is>
+          <t>pedibaehr@naver.com</t>
+        </is>
+      </c>
+      <c r="D363" t="inlineStr"/>
+      <c r="E363" t="inlineStr">
+        <is>
+          <t>0507-1387-4909</t>
+        </is>
+      </c>
+      <c r="F363" t="inlineStr"/>
+      <c r="G363" t="inlineStr">
+        <is>
+          <t>서울특별시 강남구 삼성로 651 상가동 3층 309호</t>
+        </is>
+      </c>
+      <c r="H363" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/dorothybeauty__</t>
+        </is>
+      </c>
+      <c r="I363" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J363" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K363" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L363" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M363" t="inlineStr"/>
+      <c r="N363" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O363" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P363" t="n">
+        <v>43</v>
+      </c>
+      <c r="Q363" t="n">
+        <v>76</v>
+      </c>
+      <c r="R363" t="n">
+        <v>119</v>
+      </c>
+      <c r="S363" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T363" t="inlineStr">
+        <is>
+          <t>1192134039</t>
+        </is>
+      </c>
+      <c r="U363" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1192134039</t>
+        </is>
+      </c>
+      <c r="V363" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="364">
+      <c r="A364" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B364" t="inlineStr">
+        <is>
+          <t>코코드레스네일</t>
+        </is>
+      </c>
+      <c r="C364" t="inlineStr"/>
+      <c r="D364" t="inlineStr"/>
+      <c r="E364" t="inlineStr">
+        <is>
+          <t>0507-1408-8090</t>
+        </is>
+      </c>
+      <c r="F364" t="inlineStr"/>
+      <c r="G364" t="inlineStr">
+        <is>
+          <t>서울특별시 강남구 논현로115길 71 1층(논현동) 코코드레스네일</t>
+        </is>
+      </c>
+      <c r="H364" t="inlineStr">
+        <is>
+          <t>http://www.instagram.com/cocohhlee/</t>
+        </is>
+      </c>
+      <c r="I364" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J364" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K364" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L364" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M364" t="inlineStr"/>
+      <c r="N364" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O364" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P364" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q364" t="n">
+        <v>11</v>
+      </c>
+      <c r="R364" t="n">
+        <v>21</v>
+      </c>
+      <c r="S364" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T364" t="inlineStr">
+        <is>
+          <t>400677213</t>
+        </is>
+      </c>
+      <c r="U364" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/400677213</t>
+        </is>
+      </c>
+      <c r="V364" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="365">
+      <c r="A365" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B365" t="inlineStr">
+        <is>
+          <t>논현언니네일</t>
+        </is>
+      </c>
+      <c r="C365" t="inlineStr"/>
+      <c r="D365" t="inlineStr"/>
+      <c r="E365" t="inlineStr">
+        <is>
+          <t>0507-1347-2107</t>
+        </is>
+      </c>
+      <c r="F365" t="inlineStr"/>
+      <c r="G365" t="inlineStr">
+        <is>
+          <t>서울특별시 강남구 강남대로122길 20 202호</t>
+        </is>
+      </c>
+      <c r="H365" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/nhunni_nail</t>
+        </is>
+      </c>
+      <c r="I365" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J365" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K365" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L365" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M365" t="inlineStr"/>
+      <c r="N365" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O365" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P365" t="n">
+        <v>369</v>
+      </c>
+      <c r="Q365" t="n">
+        <v>10</v>
+      </c>
+      <c r="R365" t="n">
+        <v>379</v>
+      </c>
+      <c r="S365" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T365" t="inlineStr">
+        <is>
+          <t>1009426089</t>
+        </is>
+      </c>
+      <c r="U365" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1009426089</t>
+        </is>
+      </c>
+      <c r="V365" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="366">
+      <c r="A366" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B366" t="inlineStr">
+        <is>
+          <t>제이네일</t>
+        </is>
+      </c>
+      <c r="C366" t="inlineStr"/>
+      <c r="D366" t="inlineStr"/>
+      <c r="E366" t="inlineStr">
+        <is>
+          <t>0507-1362-6427</t>
+        </is>
+      </c>
+      <c r="F366" t="inlineStr"/>
+      <c r="G366" t="inlineStr">
+        <is>
+          <t>서울특별시 강남구 선릉로 206 동부센트레빌 상가 1층 117호</t>
+        </is>
+      </c>
+      <c r="H366" t="inlineStr">
+        <is>
+          <t>https://homefine2470.mycafe24.com/</t>
+        </is>
+      </c>
+      <c r="I366" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J366" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K366" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L366" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M366" t="inlineStr"/>
+      <c r="N366" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O366" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P366" t="n">
+        <v>33</v>
+      </c>
+      <c r="Q366" t="n">
+        <v>3</v>
+      </c>
+      <c r="R366" t="n">
+        <v>36</v>
+      </c>
+      <c r="S366" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T366" t="inlineStr">
+        <is>
+          <t>2070234334</t>
+        </is>
+      </c>
+      <c r="U366" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2070234334</t>
+        </is>
+      </c>
+      <c r="V366" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="367">
+      <c r="A367" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B367" t="inlineStr">
+        <is>
+          <t>나다움네일</t>
+        </is>
+      </c>
+      <c r="C367" t="inlineStr"/>
+      <c r="D367" t="inlineStr"/>
+      <c r="E367" t="inlineStr"/>
+      <c r="F367" t="inlineStr"/>
+      <c r="G367" t="inlineStr">
+        <is>
+          <t>서울특별시 강남구 도산대로12길 9 3층</t>
+        </is>
+      </c>
+      <c r="H367" t="inlineStr">
+        <is>
+          <t>https://instagram.com/nail_nadaum</t>
+        </is>
+      </c>
+      <c r="I367" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J367" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K367" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L367" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M367" t="inlineStr"/>
+      <c r="N367" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O367" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P367" t="n">
+        <v>298</v>
+      </c>
+      <c r="Q367" t="n">
+        <v>49</v>
+      </c>
+      <c r="R367" t="n">
+        <v>347</v>
+      </c>
+      <c r="S367" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T367" t="inlineStr">
+        <is>
+          <t>1587252605</t>
+        </is>
+      </c>
+      <c r="U367" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1587252605</t>
+        </is>
+      </c>
+      <c r="V367" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="368">
+      <c r="A368" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B368" t="inlineStr">
+        <is>
+          <t>네일제트</t>
+        </is>
+      </c>
+      <c r="C368" t="inlineStr"/>
+      <c r="D368" t="inlineStr"/>
+      <c r="E368" t="inlineStr">
+        <is>
+          <t>0507-1317-2227</t>
+        </is>
+      </c>
+      <c r="F368" t="inlineStr"/>
+      <c r="G368" t="inlineStr">
+        <is>
+          <t>서울특별시 강남구 삼성로107길 18 201호</t>
+        </is>
+      </c>
+      <c r="H368" t="inlineStr">
+        <is>
+          <t>https://pf.kakao.com/_aeZxhX/friend</t>
+        </is>
+      </c>
+      <c r="I368" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J368" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K368" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L368" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M368" t="inlineStr"/>
+      <c r="N368" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O368" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P368" t="n">
+        <v>15</v>
+      </c>
+      <c r="Q368" t="n">
+        <v>0</v>
+      </c>
+      <c r="R368" t="n">
+        <v>15</v>
+      </c>
+      <c r="S368" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T368" t="inlineStr">
+        <is>
+          <t>2099735314</t>
+        </is>
+      </c>
+      <c r="U368" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2099735314</t>
+        </is>
+      </c>
+      <c r="V368" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="369">
+      <c r="A369" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B369" t="inlineStr">
+        <is>
+          <t>드네일 강남점</t>
+        </is>
+      </c>
+      <c r="C369" t="inlineStr"/>
+      <c r="D369" t="inlineStr"/>
+      <c r="E369" t="inlineStr">
+        <is>
+          <t>0507-1398-8664</t>
+        </is>
+      </c>
+      <c r="F369" t="inlineStr"/>
+      <c r="G369" t="inlineStr">
+        <is>
+          <t>서울특별시 강남구 학동로56길 42 6층</t>
+        </is>
+      </c>
+      <c r="H369" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I369" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J369" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K369" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L369" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M369" t="inlineStr"/>
+      <c r="N369" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O369" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P369" t="n">
+        <v>11</v>
+      </c>
+      <c r="Q369" t="n">
+        <v>23</v>
+      </c>
+      <c r="R369" t="n">
+        <v>34</v>
+      </c>
+      <c r="S369" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T369" t="inlineStr">
+        <is>
+          <t>1929849640</t>
+        </is>
+      </c>
+      <c r="U369" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1929849640</t>
+        </is>
+      </c>
+      <c r="V369" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="370">
+      <c r="A370" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B370" t="inlineStr">
+        <is>
+          <t>르누아 네일</t>
+        </is>
+      </c>
+      <c r="C370" t="inlineStr"/>
+      <c r="D370" t="inlineStr"/>
+      <c r="E370" t="inlineStr"/>
+      <c r="F370" t="inlineStr"/>
+      <c r="G370" t="inlineStr">
+        <is>
+          <t>서울특별시 강남구 삼성로75길 42 1층 101호</t>
+        </is>
+      </c>
+      <c r="H370" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/lenoir_nail</t>
+        </is>
+      </c>
+      <c r="I370" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J370" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K370" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L370" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M370" t="inlineStr"/>
+      <c r="N370" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O370" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P370" t="n">
+        <v>82</v>
+      </c>
+      <c r="Q370" t="n">
+        <v>0</v>
+      </c>
+      <c r="R370" t="n">
+        <v>82</v>
+      </c>
+      <c r="S370" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T370" t="inlineStr">
+        <is>
+          <t>1560804311</t>
+        </is>
+      </c>
+      <c r="U370" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1560804311</t>
+        </is>
+      </c>
+      <c r="V370" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="371">
+      <c r="A371" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B371" t="inlineStr">
+        <is>
+          <t>디올네일</t>
+        </is>
+      </c>
+      <c r="C371" t="inlineStr"/>
+      <c r="D371" t="inlineStr"/>
+      <c r="E371" t="inlineStr"/>
+      <c r="F371" t="inlineStr"/>
+      <c r="G371" t="inlineStr">
+        <is>
+          <t>서울특별시 강남구 학동로 417 제일빌딩 1층</t>
+        </is>
+      </c>
+      <c r="H371" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/dior__nail</t>
+        </is>
+      </c>
+      <c r="I371" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J371" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K371" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L371" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M371" t="inlineStr"/>
+      <c r="N371" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O371" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P371" t="n">
+        <v>53</v>
+      </c>
+      <c r="Q371" t="n">
+        <v>38</v>
+      </c>
+      <c r="R371" t="n">
+        <v>91</v>
+      </c>
+      <c r="S371" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T371" t="inlineStr">
+        <is>
+          <t>12864942</t>
+        </is>
+      </c>
+      <c r="U371" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/12864942</t>
+        </is>
+      </c>
+      <c r="V371" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="372">
+      <c r="A372" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B372" t="inlineStr">
+        <is>
+          <t>트리뷰티</t>
+        </is>
+      </c>
+      <c r="C372" t="inlineStr"/>
+      <c r="D372" t="inlineStr"/>
+      <c r="E372" t="inlineStr">
+        <is>
+          <t>0507-1366-4050</t>
+        </is>
+      </c>
+      <c r="F372" t="inlineStr"/>
+      <c r="G372" t="inlineStr">
+        <is>
+          <t>서울특별시 강남구 테헤란로14길 40-6 1층 트리뷰티</t>
+        </is>
+      </c>
+      <c r="H372" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/tree.beauty_?igsh=ZmluOXhpaWo3Mmts&amp;utm_source=qr</t>
+        </is>
+      </c>
+      <c r="I372" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J372" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K372" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L372" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M372" t="inlineStr"/>
+      <c r="N372" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O372" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P372" t="n">
+        <v>311</v>
+      </c>
+      <c r="Q372" t="n">
+        <v>53</v>
+      </c>
+      <c r="R372" t="n">
+        <v>364</v>
+      </c>
+      <c r="S372" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T372" t="inlineStr">
+        <is>
+          <t>1230803157</t>
+        </is>
+      </c>
+      <c r="U372" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1230803157</t>
+        </is>
+      </c>
+      <c r="V372" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="373">
+      <c r="A373" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B373" t="inlineStr">
+        <is>
+          <t>마발라 현대백화점압구정본점</t>
+        </is>
+      </c>
+      <c r="C373" t="inlineStr"/>
+      <c r="D373" t="inlineStr"/>
+      <c r="E373" t="inlineStr">
+        <is>
+          <t>02-3438-6104</t>
+        </is>
+      </c>
+      <c r="F373" t="inlineStr"/>
+      <c r="G373" t="inlineStr">
+        <is>
+          <t>서울특별시 강남구 압구정로 165 현대백화점압구정본점 B2</t>
+        </is>
+      </c>
+      <c r="H373" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I373" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J373" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K373" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L373" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M373" t="inlineStr"/>
+      <c r="N373" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O373" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P373" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q373" t="n">
+        <v>0</v>
+      </c>
+      <c r="R373" t="n">
+        <v>0</v>
+      </c>
+      <c r="S373" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T373" t="inlineStr">
+        <is>
+          <t>20415554</t>
+        </is>
+      </c>
+      <c r="U373" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/20415554</t>
+        </is>
+      </c>
+      <c r="V373" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="374">
+      <c r="A374" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B374" t="inlineStr">
+        <is>
+          <t>뷰티네일 강남역</t>
+        </is>
+      </c>
+      <c r="C374" t="inlineStr"/>
+      <c r="D374" t="inlineStr"/>
+      <c r="E374" t="inlineStr">
+        <is>
+          <t>0507-1403-7879</t>
+        </is>
+      </c>
+      <c r="F374" t="inlineStr"/>
+      <c r="G374" t="inlineStr">
+        <is>
+          <t>서울특별시 강남구 강남대로 438 CGV 5층</t>
+        </is>
+      </c>
+      <c r="H374" t="inlineStr">
+        <is>
+          <t>http://instagram.com/beautynail__official</t>
+        </is>
+      </c>
+      <c r="I374" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J374" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K374" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L374" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M374" t="inlineStr"/>
+      <c r="N374" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O374" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P374" t="n">
+        <v>2113</v>
+      </c>
+      <c r="Q374" t="n">
+        <v>67</v>
+      </c>
+      <c r="R374" t="n">
+        <v>2180</v>
+      </c>
+      <c r="S374" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T374" t="inlineStr">
+        <is>
+          <t>13530661</t>
+        </is>
+      </c>
+      <c r="U374" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/13530661</t>
+        </is>
+      </c>
+      <c r="V374" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="375">
+      <c r="A375" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B375" t="inlineStr">
+        <is>
+          <t>손에 물들다</t>
+        </is>
+      </c>
+      <c r="C375" t="inlineStr"/>
+      <c r="D375" t="inlineStr"/>
+      <c r="E375" t="inlineStr">
+        <is>
+          <t>02-518-0826</t>
+        </is>
+      </c>
+      <c r="F375" t="inlineStr"/>
+      <c r="G375" t="inlineStr">
+        <is>
+          <t>서울특별시 강남구 논현로159길 14 1층 손에물들다</t>
+        </is>
+      </c>
+      <c r="H375" t="inlineStr">
+        <is>
+          <t>http://www.instagram.com/hand_paint</t>
+        </is>
+      </c>
+      <c r="I375" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J375" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K375" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L375" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M375" t="inlineStr"/>
+      <c r="N375" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O375" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P375" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q375" t="n">
+        <v>7</v>
+      </c>
+      <c r="R375" t="n">
+        <v>12</v>
+      </c>
+      <c r="S375" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T375" t="inlineStr">
+        <is>
+          <t>21219990</t>
+        </is>
+      </c>
+      <c r="U375" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/21219990</t>
+        </is>
+      </c>
+      <c r="V375" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="376">
+      <c r="A376" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B376" t="inlineStr">
+        <is>
+          <t>메종드보떼 압구정점</t>
+        </is>
+      </c>
+      <c r="C376" t="inlineStr"/>
+      <c r="D376" t="inlineStr"/>
+      <c r="E376" t="inlineStr">
+        <is>
+          <t>0507-1313-0231</t>
+        </is>
+      </c>
+      <c r="F376" t="inlineStr"/>
+      <c r="G376" t="inlineStr">
+        <is>
+          <t>서울특별시 강남구 언주로172길 25 640아트타워 2층</t>
+        </is>
+      </c>
+      <c r="H376" t="inlineStr">
+        <is>
+          <t>https://youtube.com/@메종드보떼스쿨앤살롱</t>
+        </is>
+      </c>
+      <c r="I376" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J376" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K376" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L376" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M376" t="inlineStr"/>
+      <c r="N376" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O376" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P376" t="n">
+        <v>28</v>
+      </c>
+      <c r="Q376" t="n">
+        <v>78</v>
+      </c>
+      <c r="R376" t="n">
+        <v>106</v>
+      </c>
+      <c r="S376" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T376" t="inlineStr">
+        <is>
+          <t>35608505</t>
+        </is>
+      </c>
+      <c r="U376" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/35608505</t>
+        </is>
+      </c>
+      <c r="V376" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="377">
+      <c r="A377" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B377" t="inlineStr">
+        <is>
+          <t>포쉬네일 하이푸스 가로수길점</t>
+        </is>
+      </c>
+      <c r="C377" t="inlineStr"/>
+      <c r="D377" t="inlineStr"/>
+      <c r="E377" t="inlineStr">
+        <is>
+          <t>0507-1374-6141</t>
+        </is>
+      </c>
+      <c r="F377" t="inlineStr"/>
+      <c r="G377" t="inlineStr">
+        <is>
+          <t>서울특별시 강남구 가로수길 16 3층 포쉬네일 하이푸스 가로수길점</t>
+        </is>
+      </c>
+      <c r="H377" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/hifuss_garosugil</t>
+        </is>
+      </c>
+      <c r="I377" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J377" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K377" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L377" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M377" t="inlineStr"/>
+      <c r="N377" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O377" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P377" t="n">
+        <v>1334</v>
+      </c>
+      <c r="Q377" t="n">
+        <v>550</v>
+      </c>
+      <c r="R377" t="n">
+        <v>1884</v>
+      </c>
+      <c r="S377" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T377" t="inlineStr">
+        <is>
+          <t>20378592</t>
+        </is>
+      </c>
+      <c r="U377" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/20378592</t>
+        </is>
+      </c>
+      <c r="V377" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="378">
+      <c r="A378" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B378" t="inlineStr">
+        <is>
+          <t>예쁜여우</t>
+        </is>
+      </c>
+      <c r="C378" t="inlineStr">
+        <is>
+          <t>lovelyfox7979@naver.com</t>
+        </is>
+      </c>
+      <c r="D378" t="inlineStr"/>
+      <c r="E378" t="inlineStr">
+        <is>
+          <t>02-508-7979</t>
+        </is>
+      </c>
+      <c r="F378" t="inlineStr"/>
+      <c r="G378" t="inlineStr">
+        <is>
+          <t>서울특별시 강남구 선릉로 225 도곡렉슬상가 113호</t>
+        </is>
+      </c>
+      <c r="H378" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/lovelyfox7979</t>
+        </is>
+      </c>
+      <c r="I378" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J378" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K378" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L378" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M378" t="inlineStr"/>
+      <c r="N378" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O378" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P378" t="n">
+        <v>197</v>
+      </c>
+      <c r="Q378" t="n">
+        <v>27</v>
+      </c>
+      <c r="R378" t="n">
+        <v>224</v>
+      </c>
+      <c r="S378" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T378" t="inlineStr">
+        <is>
+          <t>38431957</t>
+        </is>
+      </c>
+      <c r="U378" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/38431957</t>
+        </is>
+      </c>
+      <c r="V378" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="379">
+      <c r="A379" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B379" t="inlineStr">
+        <is>
+          <t>인크리즈 네일</t>
+        </is>
+      </c>
+      <c r="C379" t="inlineStr"/>
+      <c r="D379" t="inlineStr"/>
+      <c r="E379" t="inlineStr">
+        <is>
+          <t>0507-1483-0231</t>
+        </is>
+      </c>
+      <c r="F379" t="inlineStr"/>
+      <c r="G379" t="inlineStr">
+        <is>
+          <t>서울특별시 강남구 영동대로 702 B1</t>
+        </is>
+      </c>
+      <c r="H379" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/increase_nail_/</t>
+        </is>
+      </c>
+      <c r="I379" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J379" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K379" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L379" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M379" t="inlineStr"/>
+      <c r="N379" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O379" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P379" t="n">
+        <v>119</v>
+      </c>
+      <c r="Q379" t="n">
+        <v>16</v>
+      </c>
+      <c r="R379" t="n">
+        <v>135</v>
+      </c>
+      <c r="S379" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T379" t="inlineStr">
+        <is>
+          <t>1218682872</t>
+        </is>
+      </c>
+      <c r="U379" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1218682872</t>
+        </is>
+      </c>
+      <c r="V379" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="380">
+      <c r="A380" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B380" t="inlineStr">
+        <is>
+          <t>윤이프뷰티</t>
+        </is>
+      </c>
+      <c r="C380" t="inlineStr"/>
+      <c r="D380" t="inlineStr"/>
+      <c r="E380" t="inlineStr">
+        <is>
+          <t>0507-1332-7931</t>
+        </is>
+      </c>
+      <c r="F380" t="inlineStr"/>
+      <c r="G380" t="inlineStr">
+        <is>
+          <t>서울특별시 강남구 선릉로 431 sk허브 4층 405호</t>
+        </is>
+      </c>
+      <c r="H380" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/yoonif_nail</t>
+        </is>
+      </c>
+      <c r="I380" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J380" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K380" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L380" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M380" t="inlineStr"/>
+      <c r="N380" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O380" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P380" t="n">
+        <v>225</v>
+      </c>
+      <c r="Q380" t="n">
+        <v>75</v>
+      </c>
+      <c r="R380" t="n">
+        <v>300</v>
+      </c>
+      <c r="S380" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T380" t="inlineStr">
+        <is>
+          <t>1332168960</t>
+        </is>
+      </c>
+      <c r="U380" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1332168960</t>
+        </is>
+      </c>
+      <c r="V380" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="381">
+      <c r="A381" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B381" t="inlineStr">
+        <is>
+          <t>에이치인 네일</t>
+        </is>
+      </c>
+      <c r="C381" t="inlineStr"/>
+      <c r="D381" t="inlineStr"/>
+      <c r="E381" t="inlineStr">
+        <is>
+          <t>0507-1313-4230</t>
+        </is>
+      </c>
+      <c r="F381" t="inlineStr"/>
+      <c r="G381" t="inlineStr">
+        <is>
+          <t>서울특별시 강남구 삼성로103길 22 1층 1-2호</t>
+        </is>
+      </c>
+      <c r="H381" t="inlineStr">
+        <is>
+          <t>http://www.instagram.com/h.in_nail</t>
+        </is>
+      </c>
+      <c r="I381" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J381" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K381" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L381" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M381" t="inlineStr"/>
+      <c r="N381" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O381" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P381" t="n">
+        <v>55</v>
+      </c>
+      <c r="Q381" t="n">
+        <v>6</v>
+      </c>
+      <c r="R381" t="n">
+        <v>61</v>
+      </c>
+      <c r="S381" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T381" t="inlineStr">
+        <is>
+          <t>1132309657</t>
+        </is>
+      </c>
+      <c r="U381" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1132309657</t>
+        </is>
+      </c>
+      <c r="V381" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="382">
+      <c r="A382" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B382" t="inlineStr">
+        <is>
+          <t>얼반네일</t>
+        </is>
+      </c>
+      <c r="C382" t="inlineStr"/>
+      <c r="D382" t="inlineStr"/>
+      <c r="E382" t="inlineStr">
+        <is>
+          <t>0507-1342-9539</t>
+        </is>
+      </c>
+      <c r="F382" t="inlineStr"/>
+      <c r="G382" t="inlineStr">
+        <is>
+          <t>서울특별시 강남구 언주로70길 6</t>
+        </is>
+      </c>
+      <c r="H382" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I382" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J382" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K382" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L382" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M382" t="inlineStr"/>
+      <c r="N382" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O382" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P382" t="n">
+        <v>24</v>
+      </c>
+      <c r="Q382" t="n">
+        <v>67</v>
+      </c>
+      <c r="R382" t="n">
+        <v>91</v>
+      </c>
+      <c r="S382" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T382" t="inlineStr">
+        <is>
+          <t>36615234</t>
+        </is>
+      </c>
+      <c r="U382" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/36615234</t>
+        </is>
+      </c>
+      <c r="V382" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="383">
+      <c r="A383" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B383" t="inlineStr">
+        <is>
+          <t>미스틱네일</t>
+        </is>
+      </c>
+      <c r="C383" t="inlineStr"/>
+      <c r="D383" t="inlineStr"/>
+      <c r="E383" t="inlineStr">
+        <is>
+          <t>0507-1310-8446</t>
+        </is>
+      </c>
+      <c r="F383" t="inlineStr"/>
+      <c r="G383" t="inlineStr">
+        <is>
+          <t>서울특별시 강남구 선릉로162길 3 2층</t>
+        </is>
+      </c>
+      <c r="H383" t="inlineStr">
+        <is>
+          <t>http://www.instagram.com/mystic_nail</t>
+        </is>
+      </c>
+      <c r="I383" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J383" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K383" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L383" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M383" t="inlineStr"/>
+      <c r="N383" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O383" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P383" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q383" t="n">
+        <v>101</v>
+      </c>
+      <c r="R383" t="n">
+        <v>102</v>
+      </c>
+      <c r="S383" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T383" t="inlineStr">
+        <is>
+          <t>1974625750</t>
+        </is>
+      </c>
+      <c r="U383" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1974625750</t>
+        </is>
+      </c>
+      <c r="V383" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="384">
+      <c r="A384" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B384" t="inlineStr">
+        <is>
+          <t>해피네일</t>
+        </is>
+      </c>
+      <c r="C384" t="inlineStr"/>
+      <c r="D384" t="inlineStr"/>
+      <c r="E384" t="inlineStr">
+        <is>
+          <t>0507-1381-0437</t>
+        </is>
+      </c>
+      <c r="F384" t="inlineStr"/>
+      <c r="G384" t="inlineStr">
+        <is>
+          <t>서울특별시 강남구 압구정로29길 72-1 신사상가 1층</t>
+        </is>
+      </c>
+      <c r="H384" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I384" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J384" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K384" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L384" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M384" t="inlineStr"/>
+      <c r="N384" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O384" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P384" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q384" t="n">
+        <v>0</v>
+      </c>
+      <c r="R384" t="n">
+        <v>2</v>
+      </c>
+      <c r="S384" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T384" t="inlineStr">
+        <is>
+          <t>36504683</t>
+        </is>
+      </c>
+      <c r="U384" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/36504683</t>
+        </is>
+      </c>
+      <c r="V384" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="385">
+      <c r="A385" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B385" t="inlineStr">
+        <is>
+          <t>네일수이</t>
+        </is>
+      </c>
+      <c r="C385" t="inlineStr"/>
+      <c r="D385" t="inlineStr"/>
+      <c r="E385" t="inlineStr">
+        <is>
+          <t>0507-1482-1228</t>
+        </is>
+      </c>
+      <c r="F385" t="inlineStr"/>
+      <c r="G385" t="inlineStr">
+        <is>
+          <t>서울특별시 강남구 논현로131길 24 1층 103호</t>
+        </is>
+      </c>
+      <c r="H385" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/nail__sui</t>
+        </is>
+      </c>
+      <c r="I385" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J385" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K385" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L385" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M385" t="inlineStr"/>
+      <c r="N385" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O385" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P385" t="n">
+        <v>13</v>
+      </c>
+      <c r="Q385" t="n">
+        <v>1</v>
+      </c>
+      <c r="R385" t="n">
+        <v>14</v>
+      </c>
+      <c r="S385" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T385" t="inlineStr">
+        <is>
+          <t>1542816629</t>
+        </is>
+      </c>
+      <c r="U385" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1542816629</t>
+        </is>
+      </c>
+      <c r="V385" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="386">
+      <c r="A386" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B386" t="inlineStr">
+        <is>
+          <t>NAILDOCHU</t>
+        </is>
+      </c>
+      <c r="C386" t="inlineStr"/>
+      <c r="D386" t="inlineStr"/>
+      <c r="E386" t="inlineStr">
+        <is>
+          <t>0507-1336-6736</t>
+        </is>
+      </c>
+      <c r="F386" t="inlineStr"/>
+      <c r="G386" t="inlineStr">
+        <is>
+          <t>서울특별시 강남구 도산대로37길 8</t>
+        </is>
+      </c>
+      <c r="H386" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/naildochu</t>
+        </is>
+      </c>
+      <c r="I386" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J386" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K386" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L386" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M386" t="inlineStr"/>
+      <c r="N386" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O386" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P386" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q386" t="n">
+        <v>3</v>
+      </c>
+      <c r="R386" t="n">
+        <v>3</v>
+      </c>
+      <c r="S386" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T386" t="inlineStr">
+        <is>
+          <t>1264853492</t>
+        </is>
+      </c>
+      <c r="U386" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1264853492</t>
+        </is>
+      </c>
+      <c r="V386" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="387">
+      <c r="A387" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B387" t="inlineStr">
+        <is>
+          <t>네일팰리스 우성캐릭터</t>
+        </is>
+      </c>
+      <c r="C387" t="inlineStr"/>
+      <c r="D387" t="inlineStr"/>
+      <c r="E387" t="inlineStr">
+        <is>
+          <t>0507-1332-2144</t>
+        </is>
+      </c>
+      <c r="F387" t="inlineStr"/>
+      <c r="G387" t="inlineStr">
+        <is>
+          <t>서울특별시 강남구 언주로 118 우성캐릭터 199상가 115호</t>
+        </is>
+      </c>
+      <c r="H387" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I387" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J387" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K387" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L387" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M387" t="inlineStr"/>
+      <c r="N387" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O387" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P387" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q387" t="n">
+        <v>0</v>
+      </c>
+      <c r="R387" t="n">
+        <v>2</v>
+      </c>
+      <c r="S387" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T387" t="inlineStr">
+        <is>
+          <t>1203738939</t>
+        </is>
+      </c>
+      <c r="U387" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1203738939</t>
+        </is>
+      </c>
+      <c r="V387" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="388">
+      <c r="A388" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B388" t="inlineStr">
+        <is>
+          <t>네일드루아 신사점</t>
+        </is>
+      </c>
+      <c r="C388" t="inlineStr">
+        <is>
+          <t>nailderoi1@naver.com</t>
+        </is>
+      </c>
+      <c r="D388" t="inlineStr"/>
+      <c r="E388" t="inlineStr">
+        <is>
+          <t>0507-1400-0213</t>
+        </is>
+      </c>
+      <c r="F388" t="inlineStr"/>
+      <c r="G388" t="inlineStr">
+        <is>
+          <t>서울특별시 강남구 도산대로4길 12 장원빌딩 2F 네일드루아</t>
+        </is>
+      </c>
+      <c r="H388" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/nailderoi1</t>
+        </is>
+      </c>
+      <c r="I388" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J388" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K388" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L388" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M388" t="inlineStr"/>
+      <c r="N388" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O388" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P388" t="n">
+        <v>625</v>
+      </c>
+      <c r="Q388" t="n">
+        <v>139</v>
+      </c>
+      <c r="R388" t="n">
+        <v>764</v>
+      </c>
+      <c r="S388" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T388" t="inlineStr">
+        <is>
+          <t>1459077126</t>
+        </is>
+      </c>
+      <c r="U388" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1459077126</t>
+        </is>
+      </c>
+      <c r="V388" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="389">
+      <c r="A389" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B389" t="inlineStr">
+        <is>
+          <t>데싱디바</t>
+        </is>
+      </c>
+      <c r="C389" t="inlineStr">
+        <is>
+          <t>2_eunjee@naver.com</t>
+        </is>
+      </c>
+      <c r="D389" t="inlineStr"/>
+      <c r="E389" t="inlineStr">
+        <is>
+          <t>0507-1386-6564</t>
+        </is>
+      </c>
+      <c r="F389" t="inlineStr"/>
+      <c r="G389" t="inlineStr">
+        <is>
+          <t>서울특별시 강남구 압구정로46길 35 압구정모빌딩 1층</t>
+        </is>
+      </c>
+      <c r="H389" t="inlineStr">
+        <is>
+          <t>http://www.instagram.com/dashingdiva__nail</t>
+        </is>
+      </c>
+      <c r="I389" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J389" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K389" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L389" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M389" t="inlineStr"/>
+      <c r="N389" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O389" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P389" t="n">
+        <v>93</v>
+      </c>
+      <c r="Q389" t="n">
+        <v>254</v>
+      </c>
+      <c r="R389" t="n">
+        <v>347</v>
+      </c>
+      <c r="S389" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T389" t="inlineStr">
+        <is>
+          <t>13447890</t>
+        </is>
+      </c>
+      <c r="U389" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/13447890</t>
+        </is>
+      </c>
+      <c r="V389" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="390">
+      <c r="A390" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B390" t="inlineStr">
+        <is>
+          <t>르로아네일</t>
+        </is>
+      </c>
+      <c r="C390" t="inlineStr">
+        <is>
+          <t>iyc0424@naver.com</t>
+        </is>
+      </c>
+      <c r="D390" t="inlineStr"/>
+      <c r="E390" t="inlineStr">
+        <is>
+          <t>0507-1310-0041</t>
+        </is>
+      </c>
+      <c r="F390" t="inlineStr"/>
+      <c r="G390" t="inlineStr">
+        <is>
+          <t>서울특별시 강남구 논현로63길 16 역삼서해더블루 제2층 210호</t>
+        </is>
+      </c>
+      <c r="H390" t="inlineStr">
+        <is>
+          <t>http://www.instagram.com/leloa_nail</t>
+        </is>
+      </c>
+      <c r="I390" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J390" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K390" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L390" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M390" t="inlineStr"/>
+      <c r="N390" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O390" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P390" t="n">
+        <v>31</v>
+      </c>
+      <c r="Q390" t="n">
+        <v>266</v>
+      </c>
+      <c r="R390" t="n">
+        <v>297</v>
+      </c>
+      <c r="S390" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T390" t="inlineStr">
+        <is>
+          <t>1883126989</t>
+        </is>
+      </c>
+      <c r="U390" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1883126989</t>
+        </is>
+      </c>
+      <c r="V390" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="391">
+      <c r="A391" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B391" t="inlineStr">
+        <is>
+          <t>꼬네일클래식</t>
+        </is>
+      </c>
+      <c r="C391" t="inlineStr">
+        <is>
+          <t>tmdesignk@naver.com</t>
+        </is>
+      </c>
+      <c r="D391" t="inlineStr"/>
+      <c r="E391" t="inlineStr">
+        <is>
+          <t>0507-1346-1039</t>
+        </is>
+      </c>
+      <c r="F391" t="inlineStr"/>
+      <c r="G391" t="inlineStr">
+        <is>
+          <t>서울특별시 강남구 학동로50길 6 5층</t>
+        </is>
+      </c>
+      <c r="H391" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/ggonail</t>
+        </is>
+      </c>
+      <c r="I391" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J391" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K391" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L391" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M391" t="inlineStr"/>
+      <c r="N391" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O391" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P391" t="n">
+        <v>18</v>
+      </c>
+      <c r="Q391" t="n">
+        <v>0</v>
+      </c>
+      <c r="R391" t="n">
+        <v>18</v>
+      </c>
+      <c r="S391" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T391" t="inlineStr">
+        <is>
+          <t>2059792056</t>
+        </is>
+      </c>
+      <c r="U391" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2059792056</t>
+        </is>
+      </c>
+      <c r="V391" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="392">
+      <c r="A392" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B392" t="inlineStr">
+        <is>
+          <t>네일타임</t>
+        </is>
+      </c>
+      <c r="C392" t="inlineStr">
+        <is>
+          <t>yjk2650@naver.com</t>
+        </is>
+      </c>
+      <c r="D392" t="inlineStr"/>
+      <c r="E392" t="inlineStr">
+        <is>
+          <t>0507-1430-6639</t>
+        </is>
+      </c>
+      <c r="F392" t="inlineStr"/>
+      <c r="G392" t="inlineStr">
+        <is>
+          <t>서울특별시 강남구 헌릉로590길 63 강남데시앙크 상가동 204호 네일타임</t>
+        </is>
+      </c>
+      <c r="H392" t="inlineStr">
+        <is>
+          <t>http://pf.kakao.com/_hUnkxj</t>
+        </is>
+      </c>
+      <c r="I392" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J392" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K392" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L392" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M392" t="inlineStr"/>
+      <c r="N392" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O392" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P392" t="n">
+        <v>67</v>
+      </c>
+      <c r="Q392" t="n">
+        <v>2</v>
+      </c>
+      <c r="R392" t="n">
+        <v>69</v>
+      </c>
+      <c r="S392" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T392" t="inlineStr">
+        <is>
+          <t>1181292883</t>
+        </is>
+      </c>
+      <c r="U392" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1181292883</t>
+        </is>
+      </c>
+      <c r="V392" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="393">
+      <c r="A393" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B393" t="inlineStr">
+        <is>
+          <t>찐네일</t>
+        </is>
+      </c>
+      <c r="C393" t="inlineStr">
+        <is>
+          <t>linnii@naver.com</t>
+        </is>
+      </c>
+      <c r="D393" t="inlineStr"/>
+      <c r="E393" t="inlineStr">
+        <is>
+          <t>0507-1377-7674</t>
+        </is>
+      </c>
+      <c r="F393" t="inlineStr"/>
+      <c r="G393" t="inlineStr">
+        <is>
+          <t>서울특별시 강남구 영동대로114길 31 1층 찐네일</t>
+        </is>
+      </c>
+      <c r="H393" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I393" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J393" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K393" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L393" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M393" t="inlineStr"/>
+      <c r="N393" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O393" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P393" t="n">
+        <v>23</v>
+      </c>
+      <c r="Q393" t="n">
+        <v>1</v>
+      </c>
+      <c r="R393" t="n">
+        <v>24</v>
+      </c>
+      <c r="S393" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T393" t="inlineStr">
+        <is>
+          <t>1267446966</t>
+        </is>
+      </c>
+      <c r="U393" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1267446966</t>
+        </is>
+      </c>
+      <c r="V393" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="394">
+      <c r="A394" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B394" t="inlineStr">
+        <is>
+          <t>손네일 2호점</t>
+        </is>
+      </c>
+      <c r="C394" t="inlineStr">
+        <is>
+          <t>daon77@naver.com</t>
+        </is>
+      </c>
+      <c r="D394" t="inlineStr"/>
+      <c r="E394" t="inlineStr">
+        <is>
+          <t>0507-1432-5359</t>
+        </is>
+      </c>
+      <c r="F394" t="inlineStr"/>
+      <c r="G394" t="inlineStr">
+        <is>
+          <t>서울특별시 강남구 역삼로64길 13 1층 손네일</t>
+        </is>
+      </c>
+      <c r="H394" t="inlineStr">
+        <is>
+          <t>http://www.instagram.com/yeongji_kk</t>
+        </is>
+      </c>
+      <c r="I394" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J394" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K394" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L394" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M394" t="inlineStr"/>
+      <c r="N394" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O394" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P394" t="n">
+        <v>29</v>
+      </c>
+      <c r="Q394" t="n">
+        <v>46</v>
+      </c>
+      <c r="R394" t="n">
+        <v>75</v>
+      </c>
+      <c r="S394" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T394" t="inlineStr">
+        <is>
+          <t>20264549</t>
+        </is>
+      </c>
+      <c r="U394" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/20264549</t>
+        </is>
+      </c>
+      <c r="V394" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="395">
+      <c r="A395" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B395" t="inlineStr">
+        <is>
+          <t>Nail on</t>
+        </is>
+      </c>
+      <c r="C395" t="inlineStr"/>
+      <c r="D395" t="inlineStr"/>
+      <c r="E395" t="inlineStr">
+        <is>
+          <t>0507-1312-2537</t>
+        </is>
+      </c>
+      <c r="F395" t="inlineStr"/>
+      <c r="G395" t="inlineStr">
+        <is>
+          <t>서울특별시 강남구 삼성로 212 A블럭 지상1층 104호</t>
+        </is>
+      </c>
+      <c r="H395" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/nail_.on</t>
+        </is>
+      </c>
+      <c r="I395" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J395" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K395" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L395" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M395" t="inlineStr"/>
+      <c r="N395" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O395" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P395" t="n">
+        <v>14</v>
+      </c>
+      <c r="Q395" t="n">
+        <v>1</v>
+      </c>
+      <c r="R395" t="n">
+        <v>15</v>
+      </c>
+      <c r="S395" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T395" t="inlineStr">
+        <is>
+          <t>2004026770</t>
+        </is>
+      </c>
+      <c r="U395" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2004026770</t>
+        </is>
+      </c>
+      <c r="V395" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="396">
+      <c r="A396" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B396" t="inlineStr">
+        <is>
+          <t>아이러브네일</t>
+        </is>
+      </c>
+      <c r="C396" t="inlineStr">
+        <is>
+          <t>saddysad@naver.com</t>
+        </is>
+      </c>
+      <c r="D396" t="inlineStr"/>
+      <c r="E396" t="inlineStr">
+        <is>
+          <t>02-539-2680</t>
+        </is>
+      </c>
+      <c r="F396" t="inlineStr"/>
+      <c r="G396" t="inlineStr">
+        <is>
+          <t>서울특별시 강남구 도곡로63길 12 신농프라자 107호</t>
+        </is>
+      </c>
+      <c r="H396" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I396" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J396" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K396" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L396" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M396" t="inlineStr"/>
+      <c r="N396" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O396" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P396" t="n">
+        <v>23</v>
+      </c>
+      <c r="Q396" t="n">
+        <v>46</v>
+      </c>
+      <c r="R396" t="n">
+        <v>69</v>
+      </c>
+      <c r="S396" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T396" t="inlineStr">
+        <is>
+          <t>12776753</t>
+        </is>
+      </c>
+      <c r="U396" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/12776753</t>
+        </is>
+      </c>
+      <c r="V396" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="397">
+      <c r="A397" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B397" t="inlineStr">
+        <is>
+          <t>네일테라피</t>
+        </is>
+      </c>
+      <c r="C397" t="inlineStr"/>
+      <c r="D397" t="inlineStr"/>
+      <c r="E397" t="inlineStr"/>
+      <c r="F397" t="inlineStr"/>
+      <c r="G397" t="inlineStr">
+        <is>
+          <t>서울특별시 강남구 도산대로101길 29 상가동 3호</t>
+        </is>
+      </c>
+      <c r="H397" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I397" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J397" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K397" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L397" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M397" t="inlineStr"/>
+      <c r="N397" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O397" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P397" t="n">
+        <v>25</v>
+      </c>
+      <c r="Q397" t="n">
+        <v>1</v>
+      </c>
+      <c r="R397" t="n">
+        <v>26</v>
+      </c>
+      <c r="S397" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T397" t="inlineStr">
+        <is>
+          <t>1618518655</t>
+        </is>
+      </c>
+      <c r="U397" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1618518655</t>
+        </is>
+      </c>
+      <c r="V397" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="398">
+      <c r="A398" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B398" t="inlineStr">
+        <is>
+          <t>예쁜손짓</t>
+        </is>
+      </c>
+      <c r="C398" t="inlineStr">
+        <is>
+          <t>ksb0229@naver.com</t>
+        </is>
+      </c>
+      <c r="D398" t="inlineStr"/>
+      <c r="E398" t="inlineStr">
+        <is>
+          <t>070-7721-7522</t>
+        </is>
+      </c>
+      <c r="F398" t="inlineStr"/>
+      <c r="G398" t="inlineStr">
+        <is>
+          <t>서울특별시 강남구 삼성로147길 8</t>
+        </is>
+      </c>
+      <c r="H398" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I398" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J398" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K398" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L398" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M398" t="inlineStr"/>
+      <c r="N398" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O398" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P398" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q398" t="n">
+        <v>0</v>
+      </c>
+      <c r="R398" t="n">
+        <v>0</v>
+      </c>
+      <c r="S398" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T398" t="inlineStr">
+        <is>
+          <t>762613175</t>
+        </is>
+      </c>
+      <c r="U398" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/762613175</t>
+        </is>
+      </c>
+      <c r="V398" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="399">
+      <c r="A399" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B399" t="inlineStr">
+        <is>
+          <t>다빈치 네일</t>
+        </is>
+      </c>
+      <c r="C399" t="inlineStr"/>
+      <c r="D399" t="inlineStr"/>
+      <c r="E399" t="inlineStr">
+        <is>
+          <t>0507-1468-8789</t>
+        </is>
+      </c>
+      <c r="F399" t="inlineStr"/>
+      <c r="G399" t="inlineStr">
+        <is>
+          <t>서울특별시 강남구 남부순환로 2927 클래시아상가 128호</t>
+        </is>
+      </c>
+      <c r="H399" t="inlineStr">
+        <is>
+          <t>http://www.instagram.com/davincinail</t>
+        </is>
+      </c>
+      <c r="I399" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J399" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K399" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L399" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M399" t="inlineStr"/>
+      <c r="N399" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O399" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P399" t="n">
+        <v>281</v>
+      </c>
+      <c r="Q399" t="n">
+        <v>66</v>
+      </c>
+      <c r="R399" t="n">
+        <v>347</v>
+      </c>
+      <c r="S399" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T399" t="inlineStr">
+        <is>
+          <t>1324102891</t>
+        </is>
+      </c>
+      <c r="U399" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1324102891</t>
+        </is>
+      </c>
+      <c r="V399" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="400">
+      <c r="A400" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B400" t="inlineStr">
+        <is>
+          <t>솔이네일</t>
+        </is>
+      </c>
+      <c r="C400" t="inlineStr"/>
+      <c r="D400" t="inlineStr"/>
+      <c r="E400" t="inlineStr"/>
+      <c r="F400" t="inlineStr"/>
+      <c r="G400" t="inlineStr">
+        <is>
+          <t>서울특별시 강남구 개포로 615 석탑프라자 지하1층 114호</t>
+        </is>
+      </c>
+      <c r="H400" t="inlineStr">
+        <is>
+          <t>http://instagram.com/sol2nail</t>
+        </is>
+      </c>
+      <c r="I400" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J400" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K400" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L400" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M400" t="inlineStr"/>
+      <c r="N400" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O400" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P400" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q400" t="n">
+        <v>4</v>
+      </c>
+      <c r="R400" t="n">
+        <v>14</v>
+      </c>
+      <c r="S400" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T400" t="inlineStr">
+        <is>
+          <t>1197518050</t>
+        </is>
+      </c>
+      <c r="U400" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1197518050</t>
+        </is>
+      </c>
+      <c r="V400" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="401">
+      <c r="A401" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B401" t="inlineStr">
+        <is>
+          <t>제이네일</t>
+        </is>
+      </c>
+      <c r="C401" t="inlineStr"/>
+      <c r="D401" t="inlineStr"/>
+      <c r="E401" t="inlineStr">
+        <is>
+          <t>02-548-1122</t>
+        </is>
+      </c>
+      <c r="F401" t="inlineStr"/>
+      <c r="G401" t="inlineStr">
+        <is>
+          <t>서울특별시 강남구 봉은사로73길 31 1층</t>
+        </is>
+      </c>
+      <c r="H401" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I401" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J401" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K401" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L401" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M401" t="inlineStr"/>
+      <c r="N401" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O401" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P401" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q401" t="n">
+        <v>2</v>
+      </c>
+      <c r="R401" t="n">
+        <v>7</v>
+      </c>
+      <c r="S401" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T401" t="inlineStr">
+        <is>
+          <t>36874439</t>
+        </is>
+      </c>
+      <c r="U401" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/36874439</t>
+        </is>
+      </c>
+      <c r="V401" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="402">
+      <c r="A402" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B402" t="inlineStr">
+        <is>
+          <t>드롭네일</t>
+        </is>
+      </c>
+      <c r="C402" t="inlineStr"/>
+      <c r="D402" t="inlineStr"/>
+      <c r="E402" t="inlineStr"/>
+      <c r="F402" t="inlineStr"/>
+      <c r="G402" t="inlineStr">
+        <is>
+          <t>서울특별시 강남구 언주로135길 32-13 102호 드롭네일</t>
+        </is>
+      </c>
+      <c r="H402" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/dropnail._</t>
+        </is>
+      </c>
+      <c r="I402" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J402" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K402" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L402" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M402" t="inlineStr"/>
+      <c r="N402" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O402" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P402" t="n">
+        <v>98</v>
+      </c>
+      <c r="Q402" t="n">
+        <v>16</v>
+      </c>
+      <c r="R402" t="n">
+        <v>114</v>
+      </c>
+      <c r="S402" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T402" t="inlineStr">
+        <is>
+          <t>1192786332</t>
+        </is>
+      </c>
+      <c r="U402" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1192786332</t>
+        </is>
+      </c>
+      <c r="V402" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="403">
+      <c r="A403" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B403" t="inlineStr">
+        <is>
+          <t>파리클라라 2호점</t>
+        </is>
+      </c>
+      <c r="C403" t="inlineStr">
+        <is>
+          <t>sehyuny01@naver.com</t>
+        </is>
+      </c>
+      <c r="D403" t="inlineStr"/>
+      <c r="E403" t="inlineStr">
+        <is>
+          <t>0507-1382-4101</t>
+        </is>
+      </c>
+      <c r="F403" t="inlineStr"/>
+      <c r="G403" t="inlineStr">
+        <is>
+          <t>서울특별시 강남구 개포로 623 대청타워 120호 파리클라라 네일샵</t>
+        </is>
+      </c>
+      <c r="H403" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/sehyuny01</t>
+        </is>
+      </c>
+      <c r="I403" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J403" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K403" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L403" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M403" t="inlineStr"/>
+      <c r="N403" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O403" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P403" t="n">
+        <v>284</v>
+      </c>
+      <c r="Q403" t="n">
+        <v>218</v>
+      </c>
+      <c r="R403" t="n">
+        <v>502</v>
+      </c>
+      <c r="S403" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T403" t="inlineStr">
+        <is>
+          <t>32708489</t>
+        </is>
+      </c>
+      <c r="U403" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/32708489</t>
+        </is>
+      </c>
+      <c r="V403" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="404">
+      <c r="A404" t="inlineStr">
+        <is>
+          <t>속눈썹증모,연장</t>
+        </is>
+      </c>
+      <c r="B404" t="inlineStr">
+        <is>
+          <t>아이즈 속눈썹연장,네일아트,왁싱</t>
+        </is>
+      </c>
+      <c r="C404" t="inlineStr">
+        <is>
+          <t>model18hy@naver.com</t>
+        </is>
+      </c>
+      <c r="D404" t="inlineStr"/>
+      <c r="E404" t="inlineStr">
+        <is>
+          <t>0507-1323-1774</t>
+        </is>
+      </c>
+      <c r="F404" t="inlineStr"/>
+      <c r="G404" t="inlineStr">
+        <is>
+          <t>서울특별시 강남구 강남대로124길 48 아이즈네일&amp;속눈썹연장</t>
+        </is>
+      </c>
+      <c r="H404" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I404" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J404" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K404" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L404" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M404" t="inlineStr"/>
+      <c r="N404" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O404" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P404" t="n">
+        <v>144</v>
+      </c>
+      <c r="Q404" t="n">
+        <v>79</v>
+      </c>
+      <c r="R404" t="n">
+        <v>223</v>
+      </c>
+      <c r="S404" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T404" t="inlineStr">
+        <is>
+          <t>13572479</t>
+        </is>
+      </c>
+      <c r="U404" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/13572479</t>
+        </is>
+      </c>
+      <c r="V404" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="405">
+      <c r="A405" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B405" t="inlineStr">
+        <is>
+          <t>네일언니</t>
+        </is>
+      </c>
+      <c r="C405" t="inlineStr"/>
+      <c r="D405" t="inlineStr"/>
+      <c r="E405" t="inlineStr">
+        <is>
+          <t>0507-1431-0362</t>
+        </is>
+      </c>
+      <c r="F405" t="inlineStr"/>
+      <c r="G405" t="inlineStr">
+        <is>
+          <t>서울특별시 강남구 언주로103길 51 1층</t>
+        </is>
+      </c>
+      <c r="H405" t="inlineStr">
+        <is>
+          <t>http://pf.kakao.com/_xednuG</t>
+        </is>
+      </c>
+      <c r="I405" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J405" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K405" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L405" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M405" t="inlineStr"/>
+      <c r="N405" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O405" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P405" t="n">
+        <v>82</v>
+      </c>
+      <c r="Q405" t="n">
+        <v>34</v>
+      </c>
+      <c r="R405" t="n">
+        <v>116</v>
+      </c>
+      <c r="S405" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T405" t="inlineStr">
+        <is>
+          <t>1864134999</t>
+        </is>
+      </c>
+      <c r="U405" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1864134999</t>
+        </is>
+      </c>
+      <c r="V405" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="406">
+      <c r="A406" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B406" t="inlineStr">
+        <is>
+          <t>여우손톱</t>
+        </is>
+      </c>
+      <c r="C406" t="inlineStr"/>
+      <c r="D406" t="inlineStr"/>
+      <c r="E406" t="inlineStr">
+        <is>
+          <t>0507-1303-1892</t>
+        </is>
+      </c>
+      <c r="F406" t="inlineStr"/>
+      <c r="G406" t="inlineStr">
+        <is>
+          <t>서울특별시 강남구 개포로 227</t>
+        </is>
+      </c>
+      <c r="H406" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I406" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J406" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K406" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L406" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M406" t="inlineStr"/>
+      <c r="N406" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O406" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P406" t="n">
+        <v>13</v>
+      </c>
+      <c r="Q406" t="n">
+        <v>0</v>
+      </c>
+      <c r="R406" t="n">
+        <v>13</v>
+      </c>
+      <c r="S406" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T406" t="inlineStr">
+        <is>
+          <t>1103910791</t>
+        </is>
+      </c>
+      <c r="U406" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1103910791</t>
+        </is>
+      </c>
+      <c r="V406" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="407">
+      <c r="A407" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B407" t="inlineStr">
+        <is>
+          <t>에그네일</t>
+        </is>
+      </c>
+      <c r="C407" t="inlineStr"/>
+      <c r="D407" t="inlineStr"/>
+      <c r="E407" t="inlineStr">
+        <is>
+          <t>0507-1458-7044</t>
+        </is>
+      </c>
+      <c r="F407" t="inlineStr"/>
+      <c r="G407" t="inlineStr">
+        <is>
+          <t>서울특별시 강남구 언주로93길 24 4층</t>
+        </is>
+      </c>
+      <c r="H407" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/eggnail__</t>
+        </is>
+      </c>
+      <c r="I407" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J407" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K407" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L407" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M407" t="inlineStr"/>
+      <c r="N407" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O407" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P407" t="n">
+        <v>63</v>
+      </c>
+      <c r="Q407" t="n">
+        <v>2</v>
+      </c>
+      <c r="R407" t="n">
+        <v>65</v>
+      </c>
+      <c r="S407" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T407" t="inlineStr">
+        <is>
+          <t>2097255070</t>
+        </is>
+      </c>
+      <c r="U407" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2097255070</t>
+        </is>
+      </c>
+      <c r="V407" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="408">
+      <c r="A408" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B408" t="inlineStr">
+        <is>
+          <t>오늘네일</t>
+        </is>
+      </c>
+      <c r="C408" t="inlineStr">
+        <is>
+          <t>todaynnail@naver.com</t>
+        </is>
+      </c>
+      <c r="D408" t="inlineStr"/>
+      <c r="E408" t="inlineStr"/>
+      <c r="F408" t="inlineStr"/>
+      <c r="G408" t="inlineStr">
+        <is>
+          <t>서울특별시 강남구 개포로82길 13-11 2층 204호 오늘네일</t>
+        </is>
+      </c>
+      <c r="H408" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/todaynnail</t>
+        </is>
+      </c>
+      <c r="I408" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J408" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K408" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L408" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M408" t="inlineStr"/>
+      <c r="N408" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O408" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P408" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q408" t="n">
+        <v>28</v>
+      </c>
+      <c r="R408" t="n">
+        <v>31</v>
+      </c>
+      <c r="S408" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T408" t="inlineStr">
+        <is>
+          <t>1213126581</t>
+        </is>
+      </c>
+      <c r="U408" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1213126581</t>
+        </is>
+      </c>
+      <c r="V408" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="409">
+      <c r="A409" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B409" t="inlineStr">
+        <is>
+          <t>네일935</t>
+        </is>
+      </c>
+      <c r="C409" t="inlineStr"/>
+      <c r="D409" t="inlineStr"/>
+      <c r="E409" t="inlineStr">
+        <is>
+          <t>02-553-9935</t>
+        </is>
+      </c>
+      <c r="F409" t="inlineStr"/>
+      <c r="G409" t="inlineStr">
+        <is>
+          <t>서울특별시 강남구 선릉로62길 29 1층 네일935</t>
+        </is>
+      </c>
+      <c r="H409" t="inlineStr">
+        <is>
+          <t>http://instagram.com/nail935_</t>
+        </is>
+      </c>
+      <c r="I409" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J409" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K409" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L409" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M409" t="inlineStr"/>
+      <c r="N409" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O409" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P409" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q409" t="n">
+        <v>0</v>
+      </c>
+      <c r="R409" t="n">
+        <v>2</v>
+      </c>
+      <c r="S409" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T409" t="inlineStr">
+        <is>
+          <t>1364625495</t>
+        </is>
+      </c>
+      <c r="U409" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1364625495</t>
+        </is>
+      </c>
+      <c r="V409" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="410">
+      <c r="A410" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B410" t="inlineStr">
+        <is>
+          <t>레이네일 앤 풋스파</t>
+        </is>
+      </c>
+      <c r="C410" t="inlineStr">
+        <is>
+          <t>yoo06007@naver.com</t>
+        </is>
+      </c>
+      <c r="D410" t="inlineStr"/>
+      <c r="E410" t="inlineStr">
+        <is>
+          <t>0507-1379-0569</t>
+        </is>
+      </c>
+      <c r="F410" t="inlineStr"/>
+      <c r="G410" t="inlineStr">
+        <is>
+          <t>서울특별시 강남구 삼성로 11 디에이치아너힐즈 상가 B108</t>
+        </is>
+      </c>
+      <c r="H410" t="inlineStr">
+        <is>
+          <t>http://instagram.com/leynail_</t>
+        </is>
+      </c>
+      <c r="I410" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J410" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K410" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L410" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M410" t="inlineStr"/>
+      <c r="N410" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O410" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P410" t="n">
+        <v>67</v>
+      </c>
+      <c r="Q410" t="n">
+        <v>123</v>
+      </c>
+      <c r="R410" t="n">
+        <v>190</v>
+      </c>
+      <c r="S410" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T410" t="inlineStr">
+        <is>
+          <t>972598699</t>
+        </is>
+      </c>
+      <c r="U410" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/972598699</t>
+        </is>
+      </c>
+      <c r="V410" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="411">
+      <c r="A411" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B411" t="inlineStr">
+        <is>
+          <t>네일이오나봄</t>
+        </is>
+      </c>
+      <c r="C411" t="inlineStr">
+        <is>
+          <t>nailionabom@naver.com</t>
+        </is>
+      </c>
+      <c r="D411" t="inlineStr"/>
+      <c r="E411" t="inlineStr">
+        <is>
+          <t>0507-1378-0319</t>
+        </is>
+      </c>
+      <c r="F411" t="inlineStr"/>
+      <c r="G411" t="inlineStr">
+        <is>
+          <t>서울특별시 강남구 개포로28길 19 1층</t>
+        </is>
+      </c>
+      <c r="H411" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/nailionabom</t>
+        </is>
+      </c>
+      <c r="I411" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J411" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K411" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L411" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M411" t="inlineStr"/>
+      <c r="N411" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O411" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P411" t="n">
+        <v>128</v>
+      </c>
+      <c r="Q411" t="n">
+        <v>12</v>
+      </c>
+      <c r="R411" t="n">
+        <v>140</v>
+      </c>
+      <c r="S411" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T411" t="inlineStr">
+        <is>
+          <t>2007884790</t>
+        </is>
+      </c>
+      <c r="U411" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2007884790</t>
+        </is>
+      </c>
+      <c r="V411" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="412">
+      <c r="A412" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B412" t="inlineStr">
+        <is>
+          <t>에이윤뷰티 네일아트</t>
+        </is>
+      </c>
+      <c r="C412" t="inlineStr">
+        <is>
+          <t>myidok@naver.com</t>
+        </is>
+      </c>
+      <c r="D412" t="inlineStr"/>
+      <c r="E412" t="inlineStr">
+        <is>
+          <t>0507-1391-2294</t>
+        </is>
+      </c>
+      <c r="F412" t="inlineStr"/>
+      <c r="G412" t="inlineStr">
+        <is>
+          <t>서울특별시 강남구 선릉로132길 13 2층 에이윤뷰티</t>
+        </is>
+      </c>
+      <c r="H412" t="inlineStr">
+        <is>
+          <t>https://pf.kakao.com/_WNkmK</t>
+        </is>
+      </c>
+      <c r="I412" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J412" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K412" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L412" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M412" t="inlineStr"/>
+      <c r="N412" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O412" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P412" t="n">
+        <v>451</v>
+      </c>
+      <c r="Q412" t="n">
+        <v>94</v>
+      </c>
+      <c r="R412" t="n">
+        <v>545</v>
+      </c>
+      <c r="S412" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T412" t="inlineStr">
+        <is>
+          <t>1981361793</t>
+        </is>
+      </c>
+      <c r="U412" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1981361793</t>
+        </is>
+      </c>
+      <c r="V412" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="413">
+      <c r="A413" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B413" t="inlineStr">
+        <is>
+          <t>24시아이유네일</t>
+        </is>
+      </c>
+      <c r="C413" t="inlineStr">
+        <is>
+          <t>did1267@naver.com</t>
+        </is>
+      </c>
+      <c r="D413" t="inlineStr"/>
+      <c r="E413" t="inlineStr">
+        <is>
+          <t>0507-1331-4773</t>
+        </is>
+      </c>
+      <c r="F413" t="inlineStr"/>
+      <c r="G413" t="inlineStr">
+        <is>
+          <t>서울특별시 강남구 논현로106길 31 1층 아이유네일</t>
+        </is>
+      </c>
+      <c r="H413" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/did1267</t>
+        </is>
+      </c>
+      <c r="I413" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J413" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K413" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L413" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M413" t="inlineStr"/>
+      <c r="N413" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O413" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P413" t="n">
+        <v>17</v>
+      </c>
+      <c r="Q413" t="n">
+        <v>30</v>
+      </c>
+      <c r="R413" t="n">
+        <v>47</v>
+      </c>
+      <c r="S413" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T413" t="inlineStr">
+        <is>
+          <t>1610439251</t>
+        </is>
+      </c>
+      <c r="U413" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1610439251</t>
+        </is>
+      </c>
+      <c r="V413" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="414">
+      <c r="A414" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B414" t="inlineStr">
+        <is>
+          <t>우유네일</t>
+        </is>
+      </c>
+      <c r="C414" t="inlineStr">
+        <is>
+          <t>romeosgirl@naver.com</t>
+        </is>
+      </c>
+      <c r="D414" t="inlineStr"/>
+      <c r="E414" t="inlineStr">
+        <is>
+          <t>0507-1413-9048</t>
+        </is>
+      </c>
+      <c r="F414" t="inlineStr"/>
+      <c r="G414" t="inlineStr">
+        <is>
+          <t>서울특별시 강남구 봉은사로33길 14 2층 201호</t>
+        </is>
+      </c>
+      <c r="H414" t="inlineStr">
+        <is>
+          <t>https://https//toss.place/_lb/ggPe1v1lu</t>
+        </is>
+      </c>
+      <c r="I414" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J414" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K414" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L414" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M414" t="inlineStr"/>
+      <c r="N414" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O414" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P414" t="n">
+        <v>124</v>
+      </c>
+      <c r="Q414" t="n">
+        <v>0</v>
+      </c>
+      <c r="R414" t="n">
+        <v>124</v>
+      </c>
+      <c r="S414" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T414" t="inlineStr">
+        <is>
+          <t>1545970705</t>
+        </is>
+      </c>
+      <c r="U414" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1545970705</t>
+        </is>
+      </c>
+      <c r="V414" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="415">
+      <c r="A415" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B415" t="inlineStr">
+        <is>
+          <t>윈썸네일</t>
+        </is>
+      </c>
+      <c r="C415" t="inlineStr"/>
+      <c r="D415" t="inlineStr"/>
+      <c r="E415" t="inlineStr">
+        <is>
+          <t>0507-1494-1281</t>
+        </is>
+      </c>
+      <c r="F415" t="inlineStr"/>
+      <c r="G415" t="inlineStr">
+        <is>
+          <t>서울특별시 강남구 학동로20길 25-9 이래하우스 101호 윈썸네일</t>
+        </is>
+      </c>
+      <c r="H415" t="inlineStr">
+        <is>
+          <t>http://instagram.com/_winsomenail_</t>
+        </is>
+      </c>
+      <c r="I415" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J415" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K415" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L415" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M415" t="inlineStr"/>
+      <c r="N415" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O415" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P415" t="n">
+        <v>146</v>
+      </c>
+      <c r="Q415" t="n">
+        <v>6</v>
+      </c>
+      <c r="R415" t="n">
+        <v>152</v>
+      </c>
+      <c r="S415" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T415" t="inlineStr">
+        <is>
+          <t>1143692316</t>
+        </is>
+      </c>
+      <c r="U415" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1143692316</t>
+        </is>
+      </c>
+      <c r="V415" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="416">
+      <c r="A416" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B416" t="inlineStr">
+        <is>
+          <t>루엘네일</t>
+        </is>
+      </c>
+      <c r="C416" t="inlineStr">
+        <is>
+          <t>chaparkeee@naver.com</t>
+        </is>
+      </c>
+      <c r="D416" t="inlineStr"/>
+      <c r="E416" t="inlineStr">
+        <is>
+          <t>0507-1400-3063</t>
+        </is>
+      </c>
+      <c r="F416" t="inlineStr"/>
+      <c r="G416" t="inlineStr">
+        <is>
+          <t>서울특별시 강남구 강남대로118길 33 5층 루엘네일</t>
+        </is>
+      </c>
+      <c r="H416" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/lu_el_nail?igsh=Njhla3BtcDE4MTNl</t>
+        </is>
+      </c>
+      <c r="I416" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J416" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K416" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L416" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M416" t="inlineStr"/>
+      <c r="N416" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O416" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P416" t="n">
+        <v>80</v>
+      </c>
+      <c r="Q416" t="n">
+        <v>6</v>
+      </c>
+      <c r="R416" t="n">
+        <v>86</v>
+      </c>
+      <c r="S416" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T416" t="inlineStr">
+        <is>
+          <t>2036765480</t>
+        </is>
+      </c>
+      <c r="U416" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2036765480</t>
+        </is>
+      </c>
+      <c r="V416" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="417">
+      <c r="A417" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B417" t="inlineStr">
+        <is>
+          <t>뷰티블룸</t>
+        </is>
+      </c>
+      <c r="C417" t="inlineStr">
+        <is>
+          <t>ksi6439@naver.com</t>
+        </is>
+      </c>
+      <c r="D417" t="inlineStr"/>
+      <c r="E417" t="inlineStr">
+        <is>
+          <t>070-4115-0656</t>
+        </is>
+      </c>
+      <c r="F417" t="inlineStr"/>
+      <c r="G417" t="inlineStr">
+        <is>
+          <t>서울특별시 강남구 학동로 342 sk허브 지하1층 117호</t>
+        </is>
+      </c>
+      <c r="H417" t="inlineStr">
+        <is>
+          <t>http://instagram.com/b.bloom_nail</t>
+        </is>
+      </c>
+      <c r="I417" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J417" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K417" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L417" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M417" t="inlineStr"/>
+      <c r="N417" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O417" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P417" t="n">
+        <v>11</v>
+      </c>
+      <c r="Q417" t="n">
+        <v>7</v>
+      </c>
+      <c r="R417" t="n">
+        <v>18</v>
+      </c>
+      <c r="S417" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T417" t="inlineStr">
+        <is>
+          <t>746435071</t>
+        </is>
+      </c>
+      <c r="U417" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/746435071</t>
+        </is>
+      </c>
+      <c r="V417" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="418">
+      <c r="A418" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B418" t="inlineStr">
+        <is>
+          <t>배배네일살롱</t>
+        </is>
+      </c>
+      <c r="C418" t="inlineStr"/>
+      <c r="D418" t="inlineStr"/>
+      <c r="E418" t="inlineStr">
+        <is>
+          <t>0507-1466-3870</t>
+        </is>
+      </c>
+      <c r="F418" t="inlineStr"/>
+      <c r="G418" t="inlineStr">
+        <is>
+          <t>서울특별시 강남구 논현로28길 50 4층 401호</t>
+        </is>
+      </c>
+      <c r="H418" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/yurabaebae/</t>
+        </is>
+      </c>
+      <c r="I418" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J418" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K418" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L418" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M418" t="inlineStr"/>
+      <c r="N418" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O418" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P418" t="n">
+        <v>409</v>
+      </c>
+      <c r="Q418" t="n">
+        <v>8</v>
+      </c>
+      <c r="R418" t="n">
+        <v>417</v>
+      </c>
+      <c r="S418" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T418" t="inlineStr">
+        <is>
+          <t>1754111037</t>
+        </is>
+      </c>
+      <c r="U418" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1754111037</t>
+        </is>
+      </c>
+      <c r="V418" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="419">
+      <c r="A419" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B419" t="inlineStr">
+        <is>
+          <t>달비솜뷰티</t>
+        </is>
+      </c>
+      <c r="C419" t="inlineStr">
+        <is>
+          <t>honz1@naver.com</t>
+        </is>
+      </c>
+      <c r="D419" t="inlineStr"/>
+      <c r="E419" t="inlineStr"/>
+      <c r="F419" t="inlineStr"/>
+      <c r="G419" t="inlineStr">
+        <is>
+          <t>서울특별시 강남구 학동로43길 26</t>
+        </is>
+      </c>
+      <c r="H419" t="inlineStr">
+        <is>
+          <t>http://pf.kakao.com/_exoxdws</t>
+        </is>
+      </c>
+      <c r="I419" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J419" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K419" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L419" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M419" t="inlineStr"/>
+      <c r="N419" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O419" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P419" t="n">
+        <v>76</v>
+      </c>
+      <c r="Q419" t="n">
+        <v>124</v>
+      </c>
+      <c r="R419" t="n">
+        <v>200</v>
+      </c>
+      <c r="S419" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T419" t="inlineStr">
+        <is>
+          <t>1696732507</t>
+        </is>
+      </c>
+      <c r="U419" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1696732507</t>
+        </is>
+      </c>
+      <c r="V419" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="420">
+      <c r="A420" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B420" t="inlineStr">
+        <is>
+          <t>컨셉트네일</t>
+        </is>
+      </c>
+      <c r="C420" t="inlineStr">
+        <is>
+          <t>som_somee@naver.com</t>
+        </is>
+      </c>
+      <c r="D420" t="inlineStr"/>
+      <c r="E420" t="inlineStr">
+        <is>
+          <t>0507-1353-0720</t>
+        </is>
+      </c>
+      <c r="F420" t="inlineStr"/>
+      <c r="G420" t="inlineStr">
+        <is>
+          <t>서울특별시 강남구 가로수길 35 소호빌딩, 4층 컨셉트</t>
+        </is>
+      </c>
+      <c r="H420" t="inlineStr">
+        <is>
+          <t>http://instagram.com/concept_j.sol</t>
+        </is>
+      </c>
+      <c r="I420" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J420" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K420" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L420" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M420" t="inlineStr"/>
+      <c r="N420" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O420" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P420" t="n">
+        <v>430</v>
+      </c>
+      <c r="Q420" t="n">
+        <v>507</v>
+      </c>
+      <c r="R420" t="n">
+        <v>937</v>
+      </c>
+      <c r="S420" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T420" t="inlineStr">
+        <is>
+          <t>1447169266</t>
+        </is>
+      </c>
+      <c r="U420" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1447169266</t>
+        </is>
+      </c>
+      <c r="V420" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="421">
+      <c r="A421" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B421" t="inlineStr">
+        <is>
+          <t>솜씨네일</t>
+        </is>
+      </c>
+      <c r="C421" t="inlineStr">
+        <is>
+          <t>lulungok@naver.com</t>
+        </is>
+      </c>
+      <c r="D421" t="inlineStr"/>
+      <c r="E421" t="inlineStr">
+        <is>
+          <t>070-8118-6249</t>
+        </is>
+      </c>
+      <c r="F421" t="inlineStr"/>
+      <c r="G421" t="inlineStr">
+        <is>
+          <t>서울특별시 강남구 선릉로86길 31 301호 솜씨네일</t>
+        </is>
+      </c>
+      <c r="H421" t="inlineStr">
+        <is>
+          <t>http://instagram.com/somssi_nail</t>
+        </is>
+      </c>
+      <c r="I421" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J421" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K421" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L421" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M421" t="inlineStr"/>
+      <c r="N421" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O421" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P421" t="n">
+        <v>195</v>
+      </c>
+      <c r="Q421" t="n">
+        <v>3</v>
+      </c>
+      <c r="R421" t="n">
+        <v>198</v>
+      </c>
+      <c r="S421" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T421" t="inlineStr">
+        <is>
+          <t>1344356131</t>
+        </is>
+      </c>
+      <c r="U421" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1344356131</t>
+        </is>
+      </c>
+      <c r="V421" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="422">
+      <c r="A422" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B422" t="inlineStr">
+        <is>
+          <t>비영 네일&amp;속눈썹</t>
+        </is>
+      </c>
+      <c r="C422" t="inlineStr">
+        <is>
+          <t>murteri@naver.com</t>
+        </is>
+      </c>
+      <c r="D422" t="inlineStr"/>
+      <c r="E422" t="inlineStr">
+        <is>
+          <t>0507-1314-7075</t>
+        </is>
+      </c>
+      <c r="F422" t="inlineStr"/>
+      <c r="G422" t="inlineStr">
+        <is>
+          <t>서울특별시 강남구 도산대로85길 30 1층 113호(건물외곽 코너)</t>
+        </is>
+      </c>
+      <c r="H422" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/murteri</t>
+        </is>
+      </c>
+      <c r="I422" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J422" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K422" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L422" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M422" t="inlineStr"/>
+      <c r="N422" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O422" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P422" t="n">
+        <v>16</v>
+      </c>
+      <c r="Q422" t="n">
+        <v>4</v>
+      </c>
+      <c r="R422" t="n">
+        <v>20</v>
+      </c>
+      <c r="S422" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T422" t="inlineStr">
+        <is>
+          <t>1993130371</t>
+        </is>
+      </c>
+      <c r="U422" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1993130371</t>
+        </is>
+      </c>
+      <c r="V422" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="423">
+      <c r="A423" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B423" t="inlineStr">
+        <is>
+          <t>네일 아지트</t>
+        </is>
+      </c>
+      <c r="C423" t="inlineStr"/>
+      <c r="D423" t="inlineStr"/>
+      <c r="E423" t="inlineStr">
+        <is>
+          <t>0507-1306-0317</t>
+        </is>
+      </c>
+      <c r="F423" t="inlineStr"/>
+      <c r="G423" t="inlineStr">
+        <is>
+          <t>서울특별시 강남구 삼성로146길 4-1 4층</t>
+        </is>
+      </c>
+      <c r="H423" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/nail_a.zit</t>
+        </is>
+      </c>
+      <c r="I423" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J423" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K423" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L423" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M423" t="inlineStr"/>
+      <c r="N423" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O423" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P423" t="n">
+        <v>11</v>
+      </c>
+      <c r="Q423" t="n">
+        <v>1</v>
+      </c>
+      <c r="R423" t="n">
+        <v>12</v>
+      </c>
+      <c r="S423" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T423" t="inlineStr">
+        <is>
+          <t>2005342503</t>
+        </is>
+      </c>
+      <c r="U423" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2005342503</t>
+        </is>
+      </c>
+      <c r="V423" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="424">
+      <c r="A424" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B424" t="inlineStr">
+        <is>
+          <t>앤네일</t>
+        </is>
+      </c>
+      <c r="C424" t="inlineStr">
+        <is>
+          <t>sws0394@naver.com</t>
+        </is>
+      </c>
+      <c r="D424" t="inlineStr"/>
+      <c r="E424" t="inlineStr">
+        <is>
+          <t>0507-1349-8970</t>
+        </is>
+      </c>
+      <c r="F424" t="inlineStr"/>
+      <c r="G424" t="inlineStr">
+        <is>
+          <t>서울특별시 강남구 일원로5길 5 1층</t>
+        </is>
+      </c>
+      <c r="H424" t="inlineStr">
+        <is>
+          <t>http://www.instagram.com/annnail_55</t>
+        </is>
+      </c>
+      <c r="I424" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J424" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K424" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L424" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M424" t="inlineStr"/>
+      <c r="N424" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O424" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P424" t="n">
+        <v>15</v>
+      </c>
+      <c r="Q424" t="n">
+        <v>60</v>
+      </c>
+      <c r="R424" t="n">
+        <v>75</v>
+      </c>
+      <c r="S424" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T424" t="inlineStr">
+        <is>
+          <t>1303312081</t>
+        </is>
+      </c>
+      <c r="U424" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1303312081</t>
+        </is>
+      </c>
+      <c r="V424" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="425">
+      <c r="A425" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B425" t="inlineStr">
+        <is>
+          <t>모든네일</t>
+        </is>
+      </c>
+      <c r="C425" t="inlineStr">
+        <is>
+          <t>joowon__0310@naver.com</t>
+        </is>
+      </c>
+      <c r="D425" t="inlineStr"/>
+      <c r="E425" t="inlineStr">
+        <is>
+          <t>0507-1387-8503</t>
+        </is>
+      </c>
+      <c r="F425" t="inlineStr"/>
+      <c r="G425" t="inlineStr">
+        <is>
+          <t>서울특별시 강남구 논현로85길 52 역삼푸르지오시티상가 지하1층 107호</t>
+        </is>
+      </c>
+      <c r="H425" t="inlineStr">
+        <is>
+          <t>http://instagram.com/nail_md</t>
+        </is>
+      </c>
+      <c r="I425" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J425" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K425" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L425" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M425" t="inlineStr"/>
+      <c r="N425" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O425" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P425" t="n">
+        <v>1114</v>
+      </c>
+      <c r="Q425" t="n">
+        <v>355</v>
+      </c>
+      <c r="R425" t="n">
+        <v>1469</v>
+      </c>
+      <c r="S425" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T425" t="inlineStr">
+        <is>
+          <t>38563681</t>
+        </is>
+      </c>
+      <c r="U425" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/38563681</t>
+        </is>
+      </c>
+      <c r="V425" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="426">
+      <c r="A426" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B426" t="inlineStr">
+        <is>
+          <t>누니네일 도산점</t>
+        </is>
+      </c>
+      <c r="C426" t="inlineStr"/>
+      <c r="D426" t="inlineStr"/>
+      <c r="E426" t="inlineStr">
+        <is>
+          <t>0507-1345-6826</t>
+        </is>
+      </c>
+      <c r="F426" t="inlineStr"/>
+      <c r="G426" t="inlineStr">
+        <is>
+          <t>서울특별시 강남구 선릉로153길 36 3층</t>
+        </is>
+      </c>
+      <c r="H426" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/nuninail</t>
+        </is>
+      </c>
+      <c r="I426" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J426" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K426" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L426" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M426" t="inlineStr"/>
+      <c r="N426" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O426" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P426" t="n">
+        <v>55</v>
+      </c>
+      <c r="Q426" t="n">
+        <v>12</v>
+      </c>
+      <c r="R426" t="n">
+        <v>67</v>
+      </c>
+      <c r="S426" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T426" t="inlineStr">
+        <is>
+          <t>1464780459</t>
+        </is>
+      </c>
+      <c r="U426" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1464780459</t>
+        </is>
+      </c>
+      <c r="V426" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="427">
+      <c r="A427" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B427" t="inlineStr">
+        <is>
+          <t>네일탐이나</t>
+        </is>
+      </c>
+      <c r="C427" t="inlineStr">
+        <is>
+          <t>moth0403@naver.com</t>
+        </is>
+      </c>
+      <c r="D427" t="inlineStr"/>
+      <c r="E427" t="inlineStr">
+        <is>
+          <t>02-548-4865</t>
+        </is>
+      </c>
+      <c r="F427" t="inlineStr"/>
+      <c r="G427" t="inlineStr">
+        <is>
+          <t>서울특별시 강남구 선릉로153길 7 ,2층</t>
+        </is>
+      </c>
+      <c r="H427" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/nailtam2na/</t>
+        </is>
+      </c>
+      <c r="I427" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J427" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K427" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L427" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M427" t="inlineStr"/>
+      <c r="N427" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O427" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P427" t="n">
+        <v>55</v>
+      </c>
+      <c r="Q427" t="n">
+        <v>272</v>
+      </c>
+      <c r="R427" t="n">
+        <v>327</v>
+      </c>
+      <c r="S427" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T427" t="inlineStr">
+        <is>
+          <t>33102330</t>
+        </is>
+      </c>
+      <c r="U427" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/33102330</t>
+        </is>
+      </c>
+      <c r="V427" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="428">
+      <c r="A428" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B428" t="inlineStr">
+        <is>
+          <t>나노네일</t>
+        </is>
+      </c>
+      <c r="C428" t="inlineStr"/>
+      <c r="D428" t="inlineStr"/>
+      <c r="E428" t="inlineStr">
+        <is>
+          <t>0507-1399-0853</t>
+        </is>
+      </c>
+      <c r="F428" t="inlineStr"/>
+      <c r="G428" t="inlineStr">
+        <is>
+          <t>서울특별시 강남구 언주로98길 9 제이씨빌딩 3층</t>
+        </is>
+      </c>
+      <c r="H428" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/na_nonail?igsh=dmdhMWtyZjA0cnVm&amp;utm_source=qr</t>
+        </is>
+      </c>
+      <c r="I428" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J428" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K428" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L428" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M428" t="inlineStr"/>
+      <c r="N428" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O428" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P428" t="n">
+        <v>468</v>
+      </c>
+      <c r="Q428" t="n">
+        <v>67</v>
+      </c>
+      <c r="R428" t="n">
+        <v>535</v>
+      </c>
+      <c r="S428" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T428" t="inlineStr">
+        <is>
+          <t>2053470010</t>
+        </is>
+      </c>
+      <c r="U428" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2053470010</t>
+        </is>
+      </c>
+      <c r="V428" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="429">
+      <c r="A429" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B429" t="inlineStr">
+        <is>
+          <t>파라티네일역삼</t>
+        </is>
+      </c>
+      <c r="C429" t="inlineStr">
+        <is>
+          <t>naillove1@naver.com</t>
+        </is>
+      </c>
+      <c r="D429" t="inlineStr"/>
+      <c r="E429" t="inlineStr">
+        <is>
+          <t>0507-1379-9748</t>
+        </is>
+      </c>
+      <c r="F429" t="inlineStr"/>
+      <c r="G429" t="inlineStr">
+        <is>
+          <t>서울특별시 강남구 논현로63길 16 2층 209호 서해그랑블</t>
+        </is>
+      </c>
+      <c r="H429" t="inlineStr">
+        <is>
+          <t>http://pf.kakao.com/_xjWBns</t>
+        </is>
+      </c>
+      <c r="I429" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J429" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K429" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L429" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M429" t="inlineStr"/>
+      <c r="N429" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O429" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P429" t="n">
+        <v>78</v>
+      </c>
+      <c r="Q429" t="n">
+        <v>8</v>
+      </c>
+      <c r="R429" t="n">
+        <v>86</v>
+      </c>
+      <c r="S429" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T429" t="inlineStr">
+        <is>
+          <t>1936705506</t>
+        </is>
+      </c>
+      <c r="U429" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1936705506</t>
+        </is>
+      </c>
+      <c r="V429" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="430">
+      <c r="A430" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B430" t="inlineStr">
+        <is>
+          <t>티아라네일</t>
+        </is>
+      </c>
+      <c r="C430" t="inlineStr">
+        <is>
+          <t>pkran73@naver.com</t>
+        </is>
+      </c>
+      <c r="D430" t="inlineStr"/>
+      <c r="E430" t="inlineStr">
+        <is>
+          <t>0507-1426-6604</t>
+        </is>
+      </c>
+      <c r="F430" t="inlineStr"/>
+      <c r="G430" t="inlineStr">
+        <is>
+          <t>서울특별시 강남구 학동로 342 에스케이 허브 블루</t>
+        </is>
+      </c>
+      <c r="H430" t="inlineStr">
+        <is>
+          <t>http://www.instagram.com/tiara_nail_</t>
+        </is>
+      </c>
+      <c r="I430" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J430" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K430" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L430" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M430" t="inlineStr"/>
+      <c r="N430" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O430" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P430" t="n">
+        <v>85</v>
+      </c>
+      <c r="Q430" t="n">
+        <v>46</v>
+      </c>
+      <c r="R430" t="n">
+        <v>131</v>
+      </c>
+      <c r="S430" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T430" t="inlineStr">
+        <is>
+          <t>20582046</t>
+        </is>
+      </c>
+      <c r="U430" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/20582046</t>
+        </is>
+      </c>
+      <c r="V430" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="431">
+      <c r="A431" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B431" t="inlineStr">
+        <is>
+          <t>미쥬네일 강남신논현점</t>
+        </is>
+      </c>
+      <c r="C431" t="inlineStr">
+        <is>
+          <t>ksmko2026@naver.com</t>
+        </is>
+      </c>
+      <c r="D431" t="inlineStr"/>
+      <c r="E431" t="inlineStr">
+        <is>
+          <t>0507-1446-0689</t>
+        </is>
+      </c>
+      <c r="F431" t="inlineStr"/>
+      <c r="G431" t="inlineStr">
+        <is>
+          <t>서울특별시 강남구 봉은사로2길 13 3층</t>
+        </is>
+      </c>
+      <c r="H431" t="inlineStr">
+        <is>
+          <t>http://pf.kakao.com/_PxehYs/chat</t>
+        </is>
+      </c>
+      <c r="I431" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J431" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K431" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L431" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M431" t="inlineStr"/>
+      <c r="N431" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O431" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P431" t="n">
+        <v>684</v>
+      </c>
+      <c r="Q431" t="n">
+        <v>82</v>
+      </c>
+      <c r="R431" t="n">
+        <v>766</v>
+      </c>
+      <c r="S431" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T431" t="inlineStr">
+        <is>
+          <t>1375175853</t>
+        </is>
+      </c>
+      <c r="U431" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1375175853</t>
+        </is>
+      </c>
+      <c r="V431" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="432">
+      <c r="A432" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B432" t="inlineStr">
+        <is>
+          <t>네일라로즈</t>
+        </is>
+      </c>
+      <c r="C432" t="inlineStr">
+        <is>
+          <t>yeh9298@naver.com</t>
+        </is>
+      </c>
+      <c r="D432" t="inlineStr"/>
+      <c r="E432" t="inlineStr"/>
+      <c r="F432" t="inlineStr"/>
+      <c r="G432" t="inlineStr">
+        <is>
+          <t>서울특별시 강남구 강남대로158길 16 3층 302호</t>
+        </is>
+      </c>
+      <c r="H432" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/nail_larose?igsh=OW40azBmemQ3Nnhl&amp;utm_source=qr</t>
+        </is>
+      </c>
+      <c r="I432" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J432" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K432" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L432" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M432" t="inlineStr"/>
+      <c r="N432" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O432" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P432" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q432" t="n">
+        <v>3</v>
+      </c>
+      <c r="R432" t="n">
+        <v>3</v>
+      </c>
+      <c r="S432" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T432" t="inlineStr">
+        <is>
+          <t>1202595837</t>
+        </is>
+      </c>
+      <c r="U432" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1202595837</t>
+        </is>
+      </c>
+      <c r="V432" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="433">
+      <c r="A433" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B433" t="inlineStr">
+        <is>
+          <t>키라메키네일</t>
+        </is>
+      </c>
+      <c r="C433" t="inlineStr">
+        <is>
+          <t>kirameki41@naver.com</t>
+        </is>
+      </c>
+      <c r="D433" t="inlineStr"/>
+      <c r="E433" t="inlineStr">
+        <is>
+          <t>0507-1365-4143</t>
+        </is>
+      </c>
+      <c r="F433" t="inlineStr"/>
+      <c r="G433" t="inlineStr">
+        <is>
+          <t>서울특별시 강남구 도산대로49길 10-3 4층</t>
+        </is>
+      </c>
+      <c r="H433" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/kirameki41</t>
+        </is>
+      </c>
+      <c r="I433" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J433" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K433" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L433" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M433" t="inlineStr"/>
+      <c r="N433" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O433" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P433" t="n">
+        <v>46</v>
+      </c>
+      <c r="Q433" t="n">
+        <v>91</v>
+      </c>
+      <c r="R433" t="n">
+        <v>137</v>
+      </c>
+      <c r="S433" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T433" t="inlineStr">
+        <is>
+          <t>36132831</t>
+        </is>
+      </c>
+      <c r="U433" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/36132831</t>
+        </is>
+      </c>
+      <c r="V433" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="434">
+      <c r="A434" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B434" t="inlineStr">
+        <is>
+          <t>손네일</t>
+        </is>
+      </c>
+      <c r="C434" t="inlineStr">
+        <is>
+          <t>nail4season@naver.com</t>
+        </is>
+      </c>
+      <c r="D434" t="inlineStr"/>
+      <c r="E434" t="inlineStr">
+        <is>
+          <t>0507-1323-6967</t>
+        </is>
+      </c>
+      <c r="F434" t="inlineStr"/>
+      <c r="G434" t="inlineStr">
+        <is>
+          <t>서울특별시 강남구 도곡로 408 B1</t>
+        </is>
+      </c>
+      <c r="H434" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/sonnail_?igsh=MnRqNmI5dXZrdjQ4&amp;utm_source=qr</t>
+        </is>
+      </c>
+      <c r="I434" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J434" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K434" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L434" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M434" t="inlineStr"/>
+      <c r="N434" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O434" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P434" t="n">
+        <v>9</v>
+      </c>
+      <c r="Q434" t="n">
+        <v>36</v>
+      </c>
+      <c r="R434" t="n">
+        <v>45</v>
+      </c>
+      <c r="S434" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T434" t="inlineStr">
+        <is>
+          <t>1209988321</t>
+        </is>
+      </c>
+      <c r="U434" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1209988321</t>
+        </is>
+      </c>
+      <c r="V434" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="435">
+      <c r="A435" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B435" t="inlineStr">
+        <is>
+          <t>오유정네일</t>
+        </is>
+      </c>
+      <c r="C435" t="inlineStr">
+        <is>
+          <t>ouou614@naver.com</t>
+        </is>
+      </c>
+      <c r="D435" t="inlineStr"/>
+      <c r="E435" t="inlineStr"/>
+      <c r="F435" t="inlineStr"/>
+      <c r="G435" t="inlineStr">
+        <is>
+          <t>서울특별시 강남구 논현로151길 41 3층 301호</t>
+        </is>
+      </c>
+      <c r="H435" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/ouou614</t>
+        </is>
+      </c>
+      <c r="I435" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J435" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K435" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L435" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M435" t="inlineStr"/>
+      <c r="N435" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O435" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P435" t="n">
+        <v>136</v>
+      </c>
+      <c r="Q435" t="n">
+        <v>36</v>
+      </c>
+      <c r="R435" t="n">
+        <v>172</v>
+      </c>
+      <c r="S435" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T435" t="inlineStr">
+        <is>
+          <t>1711045679</t>
+        </is>
+      </c>
+      <c r="U435" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1711045679</t>
+        </is>
+      </c>
+      <c r="V435" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="436">
+      <c r="A436" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B436" t="inlineStr">
+        <is>
+          <t>제니스리치 강남역점</t>
+        </is>
+      </c>
+      <c r="C436" t="inlineStr">
+        <is>
+          <t>jennisrich15@naver.com</t>
+        </is>
+      </c>
+      <c r="D436" t="inlineStr"/>
+      <c r="E436" t="inlineStr">
+        <is>
+          <t>0507-1351-3886</t>
+        </is>
+      </c>
+      <c r="F436" t="inlineStr"/>
+      <c r="G436" t="inlineStr">
+        <is>
+          <t>서울특별시 강남구 테헤란로4길 6 센트럴 푸르지오 시티 1층</t>
+        </is>
+      </c>
+      <c r="H436" t="inlineStr">
+        <is>
+          <t>https://zero.gongbiz.kr/shop/S000033986</t>
+        </is>
+      </c>
+      <c r="I436" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J436" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K436" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L436" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M436" t="inlineStr"/>
+      <c r="N436" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O436" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P436" t="n">
+        <v>131</v>
+      </c>
+      <c r="Q436" t="n">
+        <v>96</v>
+      </c>
+      <c r="R436" t="n">
+        <v>227</v>
+      </c>
+      <c r="S436" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T436" t="inlineStr">
+        <is>
+          <t>38654257</t>
+        </is>
+      </c>
+      <c r="U436" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/38654257</t>
+        </is>
+      </c>
+      <c r="V436" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="437">
+      <c r="A437" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B437" t="inlineStr">
+        <is>
+          <t>코코네일</t>
+        </is>
+      </c>
+      <c r="C437" t="inlineStr">
+        <is>
+          <t>jjuahlee@naver.com</t>
+        </is>
+      </c>
+      <c r="D437" t="inlineStr"/>
+      <c r="E437" t="inlineStr">
+        <is>
+          <t>0507-1340-5157</t>
+        </is>
+      </c>
+      <c r="F437" t="inlineStr"/>
+      <c r="G437" t="inlineStr">
+        <is>
+          <t>서울특별시 강남구 테헤란로 124 지하1층 103호</t>
+        </is>
+      </c>
+      <c r="H437" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I437" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J437" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K437" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L437" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M437" t="inlineStr"/>
+      <c r="N437" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O437" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P437" t="n">
+        <v>86</v>
+      </c>
+      <c r="Q437" t="n">
+        <v>9</v>
+      </c>
+      <c r="R437" t="n">
+        <v>95</v>
+      </c>
+      <c r="S437" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T437" t="inlineStr">
+        <is>
+          <t>1425952193</t>
+        </is>
+      </c>
+      <c r="U437" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1425952193</t>
+        </is>
+      </c>
+      <c r="V437" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="438">
+      <c r="A438" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B438" t="inlineStr">
+        <is>
+          <t>opopnail</t>
+        </is>
+      </c>
+      <c r="C438" t="inlineStr">
+        <is>
+          <t>peep5986@naver.com</t>
+        </is>
+      </c>
+      <c r="D438" t="inlineStr"/>
+      <c r="E438" t="inlineStr">
+        <is>
+          <t>0507-1316-2618</t>
+        </is>
+      </c>
+      <c r="F438" t="inlineStr"/>
+      <c r="G438" t="inlineStr">
+        <is>
+          <t>서울특별시 강남구 강남대로146길 7 1층 OPOPNAIL</t>
+        </is>
+      </c>
+      <c r="H438" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/opopnail?igsh=MWg5eDJrZ3A1d2V1ZA%3D%3D&amp;utm_source=qr</t>
+        </is>
+      </c>
+      <c r="I438" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J438" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K438" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L438" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M438" t="inlineStr"/>
+      <c r="N438" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O438" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P438" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q438" t="n">
+        <v>1</v>
+      </c>
+      <c r="R438" t="n">
+        <v>1</v>
+      </c>
+      <c r="S438" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T438" t="inlineStr">
+        <is>
+          <t>2001469380</t>
+        </is>
+      </c>
+      <c r="U438" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2001469380</t>
+        </is>
+      </c>
+      <c r="V438" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="439">
+      <c r="A439" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B439" t="inlineStr">
+        <is>
+          <t>핑크네일오브뉴욕</t>
+        </is>
+      </c>
+      <c r="C439" t="inlineStr">
+        <is>
+          <t>ik0726@naver.com</t>
+        </is>
+      </c>
+      <c r="D439" t="inlineStr"/>
+      <c r="E439" t="inlineStr">
+        <is>
+          <t>02-515-8586</t>
+        </is>
+      </c>
+      <c r="F439" t="inlineStr"/>
+      <c r="G439" t="inlineStr">
+        <is>
+          <t>서울특별시 강남구 압구정로54길 6</t>
+        </is>
+      </c>
+      <c r="H439" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I439" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J439" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K439" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L439" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M439" t="inlineStr"/>
+      <c r="N439" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O439" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P439" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q439" t="n">
+        <v>0</v>
+      </c>
+      <c r="R439" t="n">
+        <v>6</v>
+      </c>
+      <c r="S439" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T439" t="inlineStr">
+        <is>
+          <t>18485741</t>
+        </is>
+      </c>
+      <c r="U439" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/18485741</t>
+        </is>
+      </c>
+      <c r="V439" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="440">
+      <c r="A440" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B440" t="inlineStr">
+        <is>
+          <t>코호네일</t>
+        </is>
+      </c>
+      <c r="C440" t="inlineStr"/>
+      <c r="D440" t="inlineStr"/>
+      <c r="E440" t="inlineStr">
+        <is>
+          <t>0507-1347-6232</t>
+        </is>
+      </c>
+      <c r="F440" t="inlineStr"/>
+      <c r="G440" t="inlineStr">
+        <is>
+          <t>서울특별시 강남구 테헤란로83길 36 5층</t>
+        </is>
+      </c>
+      <c r="H440" t="inlineStr">
+        <is>
+          <t>https://linktr.ee/kohonail</t>
+        </is>
+      </c>
+      <c r="I440" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J440" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K440" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L440" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M440" t="inlineStr"/>
+      <c r="N440" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O440" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P440" t="n">
+        <v>249</v>
+      </c>
+      <c r="Q440" t="n">
+        <v>77</v>
+      </c>
+      <c r="R440" t="n">
+        <v>326</v>
+      </c>
+      <c r="S440" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T440" t="inlineStr">
+        <is>
+          <t>1047661629</t>
+        </is>
+      </c>
+      <c r="U440" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1047661629</t>
+        </is>
+      </c>
+      <c r="V440" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="441">
+      <c r="A441" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B441" t="inlineStr">
+        <is>
+          <t>토끼살롱 청담점</t>
+        </is>
+      </c>
+      <c r="C441" t="inlineStr">
+        <is>
+          <t>salondelapin@naver.com</t>
+        </is>
+      </c>
+      <c r="D441" t="inlineStr"/>
+      <c r="E441" t="inlineStr">
+        <is>
+          <t>0507-1310-2645</t>
+        </is>
+      </c>
+      <c r="F441" t="inlineStr"/>
+      <c r="G441" t="inlineStr">
+        <is>
+          <t>서울특별시 강남구 선릉로148길 48-6 1층 오른쪽 방</t>
+        </is>
+      </c>
+      <c r="H441" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/salondelapin</t>
+        </is>
+      </c>
+      <c r="I441" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J441" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K441" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L441" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M441" t="inlineStr"/>
+      <c r="N441" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O441" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P441" t="n">
+        <v>105</v>
+      </c>
+      <c r="Q441" t="n">
+        <v>98</v>
+      </c>
+      <c r="R441" t="n">
+        <v>203</v>
+      </c>
+      <c r="S441" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T441" t="inlineStr">
+        <is>
+          <t>1172579459</t>
+        </is>
+      </c>
+      <c r="U441" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1172579459</t>
+        </is>
+      </c>
+      <c r="V441" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="442">
+      <c r="A442" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B442" t="inlineStr">
+        <is>
+          <t>비 네일&amp; 비 래쉬</t>
+        </is>
+      </c>
+      <c r="C442" t="inlineStr">
+        <is>
+          <t>fe6d8jbx@naver.com</t>
+        </is>
+      </c>
+      <c r="D442" t="inlineStr"/>
+      <c r="E442" t="inlineStr">
+        <is>
+          <t>0507-1409-3215</t>
+        </is>
+      </c>
+      <c r="F442" t="inlineStr"/>
+      <c r="G442" t="inlineStr">
+        <is>
+          <t>서울특별시 강남구 학동로18길 18 1층 102호</t>
+        </is>
+      </c>
+      <c r="H442" t="inlineStr">
+        <is>
+          <t>http://pf.kakao.com/_xaWYms</t>
+        </is>
+      </c>
+      <c r="I442" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J442" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K442" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L442" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M442" t="inlineStr"/>
+      <c r="N442" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O442" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P442" t="n">
+        <v>71</v>
+      </c>
+      <c r="Q442" t="n">
+        <v>108</v>
+      </c>
+      <c r="R442" t="n">
+        <v>179</v>
+      </c>
+      <c r="S442" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T442" t="inlineStr">
+        <is>
+          <t>1129972671</t>
+        </is>
+      </c>
+      <c r="U442" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1129972671</t>
+        </is>
+      </c>
+      <c r="V442" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="443">
+      <c r="A443" t="inlineStr">
+        <is>
+          <t>세무사</t>
+        </is>
+      </c>
+      <c r="B443" t="inlineStr">
+        <is>
+          <t>세성세무법인 삼성지점</t>
+        </is>
+      </c>
+      <c r="C443" t="inlineStr">
+        <is>
+          <t>sesung1216@naver.com</t>
+        </is>
+      </c>
+      <c r="D443" t="inlineStr"/>
+      <c r="E443" t="inlineStr">
+        <is>
+          <t>02-515-4642</t>
+        </is>
+      </c>
+      <c r="F443" t="inlineStr"/>
+      <c r="G443" t="inlineStr">
+        <is>
+          <t>서울특별시 강남구 봉은사로 454 금탁타워 5층</t>
+        </is>
+      </c>
+      <c r="H443" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/sesung1216</t>
+        </is>
+      </c>
+      <c r="I443" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J443" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K443" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L443" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M443" t="inlineStr"/>
+      <c r="N443" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O443" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P443" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q443" t="n">
+        <v>44</v>
+      </c>
+      <c r="R443" t="n">
+        <v>44</v>
+      </c>
+      <c r="S443" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T443" t="inlineStr">
+        <is>
+          <t>1397509005</t>
+        </is>
+      </c>
+      <c r="U443" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1397509005</t>
+        </is>
+      </c>
+      <c r="V443" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="444">
+      <c r="A444" t="inlineStr">
+        <is>
+          <t>속눈썹증모,연장</t>
+        </is>
+      </c>
+      <c r="B444" t="inlineStr">
+        <is>
+          <t>워너비뷰티</t>
+        </is>
+      </c>
+      <c r="C444" t="inlineStr">
+        <is>
+          <t>wannabe1105@naver.com</t>
+        </is>
+      </c>
+      <c r="D444" t="inlineStr"/>
+      <c r="E444" t="inlineStr">
+        <is>
+          <t>02-552-4043</t>
+        </is>
+      </c>
+      <c r="F444" t="inlineStr"/>
+      <c r="G444" t="inlineStr">
+        <is>
           <t>서울특별시 강남구 삼성로100길 25 2층</t>
         </is>
       </c>
-      <c r="H341" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="I341" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J341" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="K341" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="L341" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M341" t="inlineStr">
+      <c r="H444" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I444" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J444" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K444" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L444" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M444" t="inlineStr">
         <is>
           <t>https://talk.naver.com/ct/w44t1n</t>
         </is>
       </c>
-      <c r="N341" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="O341" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="P341" t="n">
+      <c r="N444" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O444" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P444" t="n">
         <v>229</v>
       </c>
-      <c r="Q341" t="n">
+      <c r="Q444" t="n">
         <v>66</v>
       </c>
-      <c r="R341" t="n">
+      <c r="R444" t="n">
         <v>295</v>
       </c>
-      <c r="S341" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T341" t="inlineStr">
+      <c r="S444" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T444" t="inlineStr">
         <is>
           <t>1523636698</t>
         </is>
       </c>
-      <c r="U341" t="inlineStr">
+      <c r="U444" t="inlineStr">
         <is>
           <t>https://m.place.naver.com/place/1523636698</t>
         </is>
       </c>
-      <c r="V341" t="inlineStr">
+      <c r="V444" t="inlineStr">
         <is>
           <t>2026-04-26</t>
         </is>

--- a/naver-place-crawler/results_nail/강남_네일샵.xlsx
+++ b/naver-place-crawler/results_nail/강남_네일샵.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V393"/>
+  <dimension ref="A1:V444"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -36911,34 +36911,34 @@
     <row r="392">
       <c r="A392" t="inlineStr">
         <is>
-          <t>세무사</t>
+          <t>네일아트,네일샵</t>
         </is>
       </c>
       <c r="B392" t="inlineStr">
         <is>
-          <t>세성세무법인 삼성지점</t>
+          <t>네일산책</t>
         </is>
       </c>
       <c r="C392" t="inlineStr">
         <is>
-          <t>sesung1216@naver.com</t>
+          <t>nailstroll@naver.com</t>
         </is>
       </c>
       <c r="D392" t="inlineStr"/>
       <c r="E392" t="inlineStr">
         <is>
-          <t>02-515-4642</t>
+          <t>0507-1484-6890</t>
         </is>
       </c>
       <c r="F392" t="inlineStr"/>
       <c r="G392" t="inlineStr">
         <is>
-          <t>서울특별시 강남구 봉은사로 454 금탁타워 5층</t>
+          <t>서울특별시 강남구 봉은사로 471 2층 201-1호</t>
         </is>
       </c>
       <c r="H392" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/sesung1216</t>
+          <t>https://www.instagram.com/nailstroll</t>
         </is>
       </c>
       <c r="I392" t="inlineStr">
@@ -36953,7 +36953,7 @@
       </c>
       <c r="K392" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L392" t="inlineStr">
@@ -36964,22 +36964,22 @@
       <c r="M392" t="inlineStr"/>
       <c r="N392" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O392" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P392" t="n">
-        <v>0</v>
+        <v>615</v>
       </c>
       <c r="Q392" t="n">
-        <v>44</v>
+        <v>867</v>
       </c>
       <c r="R392" t="n">
-        <v>44</v>
+        <v>1482</v>
       </c>
       <c r="S392" t="inlineStr">
         <is>
@@ -36988,12 +36988,12 @@
       </c>
       <c r="T392" t="inlineStr">
         <is>
-          <t>1397509005</t>
+          <t>1132799547</t>
         </is>
       </c>
       <c r="U392" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1397509005</t>
+          <t>https://m.place.naver.com/place/1132799547</t>
         </is>
       </c>
       <c r="V392" t="inlineStr">
@@ -37005,35 +37005,39 @@
     <row r="393">
       <c r="A393" t="inlineStr">
         <is>
-          <t>속눈썹증모,연장</t>
+          <t>네일아트,네일샵</t>
         </is>
       </c>
       <c r="B393" t="inlineStr">
         <is>
-          <t>워너비뷰티</t>
-        </is>
-      </c>
-      <c r="C393" t="inlineStr"/>
+          <t>아캔스탑잇네일</t>
+        </is>
+      </c>
+      <c r="C393" t="inlineStr">
+        <is>
+          <t>everours-@naver.com</t>
+        </is>
+      </c>
       <c r="D393" t="inlineStr"/>
       <c r="E393" t="inlineStr">
         <is>
-          <t>02-552-4043</t>
+          <t>0507-1363-4208</t>
         </is>
       </c>
       <c r="F393" t="inlineStr"/>
       <c r="G393" t="inlineStr">
         <is>
-          <t>서울특별시 강남구 삼성로100길 25 2층</t>
+          <t>서울특별시 강남구 밤고개로 165 근린생활시설 202호</t>
         </is>
       </c>
       <c r="H393" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_xaxfwTC</t>
+          <t>https://www.instagram.com/icantstopeatnail</t>
         </is>
       </c>
       <c r="I393" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J393" t="inlineStr">
@@ -37054,39 +37058,4797 @@
       <c r="M393" t="inlineStr"/>
       <c r="N393" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O393" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P393" t="n">
+        <v>187</v>
+      </c>
+      <c r="Q393" t="n">
+        <v>10</v>
+      </c>
+      <c r="R393" t="n">
+        <v>197</v>
+      </c>
+      <c r="S393" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T393" t="inlineStr">
+        <is>
+          <t>1351793907</t>
+        </is>
+      </c>
+      <c r="U393" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1351793907</t>
+        </is>
+      </c>
+      <c r="V393" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="394">
+      <c r="A394" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B394" t="inlineStr">
+        <is>
+          <t>앤네일</t>
+        </is>
+      </c>
+      <c r="C394" t="inlineStr">
+        <is>
+          <t>sws0394@naver.com</t>
+        </is>
+      </c>
+      <c r="D394" t="inlineStr"/>
+      <c r="E394" t="inlineStr">
+        <is>
+          <t>0507-1349-8970</t>
+        </is>
+      </c>
+      <c r="F394" t="inlineStr"/>
+      <c r="G394" t="inlineStr">
+        <is>
+          <t>서울특별시 강남구 일원로5길 5 1층</t>
+        </is>
+      </c>
+      <c r="H394" t="inlineStr">
+        <is>
+          <t>http://www.instagram.com/annnail_55</t>
+        </is>
+      </c>
+      <c r="I394" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J394" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K394" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L394" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M394" t="inlineStr"/>
+      <c r="N394" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O394" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P394" t="n">
+        <v>15</v>
+      </c>
+      <c r="Q394" t="n">
+        <v>60</v>
+      </c>
+      <c r="R394" t="n">
+        <v>75</v>
+      </c>
+      <c r="S394" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T394" t="inlineStr">
+        <is>
+          <t>1303312081</t>
+        </is>
+      </c>
+      <c r="U394" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1303312081</t>
+        </is>
+      </c>
+      <c r="V394" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="395">
+      <c r="A395" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B395" t="inlineStr">
+        <is>
+          <t>네일바이제이</t>
+        </is>
+      </c>
+      <c r="C395" t="inlineStr">
+        <is>
+          <t>minjee1209@naver.com</t>
+        </is>
+      </c>
+      <c r="D395" t="inlineStr"/>
+      <c r="E395" t="inlineStr"/>
+      <c r="F395" t="inlineStr"/>
+      <c r="G395" t="inlineStr">
+        <is>
+          <t>서울특별시 강남구 선릉로 328 남서울상가 1층 9호</t>
+        </is>
+      </c>
+      <c r="H395" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/nailbyj_j/</t>
+        </is>
+      </c>
+      <c r="I395" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J395" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K395" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L395" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M395" t="inlineStr"/>
+      <c r="N395" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O395" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P395" t="n">
+        <v>288</v>
+      </c>
+      <c r="Q395" t="n">
+        <v>71</v>
+      </c>
+      <c r="R395" t="n">
+        <v>359</v>
+      </c>
+      <c r="S395" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T395" t="inlineStr">
+        <is>
+          <t>37630380</t>
+        </is>
+      </c>
+      <c r="U395" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/37630380</t>
+        </is>
+      </c>
+      <c r="V395" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="396">
+      <c r="A396" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B396" t="inlineStr">
+        <is>
+          <t>르화뷰티</t>
+        </is>
+      </c>
+      <c r="C396" t="inlineStr">
+        <is>
+          <t>writeherh@naver.com</t>
+        </is>
+      </c>
+      <c r="D396" t="inlineStr"/>
+      <c r="E396" t="inlineStr">
+        <is>
+          <t>0507-1400-9350</t>
+        </is>
+      </c>
+      <c r="F396" t="inlineStr"/>
+      <c r="G396" t="inlineStr">
+        <is>
+          <t>서울특별시 강남구 남부순환로 2615 1층 122호</t>
+        </is>
+      </c>
+      <c r="H396" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/lehwa_beauty</t>
+        </is>
+      </c>
+      <c r="I396" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J396" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K396" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L396" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M396" t="inlineStr"/>
+      <c r="N396" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O396" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P396" t="n">
+        <v>19</v>
+      </c>
+      <c r="Q396" t="n">
+        <v>3</v>
+      </c>
+      <c r="R396" t="n">
+        <v>22</v>
+      </c>
+      <c r="S396" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T396" t="inlineStr">
+        <is>
+          <t>2052556715</t>
+        </is>
+      </c>
+      <c r="U396" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2052556715</t>
+        </is>
+      </c>
+      <c r="V396" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="397">
+      <c r="A397" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B397" t="inlineStr">
+        <is>
+          <t>제로네일</t>
+        </is>
+      </c>
+      <c r="C397" t="inlineStr"/>
+      <c r="D397" t="inlineStr"/>
+      <c r="E397" t="inlineStr">
+        <is>
+          <t>0507-1422-0014</t>
+        </is>
+      </c>
+      <c r="F397" t="inlineStr"/>
+      <c r="G397" t="inlineStr">
+        <is>
+          <t>서울특별시 강남구 압구정로54길 26 3층 제로네일</t>
+        </is>
+      </c>
+      <c r="H397" t="inlineStr">
+        <is>
+          <t>https://pf.kakao.com/_AwIKs</t>
+        </is>
+      </c>
+      <c r="I397" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J397" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K397" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L397" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M397" t="inlineStr"/>
+      <c r="N397" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O397" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P397" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q397" t="n">
+        <v>1</v>
+      </c>
+      <c r="R397" t="n">
+        <v>1</v>
+      </c>
+      <c r="S397" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T397" t="inlineStr">
+        <is>
+          <t>1851003663</t>
+        </is>
+      </c>
+      <c r="U397" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1851003663</t>
+        </is>
+      </c>
+      <c r="V397" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="398">
+      <c r="A398" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B398" t="inlineStr">
+        <is>
+          <t>레푸스 선릉점 인디고네일</t>
+        </is>
+      </c>
+      <c r="C398" t="inlineStr">
+        <is>
+          <t>indigonail@naver.com</t>
+        </is>
+      </c>
+      <c r="D398" t="inlineStr"/>
+      <c r="E398" t="inlineStr">
+        <is>
+          <t>0507-1420-3046</t>
+        </is>
+      </c>
+      <c r="F398" t="inlineStr"/>
+      <c r="G398" t="inlineStr">
+        <is>
+          <t>서울특별시 강남구 테헤란로57길 24 1층</t>
+        </is>
+      </c>
+      <c r="H398" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/indigonail</t>
+        </is>
+      </c>
+      <c r="I398" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J398" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K398" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L398" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M398" t="inlineStr"/>
+      <c r="N398" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O398" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P398" t="n">
+        <v>1420</v>
+      </c>
+      <c r="Q398" t="n">
+        <v>682</v>
+      </c>
+      <c r="R398" t="n">
+        <v>2102</v>
+      </c>
+      <c r="S398" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T398" t="inlineStr">
+        <is>
+          <t>35992652</t>
+        </is>
+      </c>
+      <c r="U398" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/35992652</t>
+        </is>
+      </c>
+      <c r="V398" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="399">
+      <c r="A399" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B399" t="inlineStr">
+        <is>
+          <t>바비인형네일&amp;속눈썹</t>
+        </is>
+      </c>
+      <c r="C399" t="inlineStr">
+        <is>
+          <t>4udbfl@naver.com</t>
+        </is>
+      </c>
+      <c r="D399" t="inlineStr"/>
+      <c r="E399" t="inlineStr">
+        <is>
+          <t>0507-1495-5521</t>
+        </is>
+      </c>
+      <c r="F399" t="inlineStr"/>
+      <c r="G399" t="inlineStr">
+        <is>
+          <t>서울특별시 강남구 테헤란로1길 44 303호</t>
+        </is>
+      </c>
+      <c r="H399" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/4udbfl</t>
+        </is>
+      </c>
+      <c r="I399" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J399" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K399" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L399" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M399" t="inlineStr"/>
+      <c r="N399" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O399" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P399" t="n">
+        <v>142</v>
+      </c>
+      <c r="Q399" t="n">
+        <v>899</v>
+      </c>
+      <c r="R399" t="n">
+        <v>1041</v>
+      </c>
+      <c r="S399" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T399" t="inlineStr">
+        <is>
+          <t>31676164</t>
+        </is>
+      </c>
+      <c r="U399" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/31676164</t>
+        </is>
+      </c>
+      <c r="V399" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="400">
+      <c r="A400" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B400" t="inlineStr">
+        <is>
+          <t>연네일</t>
+        </is>
+      </c>
+      <c r="C400" t="inlineStr"/>
+      <c r="D400" t="inlineStr"/>
+      <c r="E400" t="inlineStr">
+        <is>
+          <t>02-797-2700</t>
+        </is>
+      </c>
+      <c r="F400" t="inlineStr"/>
+      <c r="G400" t="inlineStr">
+        <is>
+          <t>서울특별시 강남구 언주로 118 우성캐릭터199빌딩 130호</t>
+        </is>
+      </c>
+      <c r="H400" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I400" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J400" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K400" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L400" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M400" t="inlineStr"/>
+      <c r="N400" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O400" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P400" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q400" t="n">
+        <v>0</v>
+      </c>
+      <c r="R400" t="n">
+        <v>0</v>
+      </c>
+      <c r="S400" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T400" t="inlineStr">
+        <is>
+          <t>20034237</t>
+        </is>
+      </c>
+      <c r="U400" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/20034237</t>
+        </is>
+      </c>
+      <c r="V400" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="401">
+      <c r="A401" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B401" t="inlineStr">
+        <is>
+          <t>도쿄네일 신사점</t>
+        </is>
+      </c>
+      <c r="C401" t="inlineStr">
+        <is>
+          <t>yurinail0610@naver.com</t>
+        </is>
+      </c>
+      <c r="D401" t="inlineStr"/>
+      <c r="E401" t="inlineStr"/>
+      <c r="F401" t="inlineStr"/>
+      <c r="G401" t="inlineStr">
+        <is>
+          <t>서울특별시 강남구 논현로149길 65 2층 201호</t>
+        </is>
+      </c>
+      <c r="H401" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/yurinail0610</t>
+        </is>
+      </c>
+      <c r="I401" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J401" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K401" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L401" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M401" t="inlineStr"/>
+      <c r="N401" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O401" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P401" t="n">
+        <v>83</v>
+      </c>
+      <c r="Q401" t="n">
+        <v>59</v>
+      </c>
+      <c r="R401" t="n">
+        <v>142</v>
+      </c>
+      <c r="S401" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T401" t="inlineStr">
+        <is>
+          <t>1676138057</t>
+        </is>
+      </c>
+      <c r="U401" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1676138057</t>
+        </is>
+      </c>
+      <c r="V401" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="402">
+      <c r="A402" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B402" t="inlineStr">
+        <is>
+          <t>더꼼네일</t>
+        </is>
+      </c>
+      <c r="C402" t="inlineStr">
+        <is>
+          <t>kjuuu0716@naver.com</t>
+        </is>
+      </c>
+      <c r="D402" t="inlineStr"/>
+      <c r="E402" t="inlineStr">
+        <is>
+          <t>0507-1375-6412</t>
+        </is>
+      </c>
+      <c r="F402" t="inlineStr"/>
+      <c r="G402" t="inlineStr">
+        <is>
+          <t>서울특별시 강남구 테헤란로57길 32 B1</t>
+        </is>
+      </c>
+      <c r="H402" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/the_ccom_nail</t>
+        </is>
+      </c>
+      <c r="I402" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J402" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K402" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L402" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M402" t="inlineStr"/>
+      <c r="N402" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O402" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P402" t="n">
+        <v>128</v>
+      </c>
+      <c r="Q402" t="n">
+        <v>46</v>
+      </c>
+      <c r="R402" t="n">
+        <v>174</v>
+      </c>
+      <c r="S402" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T402" t="inlineStr">
+        <is>
+          <t>1571173388</t>
+        </is>
+      </c>
+      <c r="U402" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1571173388</t>
+        </is>
+      </c>
+      <c r="V402" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="403">
+      <c r="A403" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B403" t="inlineStr">
+        <is>
+          <t>제니스리치 강남역점</t>
+        </is>
+      </c>
+      <c r="C403" t="inlineStr">
+        <is>
+          <t>jennisrich15@naver.com</t>
+        </is>
+      </c>
+      <c r="D403" t="inlineStr"/>
+      <c r="E403" t="inlineStr">
+        <is>
+          <t>0507-1351-3886</t>
+        </is>
+      </c>
+      <c r="F403" t="inlineStr"/>
+      <c r="G403" t="inlineStr">
+        <is>
+          <t>서울특별시 강남구 테헤란로4길 6 센트럴 푸르지오 시티 1층</t>
+        </is>
+      </c>
+      <c r="H403" t="inlineStr">
+        <is>
+          <t>https://zero.gongbiz.kr/shop/S000033986</t>
+        </is>
+      </c>
+      <c r="I403" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J403" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K403" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L403" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M403" t="inlineStr"/>
+      <c r="N403" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O403" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P403" t="n">
+        <v>131</v>
+      </c>
+      <c r="Q403" t="n">
+        <v>96</v>
+      </c>
+      <c r="R403" t="n">
+        <v>227</v>
+      </c>
+      <c r="S403" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T403" t="inlineStr">
+        <is>
+          <t>38654257</t>
+        </is>
+      </c>
+      <c r="U403" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/38654257</t>
+        </is>
+      </c>
+      <c r="V403" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="404">
+      <c r="A404" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B404" t="inlineStr">
+        <is>
+          <t>참살롱</t>
+        </is>
+      </c>
+      <c r="C404" t="inlineStr">
+        <is>
+          <t>charm_salon@naver.com</t>
+        </is>
+      </c>
+      <c r="D404" t="inlineStr"/>
+      <c r="E404" t="inlineStr">
+        <is>
+          <t>0507-1340-9017</t>
+        </is>
+      </c>
+      <c r="F404" t="inlineStr"/>
+      <c r="G404" t="inlineStr">
+        <is>
+          <t>서울특별시 강남구 자곡로 202 1층 109호</t>
+        </is>
+      </c>
+      <c r="H404" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/CHAM_salon_official</t>
+        </is>
+      </c>
+      <c r="I404" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J404" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K404" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L404" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M404" t="inlineStr"/>
+      <c r="N404" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O404" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P404" t="n">
+        <v>169</v>
+      </c>
+      <c r="Q404" t="n">
+        <v>0</v>
+      </c>
+      <c r="R404" t="n">
+        <v>169</v>
+      </c>
+      <c r="S404" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T404" t="inlineStr">
+        <is>
+          <t>1081725462</t>
+        </is>
+      </c>
+      <c r="U404" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1081725462</t>
+        </is>
+      </c>
+      <c r="V404" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="405">
+      <c r="A405" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B405" t="inlineStr">
+        <is>
+          <t>더파이브센스</t>
+        </is>
+      </c>
+      <c r="C405" t="inlineStr">
+        <is>
+          <t>kmy000403@naver.com</t>
+        </is>
+      </c>
+      <c r="D405" t="inlineStr"/>
+      <c r="E405" t="inlineStr">
+        <is>
+          <t>0507-1380-4121</t>
+        </is>
+      </c>
+      <c r="F405" t="inlineStr"/>
+      <c r="G405" t="inlineStr">
+        <is>
+          <t>서울특별시 강남구 논현로114길 11 해광빌딩 1층 더파이브센스(The5Sneses)</t>
+        </is>
+      </c>
+      <c r="H405" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com//the5senses_</t>
+        </is>
+      </c>
+      <c r="I405" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J405" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K405" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L405" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M405" t="inlineStr"/>
+      <c r="N405" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O405" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P405" t="n">
+        <v>180</v>
+      </c>
+      <c r="Q405" t="n">
+        <v>145</v>
+      </c>
+      <c r="R405" t="n">
+        <v>325</v>
+      </c>
+      <c r="S405" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T405" t="inlineStr">
+        <is>
+          <t>1213490829</t>
+        </is>
+      </c>
+      <c r="U405" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1213490829</t>
+        </is>
+      </c>
+      <c r="V405" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="406">
+      <c r="A406" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B406" t="inlineStr">
+        <is>
+          <t>내일디디</t>
+        </is>
+      </c>
+      <c r="C406" t="inlineStr">
+        <is>
+          <t>black585@naver.com</t>
+        </is>
+      </c>
+      <c r="D406" t="inlineStr"/>
+      <c r="E406" t="inlineStr">
+        <is>
+          <t>0507-1341-5722</t>
+        </is>
+      </c>
+      <c r="F406" t="inlineStr"/>
+      <c r="G406" t="inlineStr">
+        <is>
+          <t>서울특별시 강남구 압구정로50길 18 6층 601호</t>
+        </is>
+      </c>
+      <c r="H406" t="inlineStr">
+        <is>
+          <t>http://www.instagram.com/tomorrow.dd_</t>
+        </is>
+      </c>
+      <c r="I406" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J406" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K406" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L406" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M406" t="inlineStr"/>
+      <c r="N406" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O406" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P406" t="n">
+        <v>379</v>
+      </c>
+      <c r="Q406" t="n">
+        <v>601</v>
+      </c>
+      <c r="R406" t="n">
+        <v>980</v>
+      </c>
+      <c r="S406" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T406" t="inlineStr">
+        <is>
+          <t>1941401558</t>
+        </is>
+      </c>
+      <c r="U406" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1941401558</t>
+        </is>
+      </c>
+      <c r="V406" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="407">
+      <c r="A407" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B407" t="inlineStr">
+        <is>
+          <t>신사동 네일 더누크룸</t>
+        </is>
+      </c>
+      <c r="C407" t="inlineStr">
+        <is>
+          <t>mmming112@naver.com</t>
+        </is>
+      </c>
+      <c r="D407" t="inlineStr"/>
+      <c r="E407" t="inlineStr">
+        <is>
+          <t>0507-1477-8027</t>
+        </is>
+      </c>
+      <c r="F407" t="inlineStr"/>
+      <c r="G407" t="inlineStr">
+        <is>
+          <t>서울특별시 강남구 압구정로14길 35 2층 202호</t>
+        </is>
+      </c>
+      <c r="H407" t="inlineStr">
+        <is>
+          <t>http://pf.kakao.com/_KWVnn</t>
+        </is>
+      </c>
+      <c r="I407" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J407" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K407" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L407" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M407" t="inlineStr"/>
+      <c r="N407" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O407" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P407" t="n">
+        <v>56</v>
+      </c>
+      <c r="Q407" t="n">
+        <v>9</v>
+      </c>
+      <c r="R407" t="n">
+        <v>65</v>
+      </c>
+      <c r="S407" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T407" t="inlineStr">
+        <is>
+          <t>1616156850</t>
+        </is>
+      </c>
+      <c r="U407" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1616156850</t>
+        </is>
+      </c>
+      <c r="V407" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="408">
+      <c r="A408" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B408" t="inlineStr">
+        <is>
+          <t>강남네일맑음</t>
+        </is>
+      </c>
+      <c r="C408" t="inlineStr">
+        <is>
+          <t>s1514@naver.com</t>
+        </is>
+      </c>
+      <c r="D408" t="inlineStr"/>
+      <c r="E408" t="inlineStr">
+        <is>
+          <t>0507-1410-3143</t>
+        </is>
+      </c>
+      <c r="F408" t="inlineStr"/>
+      <c r="G408" t="inlineStr">
+        <is>
+          <t>서울특별시 강남구 강남대로78길 24 3층 강남네일맑음</t>
+        </is>
+      </c>
+      <c r="H408" t="inlineStr">
+        <is>
+          <t>https://pf.kakao.com/_xmzLxfxb</t>
+        </is>
+      </c>
+      <c r="I408" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J408" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K408" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L408" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M408" t="inlineStr"/>
+      <c r="N408" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O408" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P408" t="n">
+        <v>2526</v>
+      </c>
+      <c r="Q408" t="n">
+        <v>360</v>
+      </c>
+      <c r="R408" t="n">
+        <v>2886</v>
+      </c>
+      <c r="S408" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T408" t="inlineStr">
+        <is>
+          <t>37700060</t>
+        </is>
+      </c>
+      <c r="U408" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/37700060</t>
+        </is>
+      </c>
+      <c r="V408" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="409">
+      <c r="A409" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B409" t="inlineStr">
+        <is>
+          <t>베릴네일</t>
+        </is>
+      </c>
+      <c r="C409" t="inlineStr">
+        <is>
+          <t>s2binini@naver.com</t>
+        </is>
+      </c>
+      <c r="D409" t="inlineStr"/>
+      <c r="E409" t="inlineStr">
+        <is>
+          <t>0507-1407-5026</t>
+        </is>
+      </c>
+      <c r="F409" t="inlineStr"/>
+      <c r="G409" t="inlineStr">
+        <is>
+          <t>서울특별시 강남구 언주로93길 29 4층 401호</t>
+        </is>
+      </c>
+      <c r="H409" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/berylnail_</t>
+        </is>
+      </c>
+      <c r="I409" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J409" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K409" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L409" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M409" t="inlineStr"/>
+      <c r="N409" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O409" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P409" t="n">
+        <v>122</v>
+      </c>
+      <c r="Q409" t="n">
+        <v>11</v>
+      </c>
+      <c r="R409" t="n">
+        <v>133</v>
+      </c>
+      <c r="S409" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T409" t="inlineStr">
+        <is>
+          <t>1208197127</t>
+        </is>
+      </c>
+      <c r="U409" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1208197127</t>
+        </is>
+      </c>
+      <c r="V409" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="410">
+      <c r="A410" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B410" t="inlineStr">
+        <is>
+          <t>핀업네일</t>
+        </is>
+      </c>
+      <c r="C410" t="inlineStr">
+        <is>
+          <t>mirabia0714@naver.com</t>
+        </is>
+      </c>
+      <c r="D410" t="inlineStr"/>
+      <c r="E410" t="inlineStr">
+        <is>
+          <t>02-515-8087</t>
+        </is>
+      </c>
+      <c r="F410" t="inlineStr"/>
+      <c r="G410" t="inlineStr">
+        <is>
+          <t>서울특별시 강남구 도산대로62길 15 1층 핀업네일</t>
+        </is>
+      </c>
+      <c r="H410" t="inlineStr">
+        <is>
+          <t>https://instagram.com/pinupnail_?igshid=OGQ5ZDc2ODk2ZA==</t>
+        </is>
+      </c>
+      <c r="I410" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J410" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K410" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L410" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M410" t="inlineStr"/>
+      <c r="N410" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O410" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P410" t="n">
+        <v>27</v>
+      </c>
+      <c r="Q410" t="n">
+        <v>4</v>
+      </c>
+      <c r="R410" t="n">
+        <v>31</v>
+      </c>
+      <c r="S410" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T410" t="inlineStr">
+        <is>
+          <t>1597938714</t>
+        </is>
+      </c>
+      <c r="U410" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1597938714</t>
+        </is>
+      </c>
+      <c r="V410" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="411">
+      <c r="A411" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B411" t="inlineStr">
+        <is>
+          <t>벨로네일</t>
+        </is>
+      </c>
+      <c r="C411" t="inlineStr">
+        <is>
+          <t>allprettylove@naver.com</t>
+        </is>
+      </c>
+      <c r="D411" t="inlineStr"/>
+      <c r="E411" t="inlineStr">
+        <is>
+          <t>0507-1402-0155</t>
+        </is>
+      </c>
+      <c r="F411" t="inlineStr"/>
+      <c r="G411" t="inlineStr">
+        <is>
+          <t>서울특별시 강남구 양재대로33길 21 1층 102호</t>
+        </is>
+      </c>
+      <c r="H411" t="inlineStr">
+        <is>
+          <t>http://instagram.com/nail_h4845</t>
+        </is>
+      </c>
+      <c r="I411" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J411" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K411" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L411" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M411" t="inlineStr"/>
+      <c r="N411" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O411" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P411" t="n">
+        <v>99</v>
+      </c>
+      <c r="Q411" t="n">
+        <v>16</v>
+      </c>
+      <c r="R411" t="n">
+        <v>115</v>
+      </c>
+      <c r="S411" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T411" t="inlineStr">
+        <is>
+          <t>1046516068</t>
+        </is>
+      </c>
+      <c r="U411" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1046516068</t>
+        </is>
+      </c>
+      <c r="V411" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="412">
+      <c r="A412" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B412" t="inlineStr">
+        <is>
+          <t>홍혜선프로네일</t>
+        </is>
+      </c>
+      <c r="C412" t="inlineStr">
+        <is>
+          <t>wootak1626@naver.com</t>
+        </is>
+      </c>
+      <c r="D412" t="inlineStr"/>
+      <c r="E412" t="inlineStr">
+        <is>
+          <t>0507-1389-2368</t>
+        </is>
+      </c>
+      <c r="F412" t="inlineStr"/>
+      <c r="G412" t="inlineStr">
+        <is>
+          <t>서울특별시 강남구 학동로38길 40 1층 101호</t>
+        </is>
+      </c>
+      <c r="H412" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/honghyesun_pronail/</t>
+        </is>
+      </c>
+      <c r="I412" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J412" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K412" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L412" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M412" t="inlineStr"/>
+      <c r="N412" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O412" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P412" t="n">
+        <v>399</v>
+      </c>
+      <c r="Q412" t="n">
+        <v>133</v>
+      </c>
+      <c r="R412" t="n">
+        <v>532</v>
+      </c>
+      <c r="S412" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T412" t="inlineStr">
+        <is>
+          <t>1488876783</t>
+        </is>
+      </c>
+      <c r="U412" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1488876783</t>
+        </is>
+      </c>
+      <c r="V412" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="413">
+      <c r="A413" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B413" t="inlineStr">
+        <is>
+          <t>제이네일</t>
+        </is>
+      </c>
+      <c r="C413" t="inlineStr">
+        <is>
+          <t>rhkdmswl@naver.com</t>
+        </is>
+      </c>
+      <c r="D413" t="inlineStr"/>
+      <c r="E413" t="inlineStr">
+        <is>
+          <t>0507-1362-6427</t>
+        </is>
+      </c>
+      <c r="F413" t="inlineStr"/>
+      <c r="G413" t="inlineStr">
+        <is>
+          <t>서울특별시 강남구 선릉로 206 동부센트레빌 상가 1층 117호</t>
+        </is>
+      </c>
+      <c r="H413" t="inlineStr">
+        <is>
+          <t>https://homefine2470.mycafe24.com/</t>
+        </is>
+      </c>
+      <c r="I413" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J413" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K413" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L413" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M413" t="inlineStr"/>
+      <c r="N413" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O413" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P413" t="n">
+        <v>33</v>
+      </c>
+      <c r="Q413" t="n">
+        <v>3</v>
+      </c>
+      <c r="R413" t="n">
+        <v>36</v>
+      </c>
+      <c r="S413" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T413" t="inlineStr">
+        <is>
+          <t>2070234334</t>
+        </is>
+      </c>
+      <c r="U413" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2070234334</t>
+        </is>
+      </c>
+      <c r="V413" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="414">
+      <c r="A414" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B414" t="inlineStr">
+        <is>
+          <t>네일 움뷰티</t>
+        </is>
+      </c>
+      <c r="C414" t="inlineStr">
+        <is>
+          <t>myvely1@naver.com</t>
+        </is>
+      </c>
+      <c r="D414" t="inlineStr"/>
+      <c r="E414" t="inlineStr">
+        <is>
+          <t>0507-1336-2648</t>
+        </is>
+      </c>
+      <c r="F414" t="inlineStr"/>
+      <c r="G414" t="inlineStr">
+        <is>
+          <t>서울특별시 강남구 학동로34길 20 3층</t>
+        </is>
+      </c>
+      <c r="H414" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/myvely1</t>
+        </is>
+      </c>
+      <c r="I414" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J414" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K414" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L414" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M414" t="inlineStr"/>
+      <c r="N414" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O414" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P414" t="n">
+        <v>19</v>
+      </c>
+      <c r="Q414" t="n">
+        <v>29</v>
+      </c>
+      <c r="R414" t="n">
+        <v>48</v>
+      </c>
+      <c r="S414" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T414" t="inlineStr">
+        <is>
+          <t>1674089540</t>
+        </is>
+      </c>
+      <c r="U414" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1674089540</t>
+        </is>
+      </c>
+      <c r="V414" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="415">
+      <c r="A415" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B415" t="inlineStr">
+        <is>
+          <t>에드민 네일</t>
+        </is>
+      </c>
+      <c r="C415" t="inlineStr">
+        <is>
+          <t>addmin3411@naver.com</t>
+        </is>
+      </c>
+      <c r="D415" t="inlineStr"/>
+      <c r="E415" t="inlineStr">
+        <is>
+          <t>0507-1300-3411</t>
+        </is>
+      </c>
+      <c r="F415" t="inlineStr"/>
+      <c r="G415" t="inlineStr">
+        <is>
+          <t>서울특별시 강남구 강남대로120길 31 1층 에드민네일</t>
+        </is>
+      </c>
+      <c r="H415" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/addmin_nail/</t>
+        </is>
+      </c>
+      <c r="I415" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J415" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K415" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L415" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M415" t="inlineStr"/>
+      <c r="N415" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O415" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P415" t="n">
+        <v>240</v>
+      </c>
+      <c r="Q415" t="n">
+        <v>48</v>
+      </c>
+      <c r="R415" t="n">
+        <v>288</v>
+      </c>
+      <c r="S415" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T415" t="inlineStr">
+        <is>
+          <t>1706496056</t>
+        </is>
+      </c>
+      <c r="U415" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1706496056</t>
+        </is>
+      </c>
+      <c r="V415" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="416">
+      <c r="A416" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B416" t="inlineStr">
+        <is>
+          <t>오늘네일</t>
+        </is>
+      </c>
+      <c r="C416" t="inlineStr">
+        <is>
+          <t>todaynnail@naver.com</t>
+        </is>
+      </c>
+      <c r="D416" t="inlineStr"/>
+      <c r="E416" t="inlineStr"/>
+      <c r="F416" t="inlineStr"/>
+      <c r="G416" t="inlineStr">
+        <is>
+          <t>서울특별시 강남구 개포로82길 13-11 2층 204호 오늘네일</t>
+        </is>
+      </c>
+      <c r="H416" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/todaynnail</t>
+        </is>
+      </c>
+      <c r="I416" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J416" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K416" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L416" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M416" t="inlineStr"/>
+      <c r="N416" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O416" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P416" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q416" t="n">
+        <v>28</v>
+      </c>
+      <c r="R416" t="n">
+        <v>31</v>
+      </c>
+      <c r="S416" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T416" t="inlineStr">
+        <is>
+          <t>1213126581</t>
+        </is>
+      </c>
+      <c r="U416" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1213126581</t>
+        </is>
+      </c>
+      <c r="V416" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="417">
+      <c r="A417" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B417" t="inlineStr">
+        <is>
+          <t>초승달네일</t>
+        </is>
+      </c>
+      <c r="C417" t="inlineStr">
+        <is>
+          <t>miwoomiwoo27@naver.com</t>
+        </is>
+      </c>
+      <c r="D417" t="inlineStr"/>
+      <c r="E417" t="inlineStr">
+        <is>
+          <t>0507-1357-0944</t>
+        </is>
+      </c>
+      <c r="F417" t="inlineStr"/>
+      <c r="G417" t="inlineStr">
+        <is>
+          <t>서울특별시 강남구 삼성로71길 37 지상1층 102호</t>
+        </is>
+      </c>
+      <c r="H417" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/nailcrescent</t>
+        </is>
+      </c>
+      <c r="I417" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J417" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K417" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L417" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M417" t="inlineStr"/>
+      <c r="N417" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O417" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P417" t="n">
+        <v>139</v>
+      </c>
+      <c r="Q417" t="n">
+        <v>3</v>
+      </c>
+      <c r="R417" t="n">
+        <v>142</v>
+      </c>
+      <c r="S417" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T417" t="inlineStr">
+        <is>
+          <t>1925396402</t>
+        </is>
+      </c>
+      <c r="U417" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1925396402</t>
+        </is>
+      </c>
+      <c r="V417" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="418">
+      <c r="A418" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B418" t="inlineStr">
+        <is>
+          <t>네일포시즌 풋풋한리쌤 역삼점</t>
+        </is>
+      </c>
+      <c r="C418" t="inlineStr">
+        <is>
+          <t>footfoot4@naver.com</t>
+        </is>
+      </c>
+      <c r="D418" t="inlineStr"/>
+      <c r="E418" t="inlineStr">
+        <is>
+          <t>02-6953-3236</t>
+        </is>
+      </c>
+      <c r="F418" t="inlineStr"/>
+      <c r="G418" t="inlineStr">
+        <is>
+          <t>서울특별시 강남구 봉은사로 206 2층</t>
+        </is>
+      </c>
+      <c r="H418" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/footfoot4</t>
+        </is>
+      </c>
+      <c r="I418" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J418" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K418" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L418" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M418" t="inlineStr"/>
+      <c r="N418" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O418" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P418" t="n">
+        <v>2099</v>
+      </c>
+      <c r="Q418" t="n">
+        <v>245</v>
+      </c>
+      <c r="R418" t="n">
+        <v>2344</v>
+      </c>
+      <c r="S418" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T418" t="inlineStr">
+        <is>
+          <t>1556154058</t>
+        </is>
+      </c>
+      <c r="U418" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1556154058</t>
+        </is>
+      </c>
+      <c r="V418" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="419">
+      <c r="A419" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B419" t="inlineStr">
+        <is>
+          <t>글로이네일</t>
+        </is>
+      </c>
+      <c r="C419" t="inlineStr">
+        <is>
+          <t>sh_0503@naver.com</t>
+        </is>
+      </c>
+      <c r="D419" t="inlineStr"/>
+      <c r="E419" t="inlineStr">
+        <is>
+          <t>0507-1406-1721</t>
+        </is>
+      </c>
+      <c r="F419" t="inlineStr"/>
+      <c r="G419" t="inlineStr">
+        <is>
+          <t>서울특별시 강남구 헌릉로571길 9 1층 106호 글로이네일</t>
+        </is>
+      </c>
+      <c r="H419" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/glowwy_nail</t>
+        </is>
+      </c>
+      <c r="I419" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J419" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K419" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L419" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M419" t="inlineStr"/>
+      <c r="N419" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O419" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P419" t="n">
+        <v>30</v>
+      </c>
+      <c r="Q419" t="n">
+        <v>1</v>
+      </c>
+      <c r="R419" t="n">
+        <v>31</v>
+      </c>
+      <c r="S419" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T419" t="inlineStr">
+        <is>
+          <t>2075735615</t>
+        </is>
+      </c>
+      <c r="U419" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2075735615</t>
+        </is>
+      </c>
+      <c r="V419" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="420">
+      <c r="A420" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B420" t="inlineStr">
+        <is>
+          <t>투떰즈업네일</t>
+        </is>
+      </c>
+      <c r="C420" t="inlineStr">
+        <is>
+          <t>2thumbsup-nail@naver.com</t>
+        </is>
+      </c>
+      <c r="D420" t="inlineStr"/>
+      <c r="E420" t="inlineStr">
+        <is>
+          <t>0507-1381-9779</t>
+        </is>
+      </c>
+      <c r="F420" t="inlineStr"/>
+      <c r="G420" t="inlineStr">
+        <is>
+          <t>서울특별시 강남구 도산대로 158 101호</t>
+        </is>
+      </c>
+      <c r="H420" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/2thumbsup_nail</t>
+        </is>
+      </c>
+      <c r="I420" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J420" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K420" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L420" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M420" t="inlineStr"/>
+      <c r="N420" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O420" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P420" t="n">
+        <v>121</v>
+      </c>
+      <c r="Q420" t="n">
+        <v>70</v>
+      </c>
+      <c r="R420" t="n">
+        <v>191</v>
+      </c>
+      <c r="S420" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T420" t="inlineStr">
+        <is>
+          <t>1370289480</t>
+        </is>
+      </c>
+      <c r="U420" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1370289480</t>
+        </is>
+      </c>
+      <c r="V420" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="421">
+      <c r="A421" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B421" t="inlineStr">
+        <is>
+          <t>레이네일 앤 풋스파</t>
+        </is>
+      </c>
+      <c r="C421" t="inlineStr">
+        <is>
+          <t>yoo06007@naver.com</t>
+        </is>
+      </c>
+      <c r="D421" t="inlineStr"/>
+      <c r="E421" t="inlineStr">
+        <is>
+          <t>0507-1379-0569</t>
+        </is>
+      </c>
+      <c r="F421" t="inlineStr"/>
+      <c r="G421" t="inlineStr">
+        <is>
+          <t>서울특별시 강남구 삼성로 11 디에이치아너힐즈 상가 B108</t>
+        </is>
+      </c>
+      <c r="H421" t="inlineStr">
+        <is>
+          <t>http://instagram.com/leynail_</t>
+        </is>
+      </c>
+      <c r="I421" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J421" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K421" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L421" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M421" t="inlineStr"/>
+      <c r="N421" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O421" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P421" t="n">
+        <v>67</v>
+      </c>
+      <c r="Q421" t="n">
+        <v>123</v>
+      </c>
+      <c r="R421" t="n">
+        <v>190</v>
+      </c>
+      <c r="S421" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T421" t="inlineStr">
+        <is>
+          <t>972598699</t>
+        </is>
+      </c>
+      <c r="U421" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/972598699</t>
+        </is>
+      </c>
+      <c r="V421" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="422">
+      <c r="A422" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B422" t="inlineStr">
+        <is>
+          <t>림네일*</t>
+        </is>
+      </c>
+      <c r="C422" t="inlineStr">
+        <is>
+          <t>freshgang@naver.com</t>
+        </is>
+      </c>
+      <c r="D422" t="inlineStr"/>
+      <c r="E422" t="inlineStr">
+        <is>
+          <t>0507-1323-5549</t>
+        </is>
+      </c>
+      <c r="F422" t="inlineStr"/>
+      <c r="G422" t="inlineStr">
+        <is>
+          <t>서울특별시 강남구 언주로 118 오피스텔건물</t>
+        </is>
+      </c>
+      <c r="H422" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I422" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J422" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K422" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L422" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M422" t="inlineStr"/>
+      <c r="N422" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O422" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P422" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q422" t="n">
+        <v>1</v>
+      </c>
+      <c r="R422" t="n">
+        <v>1</v>
+      </c>
+      <c r="S422" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T422" t="inlineStr">
+        <is>
+          <t>1109281431</t>
+        </is>
+      </c>
+      <c r="U422" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1109281431</t>
+        </is>
+      </c>
+      <c r="V422" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="423">
+      <c r="A423" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B423" t="inlineStr">
+        <is>
+          <t>아이리스네일</t>
+        </is>
+      </c>
+      <c r="C423" t="inlineStr">
+        <is>
+          <t>baaa123@naver.com</t>
+        </is>
+      </c>
+      <c r="D423" t="inlineStr"/>
+      <c r="E423" t="inlineStr">
+        <is>
+          <t>0507-1412-8911</t>
+        </is>
+      </c>
+      <c r="F423" t="inlineStr"/>
+      <c r="G423" t="inlineStr">
+        <is>
+          <t>서울특별시 강남구 역삼로63길 20 2층 아이리스네일</t>
+        </is>
+      </c>
+      <c r="H423" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I423" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J423" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K423" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L423" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M423" t="inlineStr"/>
+      <c r="N423" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O423" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P423" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q423" t="n">
+        <v>20</v>
+      </c>
+      <c r="R423" t="n">
+        <v>22</v>
+      </c>
+      <c r="S423" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T423" t="inlineStr">
+        <is>
+          <t>1711649989</t>
+        </is>
+      </c>
+      <c r="U423" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1711649989</t>
+        </is>
+      </c>
+      <c r="V423" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="424">
+      <c r="A424" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B424" t="inlineStr">
+        <is>
+          <t>포쉬네일 하이푸스 가로수길점</t>
+        </is>
+      </c>
+      <c r="C424" t="inlineStr">
+        <is>
+          <t>6607144@naver.com</t>
+        </is>
+      </c>
+      <c r="D424" t="inlineStr"/>
+      <c r="E424" t="inlineStr">
+        <is>
+          <t>0507-1374-6141</t>
+        </is>
+      </c>
+      <c r="F424" t="inlineStr"/>
+      <c r="G424" t="inlineStr">
+        <is>
+          <t>서울특별시 강남구 가로수길 16 3층 포쉬네일 하이푸스 가로수길점</t>
+        </is>
+      </c>
+      <c r="H424" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/hifuss_garosugil</t>
+        </is>
+      </c>
+      <c r="I424" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J424" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K424" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L424" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M424" t="inlineStr"/>
+      <c r="N424" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O424" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P424" t="n">
+        <v>1335</v>
+      </c>
+      <c r="Q424" t="n">
+        <v>552</v>
+      </c>
+      <c r="R424" t="n">
+        <v>1887</v>
+      </c>
+      <c r="S424" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T424" t="inlineStr">
+        <is>
+          <t>20378592</t>
+        </is>
+      </c>
+      <c r="U424" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/20378592</t>
+        </is>
+      </c>
+      <c r="V424" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="425">
+      <c r="A425" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B425" t="inlineStr">
+        <is>
+          <t>임스네일</t>
+        </is>
+      </c>
+      <c r="C425" t="inlineStr">
+        <is>
+          <t>jkhsdm@naver.com</t>
+        </is>
+      </c>
+      <c r="D425" t="inlineStr"/>
+      <c r="E425" t="inlineStr">
+        <is>
+          <t>0507-1483-3322</t>
+        </is>
+      </c>
+      <c r="F425" t="inlineStr"/>
+      <c r="G425" t="inlineStr">
+        <is>
+          <t>서울특별시 강남구 도곡로25길 31 1층</t>
+        </is>
+      </c>
+      <c r="H425" t="inlineStr">
+        <is>
+          <t>http://www.instagram.com/lim.s_nail23</t>
+        </is>
+      </c>
+      <c r="I425" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J425" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K425" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L425" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M425" t="inlineStr"/>
+      <c r="N425" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O425" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P425" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q425" t="n">
+        <v>4</v>
+      </c>
+      <c r="R425" t="n">
+        <v>9</v>
+      </c>
+      <c r="S425" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T425" t="inlineStr">
+        <is>
+          <t>1409642751</t>
+        </is>
+      </c>
+      <c r="U425" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1409642751</t>
+        </is>
+      </c>
+      <c r="V425" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="426">
+      <c r="A426" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B426" t="inlineStr">
+        <is>
+          <t>네일도예쁨</t>
+        </is>
+      </c>
+      <c r="C426" t="inlineStr">
+        <is>
+          <t>555__555@naver.com</t>
+        </is>
+      </c>
+      <c r="D426" t="inlineStr"/>
+      <c r="E426" t="inlineStr"/>
+      <c r="F426" t="inlineStr"/>
+      <c r="G426" t="inlineStr">
+        <is>
+          <t>서울특별시 강남구 도곡로93길 12 래미안하이스턴상가 1층 102호 네일도예쁨</t>
+        </is>
+      </c>
+      <c r="H426" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I426" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J426" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K426" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L426" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M426" t="inlineStr"/>
+      <c r="N426" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O426" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P426" t="n">
+        <v>15</v>
+      </c>
+      <c r="Q426" t="n">
+        <v>10</v>
+      </c>
+      <c r="R426" t="n">
+        <v>25</v>
+      </c>
+      <c r="S426" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T426" t="inlineStr">
+        <is>
+          <t>1026259823</t>
+        </is>
+      </c>
+      <c r="U426" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1026259823</t>
+        </is>
+      </c>
+      <c r="V426" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="427">
+      <c r="A427" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B427" t="inlineStr">
+        <is>
+          <t>보이니 네일</t>
+        </is>
+      </c>
+      <c r="C427" t="inlineStr">
+        <is>
+          <t>love_hpness@naver.com</t>
+        </is>
+      </c>
+      <c r="D427" t="inlineStr"/>
+      <c r="E427" t="inlineStr">
+        <is>
+          <t>0507-1362-3065</t>
+        </is>
+      </c>
+      <c r="F427" t="inlineStr"/>
+      <c r="G427" t="inlineStr">
+        <is>
+          <t>서울특별시 강남구 압구정로10길 30-8 4층 (마사타코 건물로 들어오세요)</t>
+        </is>
+      </c>
+      <c r="H427" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/BOINEE_NAIL</t>
+        </is>
+      </c>
+      <c r="I427" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J427" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K427" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L427" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M427" t="inlineStr"/>
+      <c r="N427" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O427" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P427" t="n">
+        <v>180</v>
+      </c>
+      <c r="Q427" t="n">
+        <v>11</v>
+      </c>
+      <c r="R427" t="n">
+        <v>191</v>
+      </c>
+      <c r="S427" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T427" t="inlineStr">
+        <is>
+          <t>1147038913</t>
+        </is>
+      </c>
+      <c r="U427" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1147038913</t>
+        </is>
+      </c>
+      <c r="V427" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="428">
+      <c r="A428" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B428" t="inlineStr">
+        <is>
+          <t>네일슈슈</t>
+        </is>
+      </c>
+      <c r="C428" t="inlineStr">
+        <is>
+          <t>brilliant14694@naver.com</t>
+        </is>
+      </c>
+      <c r="D428" t="inlineStr"/>
+      <c r="E428" t="inlineStr">
+        <is>
+          <t>0507-1444-1395</t>
+        </is>
+      </c>
+      <c r="F428" t="inlineStr"/>
+      <c r="G428" t="inlineStr">
+        <is>
+          <t>서울특별시 강남구 테헤란로52길 16 테헤란아이파크상가4호</t>
+        </is>
+      </c>
+      <c r="H428" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/nail_shushu/</t>
+        </is>
+      </c>
+      <c r="I428" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J428" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K428" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L428" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M428" t="inlineStr"/>
+      <c r="N428" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O428" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P428" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q428" t="n">
+        <v>15</v>
+      </c>
+      <c r="R428" t="n">
+        <v>15</v>
+      </c>
+      <c r="S428" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T428" t="inlineStr">
+        <is>
+          <t>38264509</t>
+        </is>
+      </c>
+      <c r="U428" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/38264509</t>
+        </is>
+      </c>
+      <c r="V428" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="429">
+      <c r="A429" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B429" t="inlineStr">
+        <is>
+          <t>팔색조네일</t>
+        </is>
+      </c>
+      <c r="C429" t="inlineStr">
+        <is>
+          <t>3157520@naver.com</t>
+        </is>
+      </c>
+      <c r="D429" t="inlineStr"/>
+      <c r="E429" t="inlineStr">
+        <is>
+          <t>0507-1494-2781</t>
+        </is>
+      </c>
+      <c r="F429" t="inlineStr"/>
+      <c r="G429" t="inlineStr">
+        <is>
+          <t>서울특별시 강남구 학동로4길 10 3층 304호 팔색조네일</t>
+        </is>
+      </c>
+      <c r="H429" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/8colornail</t>
+        </is>
+      </c>
+      <c r="I429" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J429" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K429" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L429" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M429" t="inlineStr"/>
+      <c r="N429" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O429" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P429" t="n">
+        <v>68</v>
+      </c>
+      <c r="Q429" t="n">
+        <v>136</v>
+      </c>
+      <c r="R429" t="n">
+        <v>204</v>
+      </c>
+      <c r="S429" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T429" t="inlineStr">
+        <is>
+          <t>1383221614</t>
+        </is>
+      </c>
+      <c r="U429" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1383221614</t>
+        </is>
+      </c>
+      <c r="V429" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="430">
+      <c r="A430" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B430" t="inlineStr">
+        <is>
+          <t>끌레르 네일</t>
+        </is>
+      </c>
+      <c r="C430" t="inlineStr">
+        <is>
+          <t>dunggmi@naver.com</t>
+        </is>
+      </c>
+      <c r="D430" t="inlineStr"/>
+      <c r="E430" t="inlineStr">
+        <is>
+          <t>02-577-4359</t>
+        </is>
+      </c>
+      <c r="F430" t="inlineStr"/>
+      <c r="G430" t="inlineStr">
+        <is>
+          <t>서울특별시 강남구 선릉로 8 래미안블레스티지 근린생활시설 지하1층 28-1호</t>
+        </is>
+      </c>
+      <c r="H430" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I430" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J430" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K430" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L430" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M430" t="inlineStr"/>
+      <c r="N430" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O430" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P430" t="n">
+        <v>286</v>
+      </c>
+      <c r="Q430" t="n">
+        <v>7</v>
+      </c>
+      <c r="R430" t="n">
+        <v>293</v>
+      </c>
+      <c r="S430" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T430" t="inlineStr">
+        <is>
+          <t>1425622508</t>
+        </is>
+      </c>
+      <c r="U430" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1425622508</t>
+        </is>
+      </c>
+      <c r="V430" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="431">
+      <c r="A431" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B431" t="inlineStr">
+        <is>
+          <t>쥬이네일</t>
+        </is>
+      </c>
+      <c r="C431" t="inlineStr">
+        <is>
+          <t>zuy0ung@naver.com</t>
+        </is>
+      </c>
+      <c r="D431" t="inlineStr"/>
+      <c r="E431" t="inlineStr">
+        <is>
+          <t>0507-1311-5621</t>
+        </is>
+      </c>
+      <c r="F431" t="inlineStr"/>
+      <c r="G431" t="inlineStr">
+        <is>
+          <t>서울특별시 강남구 일원로5길 54 1층</t>
+        </is>
+      </c>
+      <c r="H431" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/juee_nail?igsh=ZGdiY2g5a2FyemRu&amp;utm_source=qr</t>
+        </is>
+      </c>
+      <c r="I431" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J431" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K431" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L431" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M431" t="inlineStr"/>
+      <c r="N431" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O431" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P431" t="n">
+        <v>202</v>
+      </c>
+      <c r="Q431" t="n">
+        <v>83</v>
+      </c>
+      <c r="R431" t="n">
+        <v>285</v>
+      </c>
+      <c r="S431" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T431" t="inlineStr">
+        <is>
+          <t>1791943614</t>
+        </is>
+      </c>
+      <c r="U431" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1791943614</t>
+        </is>
+      </c>
+      <c r="V431" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="432">
+      <c r="A432" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B432" t="inlineStr">
+        <is>
+          <t>빼꼼네일&amp;뷰티</t>
+        </is>
+      </c>
+      <c r="C432" t="inlineStr">
+        <is>
+          <t>hemni0228@naver.com</t>
+        </is>
+      </c>
+      <c r="D432" t="inlineStr"/>
+      <c r="E432" t="inlineStr">
+        <is>
+          <t>0507-1305-8739</t>
+        </is>
+      </c>
+      <c r="F432" t="inlineStr"/>
+      <c r="G432" t="inlineStr">
+        <is>
+          <t>서울특별시 강남구 선릉로126길 14-12 1층 빼꼼네일</t>
+        </is>
+      </c>
+      <c r="H432" t="inlineStr">
+        <is>
+          <t>http://pf.kakao.com/_LAMab</t>
+        </is>
+      </c>
+      <c r="I432" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J432" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K432" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L432" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M432" t="inlineStr"/>
+      <c r="N432" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O432" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P432" t="n">
+        <v>517</v>
+      </c>
+      <c r="Q432" t="n">
+        <v>50</v>
+      </c>
+      <c r="R432" t="n">
+        <v>567</v>
+      </c>
+      <c r="S432" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T432" t="inlineStr">
+        <is>
+          <t>1769410350</t>
+        </is>
+      </c>
+      <c r="U432" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1769410350</t>
+        </is>
+      </c>
+      <c r="V432" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="433">
+      <c r="A433" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B433" t="inlineStr">
+        <is>
+          <t>에이치인 네일</t>
+        </is>
+      </c>
+      <c r="C433" t="inlineStr">
+        <is>
+          <t>92_10_13@naver.com</t>
+        </is>
+      </c>
+      <c r="D433" t="inlineStr"/>
+      <c r="E433" t="inlineStr">
+        <is>
+          <t>0507-1313-4230</t>
+        </is>
+      </c>
+      <c r="F433" t="inlineStr"/>
+      <c r="G433" t="inlineStr">
+        <is>
+          <t>서울특별시 강남구 삼성로103길 22 1층 1-2호</t>
+        </is>
+      </c>
+      <c r="H433" t="inlineStr">
+        <is>
+          <t>http://www.instagram.com/h.in_nail</t>
+        </is>
+      </c>
+      <c r="I433" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J433" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K433" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L433" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M433" t="inlineStr"/>
+      <c r="N433" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O433" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P433" t="n">
+        <v>55</v>
+      </c>
+      <c r="Q433" t="n">
+        <v>6</v>
+      </c>
+      <c r="R433" t="n">
+        <v>61</v>
+      </c>
+      <c r="S433" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T433" t="inlineStr">
+        <is>
+          <t>1132309657</t>
+        </is>
+      </c>
+      <c r="U433" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1132309657</t>
+        </is>
+      </c>
+      <c r="V433" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="434">
+      <c r="A434" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B434" t="inlineStr">
+        <is>
+          <t>언드네일</t>
+        </is>
+      </c>
+      <c r="C434" t="inlineStr">
+        <is>
+          <t>kmj5_5@naver.com</t>
+        </is>
+      </c>
+      <c r="D434" t="inlineStr"/>
+      <c r="E434" t="inlineStr">
+        <is>
+          <t>0507-1349-0237</t>
+        </is>
+      </c>
+      <c r="F434" t="inlineStr"/>
+      <c r="G434" t="inlineStr">
+        <is>
+          <t>서울특별시 강남구 학동로45길 3-4 4층</t>
+        </is>
+      </c>
+      <c r="H434" t="inlineStr">
+        <is>
+          <t>http://pf.kakao.com/_xoxeKNn</t>
+        </is>
+      </c>
+      <c r="I434" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J434" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K434" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L434" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M434" t="inlineStr"/>
+      <c r="N434" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O434" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P434" t="n">
+        <v>49</v>
+      </c>
+      <c r="Q434" t="n">
+        <v>1</v>
+      </c>
+      <c r="R434" t="n">
+        <v>50</v>
+      </c>
+      <c r="S434" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T434" t="inlineStr">
+        <is>
+          <t>2082058115</t>
+        </is>
+      </c>
+      <c r="U434" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2082058115</t>
+        </is>
+      </c>
+      <c r="V434" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="435">
+      <c r="A435" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B435" t="inlineStr">
+        <is>
+          <t>네일원스튜디오</t>
+        </is>
+      </c>
+      <c r="C435" t="inlineStr">
+        <is>
+          <t>pear0406@naver.com</t>
+        </is>
+      </c>
+      <c r="D435" t="inlineStr"/>
+      <c r="E435" t="inlineStr">
+        <is>
+          <t>0507-1447-1054</t>
+        </is>
+      </c>
+      <c r="F435" t="inlineStr"/>
+      <c r="G435" t="inlineStr">
+        <is>
+          <t>서울특별시 강남구 압구정로46길 35 B1층 고바이씬 NAIL.1STUDIO</t>
+        </is>
+      </c>
+      <c r="H435" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/nail.1studio__?igsh=MXB1ajdoNmV3aTIzag==</t>
+        </is>
+      </c>
+      <c r="I435" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J435" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K435" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L435" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M435" t="inlineStr"/>
+      <c r="N435" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O435" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P435" t="n">
+        <v>217</v>
+      </c>
+      <c r="Q435" t="n">
+        <v>10</v>
+      </c>
+      <c r="R435" t="n">
+        <v>227</v>
+      </c>
+      <c r="S435" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T435" t="inlineStr">
+        <is>
+          <t>1311074001</t>
+        </is>
+      </c>
+      <c r="U435" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1311074001</t>
+        </is>
+      </c>
+      <c r="V435" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="436">
+      <c r="A436" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B436" t="inlineStr">
+        <is>
+          <t>네일20 선릉본점</t>
+        </is>
+      </c>
+      <c r="C436" t="inlineStr">
+        <is>
+          <t>gjbnxouijl315@naver.com</t>
+        </is>
+      </c>
+      <c r="D436" t="inlineStr"/>
+      <c r="E436" t="inlineStr">
+        <is>
+          <t>0507-1304-4157</t>
+        </is>
+      </c>
+      <c r="F436" t="inlineStr"/>
+      <c r="G436" t="inlineStr">
+        <is>
+          <t>서울특별시 강남구 테헤란로64길 25 5층</t>
+        </is>
+      </c>
+      <c r="H436" t="inlineStr">
+        <is>
+          <t>http://pf.kakao.com/_vkPsxj</t>
+        </is>
+      </c>
+      <c r="I436" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J436" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K436" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L436" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M436" t="inlineStr"/>
+      <c r="N436" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O436" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P436" t="n">
+        <v>1383</v>
+      </c>
+      <c r="Q436" t="n">
+        <v>728</v>
+      </c>
+      <c r="R436" t="n">
+        <v>2111</v>
+      </c>
+      <c r="S436" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T436" t="inlineStr">
+        <is>
+          <t>1226520921</t>
+        </is>
+      </c>
+      <c r="U436" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1226520921</t>
+        </is>
+      </c>
+      <c r="V436" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="437">
+      <c r="A437" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B437" t="inlineStr">
+        <is>
+          <t>미쥬네일 강남신논현점</t>
+        </is>
+      </c>
+      <c r="C437" t="inlineStr">
+        <is>
+          <t>ksmko2026@naver.com</t>
+        </is>
+      </c>
+      <c r="D437" t="inlineStr"/>
+      <c r="E437" t="inlineStr">
+        <is>
+          <t>0507-1446-0689</t>
+        </is>
+      </c>
+      <c r="F437" t="inlineStr"/>
+      <c r="G437" t="inlineStr">
+        <is>
+          <t>서울특별시 강남구 봉은사로2길 13 3층</t>
+        </is>
+      </c>
+      <c r="H437" t="inlineStr">
+        <is>
+          <t>http://pf.kakao.com/_PxehYs/chat</t>
+        </is>
+      </c>
+      <c r="I437" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J437" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K437" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L437" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M437" t="inlineStr"/>
+      <c r="N437" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O437" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P437" t="n">
+        <v>694</v>
+      </c>
+      <c r="Q437" t="n">
+        <v>82</v>
+      </c>
+      <c r="R437" t="n">
+        <v>776</v>
+      </c>
+      <c r="S437" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T437" t="inlineStr">
+        <is>
+          <t>1375175853</t>
+        </is>
+      </c>
+      <c r="U437" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1375175853</t>
+        </is>
+      </c>
+      <c r="V437" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="438">
+      <c r="A438" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B438" t="inlineStr">
+        <is>
+          <t>whyznail</t>
+        </is>
+      </c>
+      <c r="C438" t="inlineStr">
+        <is>
+          <t>whyznail@naver.com</t>
+        </is>
+      </c>
+      <c r="D438" t="inlineStr"/>
+      <c r="E438" t="inlineStr"/>
+      <c r="F438" t="inlineStr"/>
+      <c r="G438" t="inlineStr">
+        <is>
+          <t>서울특별시 강남구 선릉로146길 11</t>
+        </is>
+      </c>
+      <c r="H438" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/whyznail</t>
+        </is>
+      </c>
+      <c r="I438" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J438" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K438" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L438" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M438" t="inlineStr"/>
+      <c r="N438" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O438" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P438" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q438" t="n">
+        <v>0</v>
+      </c>
+      <c r="R438" t="n">
+        <v>0</v>
+      </c>
+      <c r="S438" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T438" t="inlineStr">
+        <is>
+          <t>36771867</t>
+        </is>
+      </c>
+      <c r="U438" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/36771867</t>
+        </is>
+      </c>
+      <c r="V438" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="439">
+      <c r="A439" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B439" t="inlineStr">
+        <is>
+          <t>레푸스 강남세곡점</t>
+        </is>
+      </c>
+      <c r="C439" t="inlineStr">
+        <is>
+          <t>segok569@naver.com</t>
+        </is>
+      </c>
+      <c r="D439" t="inlineStr"/>
+      <c r="E439" t="inlineStr">
+        <is>
+          <t>0507-1494-9977</t>
+        </is>
+      </c>
+      <c r="F439" t="inlineStr"/>
+      <c r="G439" t="inlineStr">
+        <is>
+          <t>서울특별시 강남구 헌릉로 569 강남리더스프라자 4층 401-1호</t>
+        </is>
+      </c>
+      <c r="H439" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/segok569</t>
+        </is>
+      </c>
+      <c r="I439" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J439" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K439" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L439" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M439" t="inlineStr"/>
+      <c r="N439" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O439" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P439" t="n">
+        <v>191</v>
+      </c>
+      <c r="Q439" t="n">
+        <v>483</v>
+      </c>
+      <c r="R439" t="n">
+        <v>674</v>
+      </c>
+      <c r="S439" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T439" t="inlineStr">
+        <is>
+          <t>1486263326</t>
+        </is>
+      </c>
+      <c r="U439" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1486263326</t>
+        </is>
+      </c>
+      <c r="V439" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="440">
+      <c r="A440" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B440" t="inlineStr">
+        <is>
+          <t>뷰티블룸</t>
+        </is>
+      </c>
+      <c r="C440" t="inlineStr">
+        <is>
+          <t>ksi6439@naver.com</t>
+        </is>
+      </c>
+      <c r="D440" t="inlineStr"/>
+      <c r="E440" t="inlineStr">
+        <is>
+          <t>070-4115-0656</t>
+        </is>
+      </c>
+      <c r="F440" t="inlineStr"/>
+      <c r="G440" t="inlineStr">
+        <is>
+          <t>서울특별시 강남구 학동로 342 sk허브 지하1층 117호</t>
+        </is>
+      </c>
+      <c r="H440" t="inlineStr">
+        <is>
+          <t>http://instagram.com/b.bloom_nail</t>
+        </is>
+      </c>
+      <c r="I440" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J440" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K440" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L440" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M440" t="inlineStr"/>
+      <c r="N440" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O440" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P440" t="n">
+        <v>11</v>
+      </c>
+      <c r="Q440" t="n">
+        <v>7</v>
+      </c>
+      <c r="R440" t="n">
+        <v>18</v>
+      </c>
+      <c r="S440" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T440" t="inlineStr">
+        <is>
+          <t>746435071</t>
+        </is>
+      </c>
+      <c r="U440" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/746435071</t>
+        </is>
+      </c>
+      <c r="V440" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="441">
+      <c r="A441" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B441" t="inlineStr">
+        <is>
+          <t>네일감성</t>
+        </is>
+      </c>
+      <c r="C441" t="inlineStr">
+        <is>
+          <t>gab316@naver.com</t>
+        </is>
+      </c>
+      <c r="D441" t="inlineStr"/>
+      <c r="E441" t="inlineStr"/>
+      <c r="F441" t="inlineStr"/>
+      <c r="G441" t="inlineStr">
+        <is>
+          <t>서울특별시 강남구 선릉로130길 20 래미안삼성2차상가 2층 네일감성</t>
+        </is>
+      </c>
+      <c r="H441" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/_nailbbo</t>
+        </is>
+      </c>
+      <c r="I441" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J441" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K441" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L441" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M441" t="inlineStr"/>
+      <c r="N441" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O441" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P441" t="n">
+        <v>52</v>
+      </c>
+      <c r="Q441" t="n">
+        <v>1</v>
+      </c>
+      <c r="R441" t="n">
+        <v>53</v>
+      </c>
+      <c r="S441" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T441" t="inlineStr">
+        <is>
+          <t>1962553293</t>
+        </is>
+      </c>
+      <c r="U441" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1962553293</t>
+        </is>
+      </c>
+      <c r="V441" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="442">
+      <c r="A442" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B442" t="inlineStr">
+        <is>
+          <t>플디아네일</t>
+        </is>
+      </c>
+      <c r="C442" t="inlineStr">
+        <is>
+          <t>syonnyshinny0_0@naver.com</t>
+        </is>
+      </c>
+      <c r="D442" t="inlineStr"/>
+      <c r="E442" t="inlineStr">
+        <is>
+          <t>0507-1486-2397</t>
+        </is>
+      </c>
+      <c r="F442" t="inlineStr"/>
+      <c r="G442" t="inlineStr">
+        <is>
+          <t>서울특별시 강남구 학동로55길 12-7 102호</t>
+        </is>
+      </c>
+      <c r="H442" t="inlineStr">
+        <is>
+          <t>http://pf.kakao.com/_xhtxaKn</t>
+        </is>
+      </c>
+      <c r="I442" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J442" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K442" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L442" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M442" t="inlineStr"/>
+      <c r="N442" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O442" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P442" t="n">
+        <v>145</v>
+      </c>
+      <c r="Q442" t="n">
+        <v>22</v>
+      </c>
+      <c r="R442" t="n">
+        <v>167</v>
+      </c>
+      <c r="S442" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T442" t="inlineStr">
+        <is>
+          <t>1925563003</t>
+        </is>
+      </c>
+      <c r="U442" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1925563003</t>
+        </is>
+      </c>
+      <c r="V442" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="443">
+      <c r="A443" t="inlineStr">
+        <is>
+          <t>세무사</t>
+        </is>
+      </c>
+      <c r="B443" t="inlineStr">
+        <is>
+          <t>세성세무법인 삼성지점</t>
+        </is>
+      </c>
+      <c r="C443" t="inlineStr">
+        <is>
+          <t>sesung1216@naver.com</t>
+        </is>
+      </c>
+      <c r="D443" t="inlineStr"/>
+      <c r="E443" t="inlineStr">
+        <is>
+          <t>02-515-4642</t>
+        </is>
+      </c>
+      <c r="F443" t="inlineStr"/>
+      <c r="G443" t="inlineStr">
+        <is>
+          <t>서울특별시 강남구 봉은사로 454 금탁타워 5층</t>
+        </is>
+      </c>
+      <c r="H443" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/sesung1216</t>
+        </is>
+      </c>
+      <c r="I443" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J443" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K443" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L443" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M443" t="inlineStr"/>
+      <c r="N443" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O443" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P443" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q443" t="n">
+        <v>44</v>
+      </c>
+      <c r="R443" t="n">
+        <v>44</v>
+      </c>
+      <c r="S443" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T443" t="inlineStr">
+        <is>
+          <t>1397509005</t>
+        </is>
+      </c>
+      <c r="U443" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1397509005</t>
+        </is>
+      </c>
+      <c r="V443" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="444">
+      <c r="A444" t="inlineStr">
+        <is>
+          <t>속눈썹증모,연장</t>
+        </is>
+      </c>
+      <c r="B444" t="inlineStr">
+        <is>
+          <t>워너비뷰티</t>
+        </is>
+      </c>
+      <c r="C444" t="inlineStr"/>
+      <c r="D444" t="inlineStr"/>
+      <c r="E444" t="inlineStr">
+        <is>
+          <t>02-552-4043</t>
+        </is>
+      </c>
+      <c r="F444" t="inlineStr"/>
+      <c r="G444" t="inlineStr">
+        <is>
+          <t>서울특별시 강남구 삼성로100길 25 2층</t>
+        </is>
+      </c>
+      <c r="H444" t="inlineStr">
+        <is>
+          <t>http://pf.kakao.com/_xaxfwTC</t>
+        </is>
+      </c>
+      <c r="I444" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J444" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K444" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L444" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M444" t="inlineStr"/>
+      <c r="N444" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O444" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P444" t="n">
         <v>230</v>
       </c>
-      <c r="Q393" t="n">
+      <c r="Q444" t="n">
         <v>66</v>
       </c>
-      <c r="R393" t="n">
+      <c r="R444" t="n">
         <v>296</v>
       </c>
-      <c r="S393" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T393" t="inlineStr">
+      <c r="S444" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T444" t="inlineStr">
         <is>
           <t>1523636698</t>
         </is>
       </c>
-      <c r="U393" t="inlineStr">
+      <c r="U444" t="inlineStr">
         <is>
           <t>https://m.place.naver.com/place/1523636698</t>
         </is>
       </c>
-      <c r="V393" t="inlineStr">
+      <c r="V444" t="inlineStr">
         <is>
           <t>2026-04-29</t>
         </is>
